--- a/models/resnet18/data_train_statistics.xlsx
+++ b/models/resnet18/data_train_statistics.xlsx
@@ -485,25 +485,25 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D2" t="n">
-        <v>58673.375</v>
+        <v>57244.16796875</v>
       </c>
       <c r="E2" t="n">
         <v>104155.375</v>
       </c>
       <c r="F2" t="n">
-        <v>39709575954.75</v>
+        <v>1010045075649.812</v>
       </c>
       <c r="G2" t="n">
-        <v>100729.9919200797</v>
+        <v>100738.3266843829</v>
       </c>
       <c r="H2" t="n">
-        <v>7478343.853253898</v>
+        <v>7189362.991270711</v>
       </c>
       <c r="I2" t="n">
-        <v>2734.656075862904</v>
+        <v>2681.298750842716</v>
       </c>
     </row>
     <row r="3">
@@ -516,25 +516,25 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>305507</v>
+        <v>7751633</v>
       </c>
       <c r="D3" t="n">
-        <v>276.127197265625</v>
+        <v>272.838134765625</v>
       </c>
       <c r="E3" t="n">
-        <v>306.11328125</v>
+        <v>307.6376953125</v>
       </c>
       <c r="F3" t="n">
-        <v>91521405.62451172</v>
+        <v>2324946528.585205</v>
       </c>
       <c r="G3" t="n">
-        <v>299.572204972428</v>
+        <v>299.9299023296387</v>
       </c>
       <c r="H3" t="n">
-        <v>9.972362060689962</v>
+        <v>6.173281914396444</v>
       </c>
       <c r="I3" t="n">
-        <v>3.157904694681263</v>
+        <v>2.484609006342133</v>
       </c>
     </row>
     <row r="4">
@@ -547,25 +547,25 @@
         <v>1000</v>
       </c>
       <c r="C4" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D4" t="n">
-        <v>-795.3125</v>
+        <v>-4322.37109375</v>
       </c>
       <c r="E4" t="n">
         <v>3362.25</v>
       </c>
       <c r="F4" t="n">
-        <v>513599440.2956543</v>
+        <v>13020649555.28638</v>
       </c>
       <c r="G4" t="n">
-        <v>1302.831023179192</v>
+        <v>1298.633576030693</v>
       </c>
       <c r="H4" t="n">
-        <v>157696.8650416724</v>
+        <v>130661.1472207419</v>
       </c>
       <c r="I4" t="n">
-        <v>397.1106458427832</v>
+        <v>361.4708110217779</v>
       </c>
     </row>
     <row r="5">
@@ -578,25 +578,25 @@
         <v>975</v>
       </c>
       <c r="C5" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D5" t="n">
-        <v>1371.25244140625</v>
+        <v>-2161.78466796875</v>
       </c>
       <c r="E5" t="n">
         <v>5434.396484375</v>
       </c>
       <c r="F5" t="n">
-        <v>1367346733.543213</v>
+        <v>34770480594.78125</v>
       </c>
       <c r="G5" t="n">
-        <v>3468.504060045997</v>
+        <v>3467.884867293271</v>
       </c>
       <c r="H5" t="n">
-        <v>145863.5331202465</v>
+        <v>125153.9994691315</v>
       </c>
       <c r="I5" t="n">
-        <v>381.9208466688438</v>
+        <v>353.771111693891</v>
       </c>
     </row>
     <row r="6">
@@ -609,25 +609,25 @@
         <v>950</v>
       </c>
       <c r="C6" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D6" t="n">
-        <v>3600.1787109375</v>
+        <v>50.734619140625</v>
       </c>
       <c r="E6" t="n">
         <v>7546.09375</v>
       </c>
       <c r="F6" t="n">
-        <v>2239265295.639893</v>
+        <v>56986195687.36523</v>
       </c>
       <c r="G6" t="n">
-        <v>5680.271564565524</v>
+        <v>5683.601787732804</v>
       </c>
       <c r="H6" t="n">
-        <v>133867.400912198</v>
+        <v>118571.0881351793</v>
       </c>
       <c r="I6" t="n">
-        <v>365.8789429745829</v>
+        <v>344.3415283336869</v>
       </c>
     </row>
     <row r="7">
@@ -640,25 +640,25 @@
         <v>925</v>
       </c>
       <c r="C7" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D7" t="n">
-        <v>5878.83984375</v>
+        <v>2381.0029296875</v>
       </c>
       <c r="E7" t="n">
         <v>9699.1630859375</v>
       </c>
       <c r="F7" t="n">
-        <v>3130243913.413086</v>
+        <v>79689262969.65063</v>
       </c>
       <c r="G7" t="n">
-        <v>7940.388093423147</v>
+        <v>7947.925493433777</v>
       </c>
       <c r="H7" t="n">
-        <v>122649.1940823033</v>
+        <v>112540.3054415104</v>
       </c>
       <c r="I7" t="n">
-        <v>350.2130695481013</v>
+        <v>335.4702750490875</v>
       </c>
     </row>
     <row r="8">
@@ -671,25 +671,25 @@
         <v>900</v>
       </c>
       <c r="C8" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D8" t="n">
-        <v>8211.9130859375</v>
+        <v>4762.21826171875</v>
       </c>
       <c r="E8" t="n">
         <v>11911.2939453125</v>
       </c>
       <c r="F8" t="n">
-        <v>4041460075.727539</v>
+        <v>102910447713.0308</v>
       </c>
       <c r="G8" t="n">
-        <v>10251.84054438797</v>
+        <v>10263.92440385074</v>
       </c>
       <c r="H8" t="n">
-        <v>112612.6139778266</v>
+        <v>107619.6883903062</v>
       </c>
       <c r="I8" t="n">
-        <v>335.5780296411352</v>
+        <v>328.0543985230287</v>
       </c>
     </row>
     <row r="9">
@@ -702,25 +702,25 @@
         <v>875</v>
       </c>
       <c r="C9" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D9" t="n">
-        <v>10455.00390625</v>
+        <v>7199.91796875</v>
       </c>
       <c r="E9" t="n">
         <v>14205.31640625</v>
       </c>
       <c r="F9" t="n">
-        <v>4974215086.421875</v>
+        <v>126682940276.2607</v>
       </c>
       <c r="G9" t="n">
-        <v>12617.92989265299</v>
+        <v>12634.90880808245</v>
       </c>
       <c r="H9" t="n">
-        <v>104114.926583027</v>
+        <v>104140.4987560865</v>
       </c>
       <c r="I9" t="n">
-        <v>322.6684468351793</v>
+        <v>322.7080704848989</v>
       </c>
     </row>
     <row r="10">
@@ -733,25 +733,25 @@
         <v>850</v>
       </c>
       <c r="C10" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D10" t="n">
-        <v>12720.265625</v>
+        <v>9703.72265625</v>
       </c>
       <c r="E10" t="n">
         <v>16554.390625</v>
       </c>
       <c r="F10" t="n">
-        <v>5929903231.105469</v>
+        <v>151039716702.8516</v>
       </c>
       <c r="G10" t="n">
-        <v>15042.19297724982</v>
+        <v>15064.16762018232</v>
       </c>
       <c r="H10" t="n">
-        <v>97429.13498867453</v>
+        <v>102285.027405662</v>
       </c>
       <c r="I10" t="n">
-        <v>312.1364044591315</v>
+        <v>319.8203048676897</v>
       </c>
     </row>
     <row r="11">
@@ -764,25 +764,25 @@
         <v>825</v>
       </c>
       <c r="C11" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D11" t="n">
-        <v>15039.1875</v>
+        <v>12279.2109375</v>
       </c>
       <c r="E11" t="n">
         <v>18961.08203125</v>
       </c>
       <c r="F11" t="n">
-        <v>6909829148.941406</v>
+        <v>176012794504.0391</v>
       </c>
       <c r="G11" t="n">
-        <v>17527.93923398068</v>
+        <v>17554.8941535819</v>
       </c>
       <c r="H11" t="n">
-        <v>92501.97420731724</v>
+        <v>101978.000511229</v>
       </c>
       <c r="I11" t="n">
-        <v>304.1413720744306</v>
+        <v>319.3399450604778</v>
       </c>
     </row>
     <row r="12">
@@ -795,25 +795,25 @@
         <v>800</v>
       </c>
       <c r="C12" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D12" t="n">
-        <v>17414.94140625</v>
+        <v>14931.76171875</v>
       </c>
       <c r="E12" t="n">
         <v>21428.171875</v>
       </c>
       <c r="F12" t="n">
-        <v>7915260636.671875</v>
+        <v>201632890778.4531</v>
       </c>
       <c r="G12" t="n">
-        <v>20078.3846416751</v>
+        <v>20110.1520231545</v>
       </c>
       <c r="H12" t="n">
-        <v>89252.44218445147</v>
+        <v>103094.8214974809</v>
       </c>
       <c r="I12" t="n">
-        <v>298.7514722716048</v>
+        <v>321.0838231637977</v>
       </c>
     </row>
     <row r="13">
@@ -826,25 +826,25 @@
         <v>775</v>
       </c>
       <c r="C13" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D13" t="n">
-        <v>19848.59375</v>
+        <v>17671.6328125</v>
       </c>
       <c r="E13" t="n">
-        <v>23959.6328125</v>
+        <v>24017.8671875</v>
       </c>
       <c r="F13" t="n">
-        <v>8947517585.609375</v>
+        <v>227932347971.168</v>
       </c>
       <c r="G13" t="n">
-        <v>22696.87732576743</v>
+        <v>22733.16695008448</v>
       </c>
       <c r="H13" t="n">
-        <v>87483.35484988574</v>
+        <v>105363.2186831624</v>
       </c>
       <c r="I13" t="n">
-        <v>295.7758523779211</v>
+        <v>324.5970096645415</v>
       </c>
     </row>
     <row r="14">
@@ -857,25 +857,25 @@
         <v>750</v>
       </c>
       <c r="C14" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D14" t="n">
-        <v>22342.69140625</v>
+        <v>20502.62890625</v>
       </c>
       <c r="E14" t="n">
-        <v>26559.78125</v>
+        <v>26709.1796875</v>
       </c>
       <c r="F14" t="n">
-        <v>10008088628.02734</v>
+        <v>254948868587.6484</v>
       </c>
       <c r="G14" t="n">
-        <v>25387.19345140845</v>
+        <v>25427.69924903916</v>
       </c>
       <c r="H14" t="n">
-        <v>87132.9965972168</v>
+        <v>108630.7976827274</v>
       </c>
       <c r="I14" t="n">
-        <v>295.182988326253</v>
+        <v>329.5918653163749</v>
       </c>
     </row>
     <row r="15">
@@ -888,25 +888,25 @@
         <v>725</v>
       </c>
       <c r="C15" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D15" t="n">
-        <v>27535.30859375</v>
+        <v>26421.2265625</v>
       </c>
       <c r="E15" t="n">
-        <v>31994.69921875</v>
+        <v>32365.8828125</v>
       </c>
       <c r="F15" t="n">
-        <v>12220838968.23828</v>
+        <v>311301878224.5312</v>
       </c>
       <c r="G15" t="n">
-        <v>31000.20538950096</v>
+        <v>31048.14929756414</v>
       </c>
       <c r="H15" t="n">
-        <v>89808.19254686525</v>
+        <v>117349.6627435521</v>
       </c>
       <c r="I15" t="n">
-        <v>299.6801504051699</v>
+        <v>342.5633704054654</v>
       </c>
     </row>
     <row r="16">
@@ -919,25 +919,25 @@
         <v>700</v>
       </c>
       <c r="C16" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D16" t="n">
-        <v>33062.80078125</v>
+        <v>31926.1953125</v>
       </c>
       <c r="E16" t="n">
-        <v>37879.70703125</v>
+        <v>38350.328125</v>
       </c>
       <c r="F16" t="n">
-        <v>14568251187.83594</v>
+        <v>371069337126.7852</v>
       </c>
       <c r="G16" t="n">
-        <v>36954.80974444583</v>
+        <v>37009.14445029756</v>
       </c>
       <c r="H16" t="n">
-        <v>96415.4858910925</v>
+        <v>128424.704750733</v>
       </c>
       <c r="I16" t="n">
-        <v>310.5084312721516</v>
+        <v>358.3639278034732</v>
       </c>
     </row>
     <row r="17">
@@ -950,25 +950,25 @@
         <v>650</v>
       </c>
       <c r="C17" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D17" t="n">
-        <v>38960.63671875</v>
+        <v>37639.1796875</v>
       </c>
       <c r="E17" t="n">
-        <v>44210.859375</v>
+        <v>44689.9921875</v>
       </c>
       <c r="F17" t="n">
-        <v>17069371154.62109</v>
+        <v>434745270714.0078</v>
       </c>
       <c r="G17" t="n">
-        <v>43299.31955065746</v>
+        <v>43359.95705686945</v>
       </c>
       <c r="H17" t="n">
-        <v>108310.3016348564</v>
+        <v>142390.2501690685</v>
       </c>
       <c r="I17" t="n">
-        <v>329.1053047807896</v>
+        <v>377.3463265609836</v>
       </c>
     </row>
     <row r="18">
@@ -981,25 +981,25 @@
         <v>600</v>
       </c>
       <c r="C18" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D18" t="n">
-        <v>45283.734375</v>
+        <v>43742.5234375</v>
       </c>
       <c r="E18" t="n">
-        <v>51012.6640625</v>
+        <v>51450.26171875</v>
       </c>
       <c r="F18" t="n">
-        <v>19750884542.58594</v>
+        <v>503014445019.2148</v>
       </c>
       <c r="G18" t="n">
-        <v>50101.42749084501</v>
+        <v>50168.88326167911</v>
       </c>
       <c r="H18" t="n">
-        <v>128461.09964814</v>
+        <v>161298.3398765762</v>
       </c>
       <c r="I18" t="n">
-        <v>358.4147034485891</v>
+        <v>401.6196457801539</v>
       </c>
     </row>
     <row r="19">
@@ -1012,25 +1012,25 @@
         <v>550</v>
       </c>
       <c r="C19" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D19" t="n">
-        <v>52094.84765625</v>
+        <v>50245.98046875</v>
       </c>
       <c r="E19" t="n">
-        <v>58333.0546875</v>
+        <v>58780.80859375</v>
       </c>
       <c r="F19" t="n">
-        <v>22643571035.44922</v>
+        <v>576675784358.5039</v>
       </c>
       <c r="G19" t="n">
-        <v>57439.2113892547</v>
+        <v>57515.60495288333</v>
       </c>
       <c r="H19" t="n">
-        <v>161318.6047142559</v>
+        <v>189168.9907577027</v>
       </c>
       <c r="I19" t="n">
-        <v>401.6448738802176</v>
+        <v>434.9356167959836</v>
       </c>
     </row>
     <row r="20">
@@ -1043,25 +1043,25 @@
         <v>500</v>
       </c>
       <c r="C20" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D20" t="n">
-        <v>59485.546875</v>
+        <v>57320.828125</v>
       </c>
       <c r="E20" t="n">
-        <v>66329.875</v>
+        <v>66800.484375</v>
       </c>
       <c r="F20" t="n">
-        <v>25784988848.125</v>
+        <v>656691741613.0039</v>
       </c>
       <c r="G20" t="n">
-        <v>65407.94395011133</v>
+        <v>65496.1137798598</v>
       </c>
       <c r="H20" t="n">
-        <v>213322.1037005024</v>
+        <v>231301.7860214092</v>
       </c>
       <c r="I20" t="n">
-        <v>461.8680587575876</v>
+        <v>480.9384430687666</v>
       </c>
     </row>
     <row r="21">
@@ -1074,25 +1074,25 @@
         <v>450</v>
       </c>
       <c r="C21" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D21" t="n">
-        <v>67591.1875</v>
+        <v>65214.02734375</v>
       </c>
       <c r="E21" t="n">
-        <v>75126.015625</v>
+        <v>75588.890625</v>
       </c>
       <c r="F21" t="n">
-        <v>29222842002.22656</v>
+        <v>744277001351.5781</v>
       </c>
       <c r="G21" t="n">
-        <v>74128.63441605041</v>
+        <v>74231.55808921905</v>
       </c>
       <c r="H21" t="n">
-        <v>293325.4762004915</v>
+        <v>294324.2188584534</v>
       </c>
       <c r="I21" t="n">
-        <v>541.5953066640178</v>
+        <v>542.5165609070874</v>
       </c>
     </row>
     <row r="22">
@@ -1105,25 +1105,25 @@
         <v>400</v>
       </c>
       <c r="C22" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D22" t="n">
-        <v>76645</v>
+        <v>74065</v>
       </c>
       <c r="E22" t="n">
-        <v>84821.4375</v>
+        <v>85314.6875</v>
       </c>
       <c r="F22" t="n">
-        <v>33021461625.3125</v>
+        <v>841055358257.5859</v>
       </c>
       <c r="G22" t="n">
-        <v>83764.46946946233</v>
+        <v>83883.88942473142</v>
       </c>
       <c r="H22" t="n">
-        <v>410598.6127431005</v>
+        <v>386642.5306040271</v>
       </c>
       <c r="I22" t="n">
-        <v>640.7796912692385</v>
+        <v>621.8058624715813</v>
       </c>
     </row>
     <row r="23">
@@ -1136,25 +1136,25 @@
         <v>350</v>
       </c>
       <c r="C23" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D23" t="n">
-        <v>87026.625</v>
+        <v>83836.4375</v>
       </c>
       <c r="E23" t="n">
-        <v>95704</v>
+        <v>96179.8125</v>
       </c>
       <c r="F23" t="n">
-        <v>37271899285.625</v>
+        <v>949323544593</v>
       </c>
       <c r="G23" t="n">
-        <v>94546.41666698374</v>
+        <v>94682.17574632539</v>
       </c>
       <c r="H23" t="n">
-        <v>570460.4172637919</v>
+        <v>516897.0087338662</v>
       </c>
       <c r="I23" t="n">
-        <v>755.2883007592477</v>
+        <v>718.9554984377448</v>
       </c>
     </row>
     <row r="24">
@@ -1167,25 +1167,25 @@
         <v>300</v>
       </c>
       <c r="C24" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D24" t="n">
-        <v>99241.125</v>
+        <v>95370.125</v>
       </c>
       <c r="E24" t="n">
-        <v>108172.625</v>
+        <v>108594.3125</v>
       </c>
       <c r="F24" t="n">
-        <v>42110715728.625</v>
+        <v>1072548696688.875</v>
       </c>
       <c r="G24" t="n">
-        <v>106820.8852173798</v>
+        <v>106972.2169799613</v>
       </c>
       <c r="H24" t="n">
-        <v>758775.621460752</v>
+        <v>686421.3064129201</v>
       </c>
       <c r="I24" t="n">
-        <v>871.0772764001779</v>
+        <v>828.5054655299023</v>
       </c>
     </row>
     <row r="25">
@@ -1198,25 +1198,25 @@
         <v>250</v>
       </c>
       <c r="C25" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D25" t="n">
-        <v>106261.625</v>
+        <v>102082.0625</v>
       </c>
       <c r="E25" t="n">
-        <v>115123.9375</v>
+        <v>115556.1875</v>
       </c>
       <c r="F25" t="n">
-        <v>44814643297.125</v>
+        <v>1141391854346</v>
       </c>
       <c r="G25" t="n">
-        <v>113679.8504815229</v>
+        <v>113838.390256026</v>
       </c>
       <c r="H25" t="n">
-        <v>842305.7707227251</v>
+        <v>775708.1545666415</v>
       </c>
       <c r="I25" t="n">
-        <v>917.772178006462</v>
+        <v>880.7429560130705</v>
       </c>
     </row>
     <row r="26">
@@ -1229,25 +1229,25 @@
         <v>200</v>
       </c>
       <c r="C26" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D26" t="n">
-        <v>113608.75</v>
+        <v>109609.875</v>
       </c>
       <c r="E26" t="n">
-        <v>122678.5</v>
+        <v>123144.6875</v>
       </c>
       <c r="F26" t="n">
-        <v>47761363946.5</v>
+        <v>1216395987873.125</v>
       </c>
       <c r="G26" t="n">
-        <v>121154.7010702201</v>
+        <v>121319.0374945407</v>
       </c>
       <c r="H26" t="n">
-        <v>890043.0488890561</v>
+        <v>846740.6260925599</v>
       </c>
       <c r="I26" t="n">
-        <v>943.4209287953369</v>
+        <v>920.1851042548776</v>
       </c>
     </row>
     <row r="27">
@@ -1260,25 +1260,25 @@
         <v>150</v>
       </c>
       <c r="C27" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D27" t="n">
-        <v>121905.875</v>
+        <v>118110.75</v>
       </c>
       <c r="E27" t="n">
-        <v>130996</v>
+        <v>131516.5625</v>
       </c>
       <c r="F27" t="n">
-        <v>51011633116.5</v>
+        <v>1299099068600.562</v>
       </c>
       <c r="G27" t="n">
-        <v>129399.5533347031</v>
+        <v>129567.5505213141</v>
       </c>
       <c r="H27" t="n">
-        <v>869385.9297436732</v>
+        <v>865795.0590049953</v>
       </c>
       <c r="I27" t="n">
-        <v>932.4086709933972</v>
+        <v>930.4810900845838</v>
       </c>
     </row>
     <row r="28">
@@ -1291,25 +1291,25 @@
         <v>100</v>
       </c>
       <c r="C28" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D28" t="n">
-        <v>131533.25</v>
+        <v>127869.875</v>
       </c>
       <c r="E28" t="n">
-        <v>140232.0625</v>
+        <v>140866.1875</v>
       </c>
       <c r="F28" t="n">
-        <v>54658923434.9375</v>
+        <v>1391879173863.688</v>
       </c>
       <c r="G28" t="n">
-        <v>138651.516254807</v>
+        <v>138821.1103664469</v>
       </c>
       <c r="H28" t="n">
-        <v>746525.3689318255</v>
+        <v>791618.533078799</v>
       </c>
       <c r="I28" t="n">
-        <v>864.0169957424596</v>
+        <v>889.7294718501793</v>
       </c>
     </row>
     <row r="29">
@@ -1322,25 +1322,25 @@
         <v>1000</v>
       </c>
       <c r="C29" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.725713729858398</v>
+        <v>-2.138814926147461</v>
       </c>
       <c r="E29" t="n">
-        <v>1.451874732971191</v>
+        <v>1.7308349609375</v>
       </c>
       <c r="F29" t="n">
-        <v>444.380012512207</v>
+        <v>-2422.814295768738</v>
       </c>
       <c r="G29" t="n">
-        <v>0.00112724434833571</v>
+        <v>-0.0002416429364459035</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00390867029898018</v>
+        <v>0.003718447210900799</v>
       </c>
       <c r="I29" t="n">
-        <v>0.06251935939355249</v>
+        <v>0.060979071909146</v>
       </c>
     </row>
     <row r="30">
@@ -1353,25 +1353,25 @@
         <v>975</v>
       </c>
       <c r="C30" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D30" t="n">
-        <v>-2.180203437805176</v>
+        <v>-2.400935173034668</v>
       </c>
       <c r="E30" t="n">
-        <v>1.554008483886719</v>
+        <v>2.099066734313965</v>
       </c>
       <c r="F30" t="n">
-        <v>-103.0356607437134</v>
+        <v>-11428.87547302246</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0002613672149514053</v>
+        <v>-0.001139875653862042</v>
       </c>
       <c r="H30" t="n">
-        <v>0.009292203761730655</v>
+        <v>0.008556248384394498</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0963960775225354</v>
+        <v>0.09249999126699687</v>
       </c>
     </row>
     <row r="31">
@@ -1384,25 +1384,25 @@
         <v>950</v>
       </c>
       <c r="C31" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D31" t="n">
-        <v>-3.416229248046875</v>
+        <v>-4.727029800415039</v>
       </c>
       <c r="E31" t="n">
-        <v>2.063743591308594</v>
+        <v>2.412403106689453</v>
       </c>
       <c r="F31" t="n">
-        <v>-670.7846574783325</v>
+        <v>-23667.27976608276</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.001701557659666308</v>
+        <v>-0.002360490851631011</v>
       </c>
       <c r="H31" t="n">
-        <v>0.01782486437712647</v>
+        <v>0.01652364976495156</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1335097913155678</v>
+        <v>0.1285443494088774</v>
       </c>
     </row>
     <row r="32">
@@ -1415,25 +1415,25 @@
         <v>925</v>
       </c>
       <c r="C32" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D32" t="n">
-        <v>-4.586678504943848</v>
+        <v>-6.604527473449707</v>
       </c>
       <c r="E32" t="n">
-        <v>2.348650932312012</v>
+        <v>2.899991035461426</v>
       </c>
       <c r="F32" t="n">
-        <v>-1143.547781944275</v>
+        <v>-34448.7924823761</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.002900800526470823</v>
+        <v>-0.003435800831699997</v>
       </c>
       <c r="H32" t="n">
-        <v>0.02608362177911355</v>
+        <v>0.02449627987137436</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1615042469383191</v>
+        <v>0.1565128744588584</v>
       </c>
     </row>
     <row r="33">
@@ -1446,25 +1446,25 @@
         <v>900</v>
       </c>
       <c r="C33" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D33" t="n">
-        <v>-5.686241149902344</v>
+        <v>-7.907404899597168</v>
       </c>
       <c r="E33" t="n">
-        <v>2.842789649963379</v>
+        <v>3.30113410949707</v>
       </c>
       <c r="F33" t="n">
-        <v>-1522.166777610779</v>
+        <v>-42482.3123884201</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.003861231038691228</v>
+        <v>-0.004237035719360724</v>
       </c>
       <c r="H33" t="n">
-        <v>0.03245355688458516</v>
+        <v>0.03083903847651879</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1801487076961285</v>
+        <v>0.1756104737096247</v>
       </c>
     </row>
     <row r="34">
@@ -1477,25 +1477,25 @@
         <v>875</v>
       </c>
       <c r="C34" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D34" t="n">
-        <v>-6.651564598083496</v>
+        <v>-8.800127029418945</v>
       </c>
       <c r="E34" t="n">
-        <v>3.247403144836426</v>
+        <v>3.340728759765625</v>
       </c>
       <c r="F34" t="n">
-        <v>-1837.541897773743</v>
+        <v>-47918.9500875473</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.004661232865505232</v>
+        <v>-0.004779266752215353</v>
       </c>
       <c r="H34" t="n">
-        <v>0.03673968590485577</v>
+        <v>0.03531862348755055</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1916759919887094</v>
+        <v>0.1879324971566933</v>
       </c>
     </row>
     <row r="35">
@@ -1508,25 +1508,25 @@
         <v>850</v>
       </c>
       <c r="C35" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D35" t="n">
-        <v>-7.463762283325195</v>
+        <v>-9.277047157287598</v>
       </c>
       <c r="E35" t="n">
-        <v>3.239950180053711</v>
+        <v>3.411510467529297</v>
       </c>
       <c r="F35" t="n">
-        <v>-2083.217859268188</v>
+        <v>-51821.69149208069</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.005284431099716881</v>
+        <v>-0.005168512388922798</v>
       </c>
       <c r="H35" t="n">
-        <v>0.03953363120786042</v>
+        <v>0.03841090067414073</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1988306596273835</v>
+        <v>0.1959869910839511</v>
       </c>
     </row>
     <row r="36">
@@ -1539,25 +1539,25 @@
         <v>825</v>
       </c>
       <c r="C36" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D36" t="n">
-        <v>-8.468664169311523</v>
+        <v>-11.21321201324463</v>
       </c>
       <c r="E36" t="n">
-        <v>3.381433486938477</v>
+        <v>3.772537231445312</v>
       </c>
       <c r="F36" t="n">
-        <v>-2307.510743141174</v>
+        <v>-55127.48630332947</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.005853387575253222</v>
+        <v>-0.00549822068182539</v>
       </c>
       <c r="H36" t="n">
-        <v>0.04149048203128625</v>
+        <v>0.04066114822639713</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2036921255996074</v>
+        <v>0.2016460964819233</v>
       </c>
     </row>
     <row r="37">
@@ -1570,25 +1570,25 @@
         <v>800</v>
       </c>
       <c r="C37" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D37" t="n">
-        <v>-9.407428741455078</v>
+        <v>-12.87025260925293</v>
       </c>
       <c r="E37" t="n">
-        <v>3.918010711669922</v>
+        <v>4.08746337890625</v>
       </c>
       <c r="F37" t="n">
-        <v>-2481.648054122925</v>
+        <v>-57937.18080806732</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.006295116037631273</v>
+        <v>-0.005778449683208786</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0429014763423127</v>
+        <v>0.04220286075598235</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2071267156653451</v>
+        <v>0.2054333486948562</v>
       </c>
     </row>
     <row r="38">
@@ -1601,25 +1601,25 @@
         <v>775</v>
       </c>
       <c r="C38" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D38" t="n">
-        <v>-10.19535732269287</v>
+        <v>-13.91684150695801</v>
       </c>
       <c r="E38" t="n">
-        <v>4.278763771057129</v>
+        <v>4.463313102722168</v>
       </c>
       <c r="F38" t="n">
-        <v>-2555.878024101257</v>
+        <v>-59398.15040111542</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.006483412792163874</v>
+        <v>-0.005924161627842294</v>
       </c>
       <c r="H38" t="n">
-        <v>0.04411598201490988</v>
+        <v>0.04342311519861047</v>
       </c>
       <c r="I38" t="n">
-        <v>0.21003804896949</v>
+        <v>0.2083821374269169</v>
       </c>
     </row>
     <row r="39">
@@ -1632,25 +1632,25 @@
         <v>750</v>
       </c>
       <c r="C39" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D39" t="n">
-        <v>-10.80027484893799</v>
+        <v>-14.50279140472412</v>
       </c>
       <c r="E39" t="n">
-        <v>4.462176322937012</v>
+        <v>4.735078811645508</v>
       </c>
       <c r="F39" t="n">
-        <v>-2579.875606536865</v>
+        <v>-60723.82324504852</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.006544286680305988</v>
+        <v>-0.006056379552812455</v>
       </c>
       <c r="H39" t="n">
-        <v>0.04537297865511</v>
+        <v>0.04459916147186013</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2130093393612355</v>
+        <v>0.2111851355371872</v>
       </c>
     </row>
     <row r="40">
@@ -1663,25 +1663,25 @@
         <v>725</v>
       </c>
       <c r="C40" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D40" t="n">
-        <v>-11.51120758056641</v>
+        <v>-14.14280891418457</v>
       </c>
       <c r="E40" t="n">
-        <v>4.491165161132812</v>
+        <v>6.10694408416748</v>
       </c>
       <c r="F40" t="n">
-        <v>-2484.213390350342</v>
+        <v>-62648.70530414581</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.006301623442740672</v>
+        <v>-0.006248360487498465</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0479434896719566</v>
+        <v>0.04701351997328641</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2189600184324905</v>
+        <v>0.2168260131379222</v>
       </c>
     </row>
     <row r="41">
@@ -1694,25 +1694,25 @@
         <v>700</v>
       </c>
       <c r="C41" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D41" t="n">
-        <v>-12.50522994995117</v>
+        <v>-14.72065544128418</v>
       </c>
       <c r="E41" t="n">
-        <v>4.285874366760254</v>
+        <v>5.051517486572266</v>
       </c>
       <c r="F41" t="n">
-        <v>-2360.066487312317</v>
+        <v>-65569.61175251007</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.005986704024961614</v>
+        <v>-0.006539681375153486</v>
       </c>
       <c r="H41" t="n">
-        <v>0.04958966554684054</v>
+        <v>0.04905054993134285</v>
       </c>
       <c r="I41" t="n">
-        <v>0.2226873717722685</v>
+        <v>0.2214735874350322</v>
       </c>
     </row>
     <row r="42">
@@ -1725,25 +1725,25 @@
         <v>650</v>
       </c>
       <c r="C42" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D42" t="n">
-        <v>-12.94777584075928</v>
+        <v>-15.0778169631958</v>
       </c>
       <c r="E42" t="n">
-        <v>3.974186897277832</v>
+        <v>4.582921981811523</v>
       </c>
       <c r="F42" t="n">
-        <v>-2327.519852638245</v>
+        <v>-67779.94095611572</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.00590414403360132</v>
+        <v>-0.006760131799358101</v>
       </c>
       <c r="H42" t="n">
-        <v>0.04792025248302208</v>
+        <v>0.04832009215640842</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2189069493712387</v>
+        <v>0.2198183162441393</v>
       </c>
     </row>
     <row r="43">
@@ -1756,25 +1756,25 @@
         <v>600</v>
       </c>
       <c r="C43" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D43" t="n">
-        <v>-12.55074977874756</v>
+        <v>-14.58753776550293</v>
       </c>
       <c r="E43" t="n">
-        <v>3.490689277648926</v>
+        <v>3.555633544921875</v>
       </c>
       <c r="F43" t="n">
-        <v>-2374.503860473633</v>
+        <v>-70852.97952270508</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.00602332684066591</v>
+        <v>-0.007066625806900938</v>
       </c>
       <c r="H43" t="n">
-        <v>0.04631839586504494</v>
+        <v>0.04741564897971055</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2152170900859059</v>
+        <v>0.2177513466771458</v>
       </c>
     </row>
     <row r="44">
@@ -1787,25 +1787,25 @@
         <v>550</v>
       </c>
       <c r="C44" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D44" t="n">
-        <v>-11.1440544128418</v>
+        <v>-14.42328262329102</v>
       </c>
       <c r="E44" t="n">
-        <v>2.829226493835449</v>
+        <v>2.957959175109863</v>
       </c>
       <c r="F44" t="n">
-        <v>-2282.618054389954</v>
+        <v>-71383.06396961212</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.005790243099985169</v>
+        <v>-0.007119494556494621</v>
       </c>
       <c r="H44" t="n">
-        <v>0.04544971863847746</v>
+        <v>0.04685177605657885</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2131893961680024</v>
+        <v>0.2164527109014319</v>
       </c>
     </row>
     <row r="45">
@@ -1818,25 +1818,25 @@
         <v>500</v>
       </c>
       <c r="C45" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D45" t="n">
-        <v>-8.983338356018066</v>
+        <v>-14.67950439453125</v>
       </c>
       <c r="E45" t="n">
-        <v>2.170618057250977</v>
+        <v>2.667131423950195</v>
       </c>
       <c r="F45" t="n">
-        <v>-2221.765473365784</v>
+        <v>-72032.88622665405</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.005635880333637185</v>
+        <v>-0.007184305532157776</v>
       </c>
       <c r="H45" t="n">
-        <v>0.04441681160024083</v>
+        <v>0.0460781127435935</v>
       </c>
       <c r="I45" t="n">
-        <v>0.210752963443556</v>
+        <v>0.2146581299266196</v>
       </c>
     </row>
     <row r="46">
@@ -1849,25 +1849,25 @@
         <v>450</v>
       </c>
       <c r="C46" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D46" t="n">
-        <v>-6.739585876464844</v>
+        <v>-14.51239013671875</v>
       </c>
       <c r="E46" t="n">
-        <v>1.613343238830566</v>
+        <v>2.369221687316895</v>
       </c>
       <c r="F46" t="n">
-        <v>-2305.395331382751</v>
+        <v>-73099.54794216156</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.005848021478934883</v>
+        <v>-0.007290690602437312</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0409398871574122</v>
+        <v>0.04292757610627798</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2023360747800851</v>
+        <v>0.207189710425682</v>
       </c>
     </row>
     <row r="47">
@@ -1880,25 +1880,25 @@
         <v>400</v>
       </c>
       <c r="C47" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D47" t="n">
-        <v>-6.403117179870605</v>
+        <v>-13.51175689697266</v>
       </c>
       <c r="E47" t="n">
-        <v>1.330451965332031</v>
+        <v>1.987301826477051</v>
       </c>
       <c r="F47" t="n">
-        <v>-2481.350485801697</v>
+        <v>-71394.13938236237</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.006294361205733115</v>
+        <v>-0.007120599179025518</v>
       </c>
       <c r="H47" t="n">
-        <v>0.03503442618162993</v>
+        <v>0.03697289233558221</v>
       </c>
       <c r="I47" t="n">
-        <v>0.187174854565537</v>
+        <v>0.1922833646875938</v>
       </c>
     </row>
     <row r="48">
@@ -1911,25 +1911,25 @@
         <v>350</v>
       </c>
       <c r="C48" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D48" t="n">
-        <v>-5.744803428649902</v>
+        <v>-11.9915885925293</v>
       </c>
       <c r="E48" t="n">
-        <v>1.145950317382812</v>
+        <v>1.664351463317871</v>
       </c>
       <c r="F48" t="n">
-        <v>-2328.519551277161</v>
+        <v>-62053.81642627716</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.005906679936677575</v>
+        <v>-0.006189028372957861</v>
       </c>
       <c r="H48" t="n">
-        <v>0.02758341798419966</v>
+        <v>0.02904300422453121</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1660825637573062</v>
+        <v>0.1704200816351501</v>
       </c>
     </row>
     <row r="49">
@@ -1942,25 +1942,25 @@
         <v>300</v>
       </c>
       <c r="C49" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D49" t="n">
-        <v>-4.513283729553223</v>
+        <v>-9.580441474914551</v>
       </c>
       <c r="E49" t="n">
-        <v>1.148579597473145</v>
+        <v>1.486281394958496</v>
       </c>
       <c r="F49" t="n">
-        <v>-1799.263743400574</v>
+        <v>-43618.08973026276</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.004564133914231648</v>
+        <v>-0.004350314137979509</v>
       </c>
       <c r="H49" t="n">
-        <v>0.01969427744665438</v>
+        <v>0.02057371278655632</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1403363012433147</v>
+        <v>0.1434353958636303</v>
       </c>
     </row>
     <row r="50">
@@ -1973,25 +1973,25 @@
         <v>250</v>
       </c>
       <c r="C50" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D50" t="n">
-        <v>-3.683189392089844</v>
+        <v>-8.87787914276123</v>
       </c>
       <c r="E50" t="n">
-        <v>1.105198860168457</v>
+        <v>1.505794525146484</v>
       </c>
       <c r="F50" t="n">
-        <v>-1401.893513679504</v>
+        <v>-33490.62929344177</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.003556137755453845</v>
+        <v>-0.003340237021063417</v>
       </c>
       <c r="H50" t="n">
-        <v>0.01544110262688656</v>
+        <v>0.0160246975916697</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1242622333087836</v>
+        <v>0.1265886945649954</v>
       </c>
     </row>
     <row r="51">
@@ -2004,25 +2004,25 @@
         <v>200</v>
       </c>
       <c r="C51" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D51" t="n">
-        <v>-2.778288841247559</v>
+        <v>-7.655767440795898</v>
       </c>
       <c r="E51" t="n">
-        <v>1.088249206542969</v>
+        <v>1.579972267150879</v>
       </c>
       <c r="F51" t="n">
-        <v>-1046.641478538513</v>
+        <v>-24104.18044757843</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.002654981453253054</v>
+        <v>-0.002404065781742746</v>
       </c>
       <c r="H51" t="n">
-        <v>0.01060108032222975</v>
+        <v>0.01105741416900901</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1029615477847422</v>
+        <v>0.105154239900296</v>
       </c>
     </row>
     <row r="52">
@@ -2035,25 +2035,25 @@
         <v>150</v>
       </c>
       <c r="C52" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D52" t="n">
-        <v>-2.313662528991699</v>
+        <v>-5.896099090576172</v>
       </c>
       <c r="E52" t="n">
-        <v>0.8885717391967773</v>
+        <v>1.70118522644043</v>
       </c>
       <c r="F52" t="n">
-        <v>-801.9082479476929</v>
+        <v>-15835.83107471466</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.00203417461391335</v>
+        <v>-0.001579409832870084</v>
       </c>
       <c r="H52" t="n">
-        <v>0.005913568320901291</v>
+        <v>0.006414038617623939</v>
       </c>
       <c r="I52" t="n">
-        <v>0.07689972900408226</v>
+        <v>0.08008769329693508</v>
       </c>
     </row>
     <row r="53">
@@ -2066,25 +2066,25 @@
         <v>100</v>
       </c>
       <c r="C53" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D53" t="n">
-        <v>-1.407973289489746</v>
+        <v>-3.676130294799805</v>
       </c>
       <c r="E53" t="n">
-        <v>0.8197755813598633</v>
+        <v>1.266777038574219</v>
       </c>
       <c r="F53" t="n">
-        <v>-443.0694340467453</v>
+        <v>-8666.518324315548</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.00112391984649799</v>
+        <v>-0.0008643679130947845</v>
       </c>
       <c r="H53" t="n">
-        <v>0.002768463433421609</v>
+        <v>0.003069765605709968</v>
       </c>
       <c r="I53" t="n">
-        <v>0.05261618984135595</v>
+        <v>0.05540546548590642</v>
       </c>
     </row>
     <row r="54">
@@ -2097,25 +2097,25 @@
         <v>1000</v>
       </c>
       <c r="C54" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D54" t="n">
-        <v>16.67861557006836</v>
+        <v>5.437365531921387</v>
       </c>
       <c r="E54" t="n">
-        <v>103.4562149047852</v>
+        <v>108.203727722168</v>
       </c>
       <c r="F54" t="n">
-        <v>31500055.71677399</v>
+        <v>799480648.9655766</v>
       </c>
       <c r="G54" t="n">
-        <v>79.90516850264063</v>
+        <v>79.73737483104152</v>
       </c>
       <c r="H54" t="n">
-        <v>155.0884235411933</v>
+        <v>141.5479151988288</v>
       </c>
       <c r="I54" t="n">
-        <v>12.45345026654033</v>
+        <v>11.89739110892925</v>
       </c>
     </row>
     <row r="55">
@@ -2128,25 +2128,25 @@
         <v>975</v>
       </c>
       <c r="C55" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D55" t="n">
-        <v>15.51215267181396</v>
+        <v>4.126392364501953</v>
       </c>
       <c r="E55" t="n">
-        <v>104.0266723632812</v>
+        <v>108.0694427490234</v>
       </c>
       <c r="F55" t="n">
-        <v>33285206.51290226</v>
+        <v>845822823.3023</v>
       </c>
       <c r="G55" t="n">
-        <v>84.43350256178624</v>
+        <v>84.35937954166702</v>
       </c>
       <c r="H55" t="n">
-        <v>184.3417423124078</v>
+        <v>165.8345788801995</v>
       </c>
       <c r="I55" t="n">
-        <v>13.57725091144771</v>
+        <v>12.87767754217349</v>
       </c>
     </row>
     <row r="56">
@@ -2159,25 +2159,25 @@
         <v>950</v>
       </c>
       <c r="C56" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D56" t="n">
-        <v>9.675236701965332</v>
+        <v>0.02105144038796425</v>
       </c>
       <c r="E56" t="n">
-        <v>105.0226135253906</v>
+        <v>108.5846328735352</v>
       </c>
       <c r="F56" t="n">
-        <v>33340177.91864967</v>
+        <v>846053103.6325303</v>
       </c>
       <c r="G56" t="n">
-        <v>84.57294674177653</v>
+        <v>84.38234688807047</v>
       </c>
       <c r="H56" t="n">
-        <v>193.5928424174363</v>
+        <v>184.7366466254045</v>
       </c>
       <c r="I56" t="n">
-        <v>13.91376449482441</v>
+        <v>13.59178599836697</v>
       </c>
     </row>
     <row r="57">
@@ -2190,25 +2190,25 @@
         <v>925</v>
       </c>
       <c r="C57" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D57" t="n">
-        <v>4.15870475769043</v>
+        <v>0.4477879405021667</v>
       </c>
       <c r="E57" t="n">
-        <v>104.5807495117188</v>
+        <v>109.2074737548828</v>
       </c>
       <c r="F57" t="n">
-        <v>31953081.29117584</v>
+        <v>806131517.6582989</v>
       </c>
       <c r="G57" t="n">
-        <v>81.05434376709285</v>
+        <v>80.40070897251194</v>
       </c>
       <c r="H57" t="n">
-        <v>207.8243228763716</v>
+        <v>211.5394880794512</v>
       </c>
       <c r="I57" t="n">
-        <v>14.41611330686505</v>
+        <v>14.54439713702329</v>
       </c>
     </row>
     <row r="58">
@@ -2221,25 +2221,25 @@
         <v>900</v>
       </c>
       <c r="C58" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D58" t="n">
-        <v>3.761618614196777</v>
+        <v>-0.9287099838256836</v>
       </c>
       <c r="E58" t="n">
-        <v>106.1202774047852</v>
+        <v>110.0415496826172</v>
       </c>
       <c r="F58" t="n">
-        <v>30639210.83604574</v>
+        <v>767206354.0854805</v>
       </c>
       <c r="G58" t="n">
-        <v>77.72149124607638</v>
+        <v>76.5184507062467</v>
       </c>
       <c r="H58" t="n">
-        <v>244.3718916320555</v>
+        <v>262.6125286123836</v>
       </c>
       <c r="I58" t="n">
-        <v>15.63239878048329</v>
+        <v>16.20532408230035</v>
       </c>
     </row>
     <row r="59">
@@ -2252,25 +2252,25 @@
         <v>875</v>
       </c>
       <c r="C59" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D59" t="n">
-        <v>0.9878721237182617</v>
+        <v>-0.9581308364868164</v>
       </c>
       <c r="E59" t="n">
-        <v>105.8134918212891</v>
+        <v>110.1420669555664</v>
       </c>
       <c r="F59" t="n">
-        <v>29111179.53664565</v>
+        <v>726642248.4071285</v>
       </c>
       <c r="G59" t="n">
-        <v>73.84538386538834</v>
+        <v>72.47273014584832</v>
       </c>
       <c r="H59" t="n">
-        <v>317.4213899866554</v>
+        <v>336.8494977824636</v>
       </c>
       <c r="I59" t="n">
-        <v>17.81632369448466</v>
+        <v>18.35346010381867</v>
       </c>
     </row>
     <row r="60">
@@ -2283,25 +2283,25 @@
         <v>850</v>
       </c>
       <c r="C60" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.2125970125198364</v>
+        <v>-3.572824478149414</v>
       </c>
       <c r="E60" t="n">
-        <v>106.1613159179688</v>
+        <v>122.3688888549805</v>
       </c>
       <c r="F60" t="n">
-        <v>27457910.85495675</v>
+        <v>684961951.1587551</v>
       </c>
       <c r="G60" t="n">
-        <v>69.65159088361445</v>
+        <v>68.31568458250334</v>
       </c>
       <c r="H60" t="n">
-        <v>406.5155970036662</v>
+        <v>416.3709013661519</v>
       </c>
       <c r="I60" t="n">
-        <v>20.16223194499226</v>
+        <v>20.40516849639208</v>
       </c>
     </row>
     <row r="61">
@@ -2314,25 +2314,25 @@
         <v>825</v>
       </c>
       <c r="C61" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D61" t="n">
-        <v>-2.66108512878418</v>
+        <v>-4.339694976806641</v>
       </c>
       <c r="E61" t="n">
-        <v>104.9540557861328</v>
+        <v>115.7575988769531</v>
       </c>
       <c r="F61" t="n">
-        <v>25873726.44174194</v>
+        <v>646965462.1959532</v>
       </c>
       <c r="G61" t="n">
-        <v>65.63304172245292</v>
+        <v>64.52604904021635</v>
       </c>
       <c r="H61" t="n">
-        <v>473.827734767299</v>
+        <v>476.3767486871807</v>
       </c>
       <c r="I61" t="n">
-        <v>21.76758449546708</v>
+        <v>21.82605664537643</v>
       </c>
     </row>
     <row r="62">
@@ -2345,25 +2345,25 @@
         <v>800</v>
       </c>
       <c r="C62" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.4023284912109375</v>
+        <v>-5.542159080505371</v>
       </c>
       <c r="E62" t="n">
-        <v>105.4152450561523</v>
+        <v>115.3020858764648</v>
       </c>
       <c r="F62" t="n">
-        <v>24381897.52866209</v>
+        <v>614790993.5980947</v>
       </c>
       <c r="G62" t="n">
-        <v>61.84876775962054</v>
+        <v>61.31708123605928</v>
       </c>
       <c r="H62" t="n">
-        <v>525.3418546836863</v>
+        <v>513.1041442007436</v>
       </c>
       <c r="I62" t="n">
-        <v>22.92033714157988</v>
+        <v>22.65180222853677</v>
       </c>
     </row>
     <row r="63">
@@ -2376,25 +2376,25 @@
         <v>775</v>
       </c>
       <c r="C63" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D63" t="n">
-        <v>-2.76849365234375</v>
+        <v>-3.032523155212402</v>
       </c>
       <c r="E63" t="n">
-        <v>106.7638626098633</v>
+        <v>112.8669815063477</v>
       </c>
       <c r="F63" t="n">
-        <v>23052712.51906395</v>
+        <v>586976379.7173281</v>
       </c>
       <c r="G63" t="n">
-        <v>58.47706730556178</v>
+        <v>58.54294993511908</v>
       </c>
       <c r="H63" t="n">
-        <v>564.7173654687899</v>
+        <v>536.4232597026821</v>
       </c>
       <c r="I63" t="n">
-        <v>23.76378264226447</v>
+        <v>23.16081301903459</v>
       </c>
     </row>
     <row r="64">
@@ -2407,25 +2407,25 @@
         <v>750</v>
       </c>
       <c r="C64" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D64" t="n">
-        <v>-3.500700950622559</v>
+        <v>-5.241782188415527</v>
       </c>
       <c r="E64" t="n">
-        <v>106.7362213134766</v>
+        <v>114.5705184936523</v>
       </c>
       <c r="F64" t="n">
-        <v>21822524.16844749</v>
+        <v>561572819.367018</v>
       </c>
       <c r="G64" t="n">
-        <v>55.35648846183453</v>
+        <v>56.00928859345133</v>
       </c>
       <c r="H64" t="n">
-        <v>583.7062686612991</v>
+        <v>545.0898531239231</v>
       </c>
       <c r="I64" t="n">
-        <v>24.16001383818517</v>
+        <v>23.34715942302025</v>
       </c>
     </row>
     <row r="65">
@@ -2438,25 +2438,25 @@
         <v>725</v>
       </c>
       <c r="C65" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D65" t="n">
-        <v>-3.693939208984375</v>
+        <v>-6.19677734375</v>
       </c>
       <c r="E65" t="n">
-        <v>106.7437438964844</v>
+        <v>114.904670715332</v>
       </c>
       <c r="F65" t="n">
-        <v>19753568.14733326</v>
+        <v>519284117.4072941</v>
       </c>
       <c r="G65" t="n">
-        <v>50.10823490386859</v>
+        <v>51.7915628940942</v>
       </c>
       <c r="H65" t="n">
-        <v>593.8057673926629</v>
+        <v>545.8643188104913</v>
       </c>
       <c r="I65" t="n">
-        <v>24.36813015790631</v>
+        <v>23.36373940127075</v>
       </c>
     </row>
     <row r="66">
@@ -2469,25 +2469,25 @@
         <v>700</v>
       </c>
       <c r="C66" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D66" t="n">
-        <v>-3.343767166137695</v>
+        <v>-9.847058296203613</v>
       </c>
       <c r="E66" t="n">
-        <v>108.0926361083984</v>
+        <v>119.0913238525391</v>
       </c>
       <c r="F66" t="n">
-        <v>18567932.3965205</v>
+        <v>494826096.3200818</v>
       </c>
       <c r="G66" t="n">
-        <v>47.10067119340187</v>
+        <v>49.35220629730875</v>
       </c>
       <c r="H66" t="n">
-        <v>651.2174966973394</v>
+        <v>608.5433735509779</v>
       </c>
       <c r="I66" t="n">
-        <v>25.51896347223647</v>
+        <v>24.66867190488734</v>
       </c>
     </row>
     <row r="67">
@@ -2500,25 +2500,25 @@
         <v>650</v>
       </c>
       <c r="C67" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D67" t="n">
-        <v>-4.521732330322266</v>
+        <v>-5.791181564331055</v>
       </c>
       <c r="E67" t="n">
-        <v>109.105712890625</v>
+        <v>114.8564529418945</v>
       </c>
       <c r="F67" t="n">
-        <v>17873955.98203951</v>
+        <v>476936631.3311185</v>
       </c>
       <c r="G67" t="n">
-        <v>45.34028375680336</v>
+        <v>47.56797427468587</v>
       </c>
       <c r="H67" t="n">
-        <v>777.8178602556129</v>
+        <v>750.9843119148078</v>
       </c>
       <c r="I67" t="n">
-        <v>27.88938615774132</v>
+        <v>27.40409297741503</v>
       </c>
     </row>
     <row r="68">
@@ -2531,25 +2531,25 @@
         <v>600</v>
       </c>
       <c r="C68" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D68" t="n">
-        <v>-8.64772891998291</v>
+        <v>-7.655652046203613</v>
       </c>
       <c r="E68" t="n">
-        <v>112.9522018432617</v>
+        <v>114.9189147949219</v>
       </c>
       <c r="F68" t="n">
-        <v>16477110.90925062</v>
+        <v>434971300.7473565</v>
       </c>
       <c r="G68" t="n">
-        <v>41.7969522174295</v>
+        <v>43.38250049368125</v>
       </c>
       <c r="H68" t="n">
-        <v>793.0999758372078</v>
+        <v>809.973580038239</v>
       </c>
       <c r="I68" t="n">
-        <v>28.16203074774985</v>
+        <v>28.46003478631463</v>
       </c>
     </row>
     <row r="69">
@@ -2562,25 +2562,25 @@
         <v>550</v>
       </c>
       <c r="C69" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D69" t="n">
-        <v>-4.976059913635254</v>
+        <v>-4.89570140838623</v>
       </c>
       <c r="E69" t="n">
-        <v>113.1898880004883</v>
+        <v>118.9282073974609</v>
       </c>
       <c r="F69" t="n">
-        <v>14842727.63668096</v>
+        <v>384949060.2008683</v>
       </c>
       <c r="G69" t="n">
-        <v>37.65106523974292</v>
+        <v>38.39345898341495</v>
       </c>
       <c r="H69" t="n">
-        <v>726.3915227232847</v>
+        <v>749.8189669638443</v>
       </c>
       <c r="I69" t="n">
-        <v>26.9516515769124</v>
+        <v>27.38282247986581</v>
       </c>
     </row>
     <row r="70">
@@ -2593,25 +2593,25 @@
         <v>500</v>
       </c>
       <c r="C70" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.7033414840698242</v>
+        <v>-8.479220390319824</v>
       </c>
       <c r="E70" t="n">
-        <v>119.0120544433594</v>
+        <v>131.3380889892578</v>
       </c>
       <c r="F70" t="n">
-        <v>14245148.60844904</v>
+        <v>361184774.0162191</v>
       </c>
       <c r="G70" t="n">
-        <v>36.13520592273578</v>
+        <v>36.02329305438413</v>
       </c>
       <c r="H70" t="n">
-        <v>711.7812434904263</v>
+        <v>725.6675188043481</v>
       </c>
       <c r="I70" t="n">
-        <v>26.67922868994578</v>
+        <v>26.93821669681102</v>
       </c>
     </row>
     <row r="71">
@@ -2624,25 +2624,25 @@
         <v>450</v>
       </c>
       <c r="C71" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D71" t="n">
-        <v>-2.877341270446777</v>
+        <v>-10.94512271881104</v>
       </c>
       <c r="E71" t="n">
-        <v>113.9680023193359</v>
+        <v>139.7909698486328</v>
       </c>
       <c r="F71" t="n">
-        <v>14914200.58256978</v>
+        <v>373099676.9571382</v>
       </c>
       <c r="G71" t="n">
-        <v>37.83236834079057</v>
+        <v>37.21164337043614</v>
       </c>
       <c r="H71" t="n">
-        <v>750.8832507628746</v>
+        <v>764.8233707592289</v>
       </c>
       <c r="I71" t="n">
-        <v>27.40224900921227</v>
+        <v>27.65544016571114</v>
       </c>
     </row>
     <row r="72">
@@ -2655,25 +2655,25 @@
         <v>400</v>
       </c>
       <c r="C72" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D72" t="n">
-        <v>-3.265727996826172</v>
+        <v>-8.509300231933594</v>
       </c>
       <c r="E72" t="n">
-        <v>128.1721343994141</v>
+        <v>139.2088928222656</v>
       </c>
       <c r="F72" t="n">
-        <v>16394331.44436622</v>
+        <v>409373090.4784034</v>
       </c>
       <c r="G72" t="n">
-        <v>41.58696823677818</v>
+        <v>40.82942545695533</v>
       </c>
       <c r="H72" t="n">
-        <v>808.4169229584213</v>
+        <v>819.3016539773708</v>
       </c>
       <c r="I72" t="n">
-        <v>28.43267351056565</v>
+        <v>28.62344587881359</v>
       </c>
     </row>
     <row r="73">
@@ -2686,25 +2686,25 @@
         <v>350</v>
       </c>
       <c r="C73" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D73" t="n">
-        <v>0.6106426119804382</v>
+        <v>-5.738934516906738</v>
       </c>
       <c r="E73" t="n">
-        <v>125.4318618774414</v>
+        <v>129.5653686523438</v>
       </c>
       <c r="F73" t="n">
-        <v>18427186.18271345</v>
+        <v>466342569.2067576</v>
       </c>
       <c r="G73" t="n">
-        <v>46.74364484298899</v>
+        <v>46.51135995426869</v>
       </c>
       <c r="H73" t="n">
-        <v>871.7857146918041</v>
+        <v>867.4816007377142</v>
       </c>
       <c r="I73" t="n">
-        <v>29.52601758943803</v>
+        <v>29.45304060258829</v>
       </c>
     </row>
     <row r="74">
@@ -2717,25 +2717,25 @@
         <v>300</v>
       </c>
       <c r="C74" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D74" t="n">
-        <v>1.554368019104004</v>
+        <v>-5.420136451721191</v>
       </c>
       <c r="E74" t="n">
-        <v>129.2307586669922</v>
+        <v>133.7701568603516</v>
       </c>
       <c r="F74" t="n">
-        <v>21950032.66560268</v>
+        <v>552663292.5238219</v>
       </c>
       <c r="G74" t="n">
-        <v>55.67993512625674</v>
+        <v>55.12068386939426</v>
       </c>
       <c r="H74" t="n">
-        <v>898.6376122216324</v>
+        <v>903.9253678769517</v>
       </c>
       <c r="I74" t="n">
-        <v>29.97728493745944</v>
+        <v>30.06535161738428</v>
       </c>
     </row>
     <row r="75">
@@ -2748,25 +2748,25 @@
         <v>250</v>
       </c>
       <c r="C75" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D75" t="n">
-        <v>1.012252569198608</v>
+        <v>-4.314042091369629</v>
       </c>
       <c r="E75" t="n">
-        <v>135.9038696289062</v>
+        <v>168.4070892333984</v>
       </c>
       <c r="F75" t="n">
-        <v>23466272.87229753</v>
+        <v>593370526.130264</v>
       </c>
       <c r="G75" t="n">
-        <v>59.5261324249464</v>
+        <v>59.18067950357418</v>
       </c>
       <c r="H75" t="n">
-        <v>885.0241054579577</v>
+        <v>886.4656914189896</v>
       </c>
       <c r="I75" t="n">
-        <v>29.74935470658074</v>
+        <v>29.77357370923064</v>
       </c>
     </row>
     <row r="76">
@@ -2779,25 +2779,25 @@
         <v>200</v>
       </c>
       <c r="C76" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D76" t="n">
-        <v>1.048867106437683</v>
+        <v>-4.440022468566895</v>
       </c>
       <c r="E76" t="n">
-        <v>136.1002655029297</v>
+        <v>148.8643646240234</v>
       </c>
       <c r="F76" t="n">
-        <v>24228688.77055109</v>
+        <v>618388394.1481723</v>
       </c>
       <c r="G76" t="n">
-        <v>61.46012807774146</v>
+        <v>61.67587325491589</v>
       </c>
       <c r="H76" t="n">
-        <v>843.5504041974707</v>
+        <v>831.5248213876281</v>
       </c>
       <c r="I76" t="n">
-        <v>29.04393919903894</v>
+        <v>28.83617210011808</v>
       </c>
     </row>
     <row r="77">
@@ -2810,25 +2810,25 @@
         <v>150</v>
       </c>
       <c r="C77" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D77" t="n">
-        <v>0.9752813577651978</v>
+        <v>-1.075922966003418</v>
       </c>
       <c r="E77" t="n">
-        <v>137.7368621826172</v>
+        <v>147.6380920410156</v>
       </c>
       <c r="F77" t="n">
-        <v>24797229.88528633</v>
+        <v>632354903.6394479</v>
       </c>
       <c r="G77" t="n">
-        <v>62.90232786246778</v>
+        <v>63.06884355860989</v>
       </c>
       <c r="H77" t="n">
-        <v>817.8652776333287</v>
+        <v>795.9576664455182</v>
       </c>
       <c r="I77" t="n">
-        <v>28.59834396662381</v>
+        <v>28.21272171282874</v>
       </c>
     </row>
     <row r="78">
@@ -2841,25 +2841,25 @@
         <v>100</v>
       </c>
       <c r="C78" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D78" t="n">
-        <v>0.2638511657714844</v>
+        <v>-19.89750671386719</v>
       </c>
       <c r="E78" t="n">
-        <v>146.3963012695312</v>
+        <v>168.4141845703125</v>
       </c>
       <c r="F78" t="n">
-        <v>25087587.7014569</v>
+        <v>632863170.6179223</v>
       </c>
       <c r="G78" t="n">
-        <v>63.63886910657787</v>
+        <v>63.11953631099761</v>
       </c>
       <c r="H78" t="n">
-        <v>878.3102780902391</v>
+        <v>854.9545310584356</v>
       </c>
       <c r="I78" t="n">
-        <v>29.63630000675251</v>
+        <v>29.23960552159409</v>
       </c>
     </row>
     <row r="79">
@@ -2872,25 +2872,25 @@
         <v>1000</v>
       </c>
       <c r="C79" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D79" t="n">
-        <v>268.8011474609375</v>
+        <v>255.1848907470703</v>
       </c>
       <c r="E79" t="n">
-        <v>309.9418029785156</v>
+        <v>318.2398071289062</v>
       </c>
       <c r="F79" t="n">
-        <v>117082966.7793274</v>
+        <v>2982892580.056778</v>
       </c>
       <c r="G79" t="n">
-        <v>297.0005600437505</v>
+        <v>297.5031653917632</v>
       </c>
       <c r="H79" t="n">
-        <v>12.54953185796293</v>
+        <v>10.29535471809472</v>
       </c>
       <c r="I79" t="n">
-        <v>3.542531842900348</v>
+        <v>3.208637517404345</v>
       </c>
     </row>
     <row r="80">
@@ -2903,25 +2903,25 @@
         <v>975</v>
       </c>
       <c r="C80" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D80" t="n">
-        <v>265.8878479003906</v>
+        <v>253.9454193115234</v>
       </c>
       <c r="E80" t="n">
-        <v>308.99169921875</v>
+        <v>316.7802124023438</v>
       </c>
       <c r="F80" t="n">
-        <v>116353790.9586182</v>
+        <v>2964174687.582321</v>
       </c>
       <c r="G80" t="n">
-        <v>295.1508834163286</v>
+        <v>295.636308939122</v>
       </c>
       <c r="H80" t="n">
-        <v>12.04411255407127</v>
+        <v>10.29164871898972</v>
       </c>
       <c r="I80" t="n">
-        <v>3.470462873172867</v>
+        <v>3.208059961875669</v>
       </c>
     </row>
     <row r="81">
@@ -2934,25 +2934,25 @@
         <v>950</v>
       </c>
       <c r="C81" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D81" t="n">
-        <v>266.6195373535156</v>
+        <v>252.6427001953125</v>
       </c>
       <c r="E81" t="n">
-        <v>306.7196655273438</v>
+        <v>315.1768798828125</v>
       </c>
       <c r="F81" t="n">
-        <v>115775753.4853516</v>
+        <v>2949466694.461182</v>
       </c>
       <c r="G81" t="n">
-        <v>293.6845945272708</v>
+        <v>294.1693856783398</v>
       </c>
       <c r="H81" t="n">
-        <v>12.06151275020964</v>
+        <v>10.57754093144271</v>
       </c>
       <c r="I81" t="n">
-        <v>3.472968866864435</v>
+        <v>3.252313166262239</v>
       </c>
     </row>
     <row r="82">
@@ -2965,25 +2965,25 @@
         <v>925</v>
       </c>
       <c r="C82" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D82" t="n">
-        <v>264.9251403808594</v>
+        <v>251.3966522216797</v>
       </c>
       <c r="E82" t="n">
-        <v>304.3163757324219</v>
+        <v>312.859130859375</v>
       </c>
       <c r="F82" t="n">
-        <v>115296104.5733032</v>
+        <v>2937569284.775055</v>
       </c>
       <c r="G82" t="n">
-        <v>292.4678847066933</v>
+        <v>292.982780077706</v>
       </c>
       <c r="H82" t="n">
-        <v>12.15314197181503</v>
+        <v>10.77418475424225</v>
       </c>
       <c r="I82" t="n">
-        <v>3.486135678916561</v>
+        <v>3.28240533058339</v>
       </c>
     </row>
     <row r="83">
@@ -2996,25 +2996,25 @@
         <v>900</v>
       </c>
       <c r="C83" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D83" t="n">
-        <v>263.0934143066406</v>
+        <v>250.0228271484375</v>
       </c>
       <c r="E83" t="n">
-        <v>302.2023315429688</v>
+        <v>310.3804931640625</v>
       </c>
       <c r="F83" t="n">
-        <v>114833026.574707</v>
+        <v>2926298693.782501</v>
       </c>
       <c r="G83" t="n">
-        <v>291.293209784198</v>
+        <v>291.8586911586017</v>
       </c>
       <c r="H83" t="n">
-        <v>11.68299875321335</v>
+        <v>10.51822467950567</v>
       </c>
       <c r="I83" t="n">
-        <v>3.418040191866291</v>
+        <v>3.243181259119766</v>
       </c>
     </row>
     <row r="84">
@@ -3027,25 +3027,25 @@
         <v>875</v>
       </c>
       <c r="C84" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D84" t="n">
-        <v>261.5077514648438</v>
+        <v>248.6092681884766</v>
       </c>
       <c r="E84" t="n">
-        <v>300.3567504882812</v>
+        <v>307.8746643066406</v>
       </c>
       <c r="F84" t="n">
-        <v>114396853.6416321</v>
+        <v>2915426337.656647</v>
       </c>
       <c r="G84" t="n">
-        <v>290.1867840677801</v>
+        <v>290.774320777872</v>
       </c>
       <c r="H84" t="n">
-        <v>10.83612553308917</v>
+        <v>10.06184956860948</v>
       </c>
       <c r="I84" t="n">
-        <v>3.291827081286192</v>
+        <v>3.172041861106104</v>
       </c>
     </row>
     <row r="85">
@@ -3058,25 +3058,25 @@
         <v>850</v>
       </c>
       <c r="C85" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D85" t="n">
-        <v>259.8253173828125</v>
+        <v>247.3075866699219</v>
       </c>
       <c r="E85" t="n">
-        <v>298.7114868164062</v>
+        <v>305.3089599609375</v>
       </c>
       <c r="F85" t="n">
-        <v>113969577.4518127</v>
+        <v>2904454260.914337</v>
       </c>
       <c r="G85" t="n">
-        <v>289.1029264310931</v>
+        <v>289.6800046152406</v>
       </c>
       <c r="H85" t="n">
-        <v>10.07633863185927</v>
+        <v>9.398639052206656</v>
       </c>
       <c r="I85" t="n">
-        <v>3.174324909623977</v>
+        <v>3.065719989204275</v>
       </c>
     </row>
     <row r="86">
@@ -3089,25 +3089,25 @@
         <v>825</v>
       </c>
       <c r="C86" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D86" t="n">
-        <v>258.5432739257812</v>
+        <v>247.0019073486328</v>
       </c>
       <c r="E86" t="n">
-        <v>296.41064453125</v>
+        <v>302.8648681640625</v>
       </c>
       <c r="F86" t="n">
-        <v>113517355.425415</v>
+        <v>2892697740.646317</v>
       </c>
       <c r="G86" t="n">
-        <v>287.955789500771</v>
+        <v>288.5074508273095</v>
       </c>
       <c r="H86" t="n">
-        <v>9.270515770437424</v>
+        <v>8.455037033638115</v>
       </c>
       <c r="I86" t="n">
-        <v>3.044752168968342</v>
+        <v>2.907754637798402</v>
       </c>
     </row>
     <row r="87">
@@ -3120,25 +3120,25 @@
         <v>800</v>
       </c>
       <c r="C87" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D87" t="n">
-        <v>257.9334716796875</v>
+        <v>246.7183990478516</v>
       </c>
       <c r="E87" t="n">
-        <v>294.8358764648438</v>
+        <v>301.2190551757812</v>
       </c>
       <c r="F87" t="n">
-        <v>113034513.1390686</v>
+        <v>2879884617.562988</v>
       </c>
       <c r="G87" t="n">
-        <v>286.7309791513037</v>
+        <v>287.2295152082643</v>
       </c>
       <c r="H87" t="n">
-        <v>8.395383354704327</v>
+        <v>7.488181342029197</v>
       </c>
       <c r="I87" t="n">
-        <v>2.897478792796304</v>
+        <v>2.736454154929184</v>
       </c>
     </row>
     <row r="88">
@@ -3151,25 +3151,25 @@
         <v>775</v>
       </c>
       <c r="C88" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D88" t="n">
-        <v>258.1588134765625</v>
+        <v>246.04736328125</v>
       </c>
       <c r="E88" t="n">
-        <v>292.5713806152344</v>
+        <v>299.0550537109375</v>
       </c>
       <c r="F88" t="n">
-        <v>112514839.0842285</v>
+        <v>2866125498.536865</v>
       </c>
       <c r="G88" t="n">
-        <v>285.4127388506575</v>
+        <v>285.8572292967155</v>
       </c>
       <c r="H88" t="n">
-        <v>7.610923796632614</v>
+        <v>6.661261281562805</v>
       </c>
       <c r="I88" t="n">
-        <v>2.758790277754475</v>
+        <v>2.580941936883278</v>
       </c>
     </row>
     <row r="89">
@@ -3182,25 +3182,25 @@
         <v>750</v>
       </c>
       <c r="C89" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D89" t="n">
-        <v>258.7150573730469</v>
+        <v>246.3654022216797</v>
       </c>
       <c r="E89" t="n">
-        <v>292.0692749023438</v>
+        <v>297.671630859375</v>
       </c>
       <c r="F89" t="n">
-        <v>111962819.5762634</v>
+        <v>2851552502.29895</v>
       </c>
       <c r="G89" t="n">
-        <v>284.0124488893542</v>
+        <v>284.4037701480342</v>
       </c>
       <c r="H89" t="n">
-        <v>6.879941581602409</v>
+        <v>5.974969541316645</v>
       </c>
       <c r="I89" t="n">
-        <v>2.622964273794519</v>
+        <v>2.444375081961982</v>
       </c>
     </row>
     <row r="90">
@@ -3213,25 +3213,25 @@
         <v>725</v>
       </c>
       <c r="C90" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D90" t="n">
-        <v>260.3219604492188</v>
+        <v>242.462158203125</v>
       </c>
       <c r="E90" t="n">
-        <v>287.0588989257812</v>
+        <v>294.1692504882812</v>
       </c>
       <c r="F90" t="n">
-        <v>110747330.3556824</v>
+        <v>2819645475.68222</v>
       </c>
       <c r="G90" t="n">
-        <v>280.9291568514941</v>
+        <v>281.2214760620246</v>
       </c>
       <c r="H90" t="n">
-        <v>5.859919288894884</v>
+        <v>4.945534566297511</v>
       </c>
       <c r="I90" t="n">
-        <v>2.420727016599534</v>
+        <v>2.223855788107114</v>
       </c>
     </row>
     <row r="91">
@@ -3244,25 +3244,25 @@
         <v>700</v>
       </c>
       <c r="C91" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D91" t="n">
-        <v>257.7081909179688</v>
+        <v>239.9819946289062</v>
       </c>
       <c r="E91" t="n">
-        <v>283.553466796875</v>
+        <v>289.8150634765625</v>
       </c>
       <c r="F91" t="n">
-        <v>109363434.767395</v>
+        <v>2783950845.061508</v>
       </c>
       <c r="G91" t="n">
-        <v>277.4186738489747</v>
+        <v>277.661419736782</v>
       </c>
       <c r="H91" t="n">
-        <v>5.526863008109731</v>
+        <v>4.40748699557196</v>
       </c>
       <c r="I91" t="n">
-        <v>2.350928116321239</v>
+        <v>2.099401580349019</v>
       </c>
     </row>
     <row r="92">
@@ -3275,25 +3275,25 @@
         <v>650</v>
       </c>
       <c r="C92" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D92" t="n">
-        <v>254.9344024658203</v>
+        <v>238.6626434326172</v>
       </c>
       <c r="E92" t="n">
-        <v>279.3798522949219</v>
+        <v>286.2237548828125</v>
       </c>
       <c r="F92" t="n">
-        <v>107919416.9032288</v>
+        <v>2747194936.990646</v>
       </c>
       <c r="G92" t="n">
-        <v>273.7556806214548</v>
+        <v>273.9955153488576</v>
       </c>
       <c r="H92" t="n">
-        <v>5.544435037751647</v>
+        <v>4.273986207056101</v>
       </c>
       <c r="I92" t="n">
-        <v>2.354662404199729</v>
+        <v>2.067362137376057</v>
       </c>
     </row>
     <row r="93">
@@ -3306,25 +3306,25 @@
         <v>600</v>
       </c>
       <c r="C93" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D93" t="n">
-        <v>251.0818176269531</v>
+        <v>236.7375946044922</v>
       </c>
       <c r="E93" t="n">
-        <v>276.08251953125</v>
+        <v>281.2777099609375</v>
       </c>
       <c r="F93" t="n">
-        <v>106440406.7268982</v>
+        <v>2709923650.035248</v>
       </c>
       <c r="G93" t="n">
-        <v>270.0039235318991</v>
+        <v>270.2782088921709</v>
       </c>
       <c r="H93" t="n">
-        <v>6.467919152473489</v>
+        <v>4.871282870012011</v>
       </c>
       <c r="I93" t="n">
-        <v>2.543210402714154</v>
+        <v>2.207098291878278</v>
       </c>
     </row>
     <row r="94">
@@ -3337,25 +3337,25 @@
         <v>550</v>
       </c>
       <c r="C94" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D94" t="n">
-        <v>246.6770782470703</v>
+        <v>233.0751647949219</v>
       </c>
       <c r="E94" t="n">
-        <v>272.2085571289062</v>
+        <v>278.5971069335938</v>
       </c>
       <c r="F94" t="n">
-        <v>104754162.8332214</v>
+        <v>2667786780.278778</v>
       </c>
       <c r="G94" t="n">
-        <v>265.7264834006094</v>
+        <v>266.0756264002401</v>
       </c>
       <c r="H94" t="n">
-        <v>7.814144859234939</v>
+        <v>5.68423344348288</v>
       </c>
       <c r="I94" t="n">
-        <v>2.795379197753847</v>
+        <v>2.384163048846047</v>
       </c>
     </row>
     <row r="95">
@@ -3368,25 +3368,25 @@
         <v>500</v>
       </c>
       <c r="C95" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D95" t="n">
-        <v>240.6556701660156</v>
+        <v>229.6830139160156</v>
       </c>
       <c r="E95" t="n">
-        <v>266.2774047851562</v>
+        <v>274.2037963867188</v>
       </c>
       <c r="F95" t="n">
-        <v>102785116.9932709</v>
+        <v>2618367403.070099</v>
       </c>
       <c r="G95" t="n">
-        <v>260.7316687550314</v>
+        <v>261.1467123489696</v>
       </c>
       <c r="H95" t="n">
-        <v>9.179618230614047</v>
+        <v>6.68986304673547</v>
       </c>
       <c r="I95" t="n">
-        <v>3.029788479517018</v>
+        <v>2.586476956544455</v>
       </c>
     </row>
     <row r="96">
@@ -3399,25 +3399,25 @@
         <v>450</v>
       </c>
       <c r="C96" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D96" t="n">
-        <v>234.2025451660156</v>
+        <v>225.9030609130859</v>
       </c>
       <c r="E96" t="n">
-        <v>260.3731384277344</v>
+        <v>267.074951171875</v>
       </c>
       <c r="F96" t="n">
-        <v>100441992.2346191</v>
+        <v>2559050547.163849</v>
       </c>
       <c r="G96" t="n">
-        <v>254.7879402630501</v>
+        <v>255.2306587467777</v>
       </c>
       <c r="H96" t="n">
-        <v>9.938911416668018</v>
+        <v>7.493912165690227</v>
       </c>
       <c r="I96" t="n">
-        <v>3.152603910526665</v>
+        <v>2.737501080491152</v>
       </c>
     </row>
     <row r="97">
@@ -3430,25 +3430,25 @@
         <v>400</v>
       </c>
       <c r="C97" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D97" t="n">
-        <v>227.8123779296875</v>
+        <v>221.6041412353516</v>
       </c>
       <c r="E97" t="n">
-        <v>253.8418731689453</v>
+        <v>261.0946044921875</v>
       </c>
       <c r="F97" t="n">
-        <v>97670732.19630432</v>
+        <v>2488197158.048065</v>
       </c>
       <c r="G97" t="n">
-        <v>247.7581749090714</v>
+        <v>248.1639920885112</v>
       </c>
       <c r="H97" t="n">
-        <v>9.955538746258011</v>
+        <v>7.876223627061692</v>
       </c>
       <c r="I97" t="n">
-        <v>3.155239887276086</v>
+        <v>2.80646105033754</v>
       </c>
     </row>
     <row r="98">
@@ -3461,25 +3461,25 @@
         <v>350</v>
       </c>
       <c r="C98" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D98" t="n">
-        <v>221.4880218505859</v>
+        <v>216.825927734375</v>
       </c>
       <c r="E98" t="n">
-        <v>245.4207305908203</v>
+        <v>253.9608917236328</v>
       </c>
       <c r="F98" t="n">
-        <v>94388506.37608337</v>
+        <v>2403975695.42659</v>
       </c>
       <c r="G98" t="n">
-        <v>239.432259247633</v>
+        <v>239.764041017079</v>
       </c>
       <c r="H98" t="n">
-        <v>8.825440604972064</v>
+        <v>7.575955226003828</v>
       </c>
       <c r="I98" t="n">
-        <v>2.970764313265538</v>
+        <v>2.752445317531999</v>
       </c>
     </row>
     <row r="99">
@@ -3492,25 +3492,25 @@
         <v>300</v>
       </c>
       <c r="C99" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D99" t="n">
-        <v>213.8577117919922</v>
+        <v>210.1175231933594</v>
       </c>
       <c r="E99" t="n">
-        <v>237.2065582275391</v>
+        <v>243.81591796875</v>
       </c>
       <c r="F99" t="n">
-        <v>90502162.43254089</v>
+        <v>2304446570.033173</v>
       </c>
       <c r="G99" t="n">
-        <v>229.5738967590037</v>
+        <v>229.8373577529269</v>
       </c>
       <c r="H99" t="n">
-        <v>6.234857949216781</v>
+        <v>6.10071474178661</v>
       </c>
       <c r="I99" t="n">
-        <v>2.496969753364422</v>
+        <v>2.469962498052675</v>
       </c>
     </row>
     <row r="100">
@@ -3523,25 +3523,25 @@
         <v>250</v>
       </c>
       <c r="C100" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D100" t="n">
-        <v>210.1694793701172</v>
+        <v>205.1709289550781</v>
       </c>
       <c r="E100" t="n">
-        <v>235.3089904785156</v>
+        <v>238.6356811523438</v>
       </c>
       <c r="F100" t="n">
-        <v>88321861.2469635</v>
+        <v>2248466244.028961</v>
       </c>
       <c r="G100" t="n">
-        <v>224.0431975378177</v>
+        <v>224.2540778529853</v>
       </c>
       <c r="H100" t="n">
-        <v>4.740812020642847</v>
+        <v>4.79171467876384</v>
       </c>
       <c r="I100" t="n">
-        <v>2.177340584438467</v>
+        <v>2.188998556135622</v>
       </c>
     </row>
     <row r="101">
@@ -3554,25 +3554,25 @@
         <v>200</v>
       </c>
       <c r="C101" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D101" t="n">
-        <v>206.5653533935547</v>
+        <v>202.6686401367188</v>
       </c>
       <c r="E101" t="n">
-        <v>232.3549041748047</v>
+        <v>235.3539276123047</v>
       </c>
       <c r="F101" t="n">
-        <v>86013706.68171692</v>
+        <v>2188973182.29628</v>
       </c>
       <c r="G101" t="n">
-        <v>218.1881767999353</v>
+        <v>218.3204501043177</v>
       </c>
       <c r="H101" t="n">
-        <v>4.120256931280375</v>
+        <v>3.513912503862053</v>
       </c>
       <c r="I101" t="n">
-        <v>2.029841602510003</v>
+        <v>1.874543278738065</v>
       </c>
     </row>
     <row r="102">
@@ -3585,25 +3585,25 @@
         <v>150</v>
       </c>
       <c r="C102" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D102" t="n">
-        <v>202.9137268066406</v>
+        <v>199.7282409667969</v>
       </c>
       <c r="E102" t="n">
-        <v>229.7372131347656</v>
+        <v>231.593505859375</v>
       </c>
       <c r="F102" t="n">
-        <v>83623884.26821899</v>
+        <v>2127541516.277298</v>
       </c>
       <c r="G102" t="n">
-        <v>212.1259918832195</v>
+        <v>212.1934728145124</v>
       </c>
       <c r="H102" t="n">
-        <v>5.51898371574673</v>
+        <v>3.717591481198834</v>
       </c>
       <c r="I102" t="n">
-        <v>2.349251735286521</v>
+        <v>1.928105671688882</v>
       </c>
     </row>
     <row r="103">
@@ -3616,25 +3616,25 @@
         <v>100</v>
       </c>
       <c r="C103" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D103" t="n">
-        <v>198.3208923339844</v>
+        <v>197.075439453125</v>
       </c>
       <c r="E103" t="n">
-        <v>226.6881866455078</v>
+        <v>229.3795166015625</v>
       </c>
       <c r="F103" t="n">
-        <v>81309057.20593262</v>
+        <v>2067850418.73085</v>
       </c>
       <c r="G103" t="n">
-        <v>206.2540452387578</v>
+        <v>206.2400936735711</v>
       </c>
       <c r="H103" t="n">
-        <v>10.80174101830508</v>
+        <v>7.949036296630696</v>
       </c>
       <c r="I103" t="n">
-        <v>3.286600221856178</v>
+        <v>2.81940353561364</v>
       </c>
     </row>
     <row r="104">
@@ -3647,25 +3647,25 @@
         <v>1000</v>
       </c>
       <c r="C104" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D104" t="n">
-        <v>-22.9334716796875</v>
+        <v>-35.444091796875</v>
       </c>
       <c r="E104" t="n">
-        <v>19.58624267578125</v>
+        <v>31.78263854980469</v>
       </c>
       <c r="F104" t="n">
-        <v>-1078328.365127563</v>
+        <v>-28661084.70574951</v>
       </c>
       <c r="G104" t="n">
-        <v>-2.735360549562841</v>
+        <v>-2.85855530987966</v>
       </c>
       <c r="H104" t="n">
-        <v>19.67459611549316</v>
+        <v>21.09356699685789</v>
       </c>
       <c r="I104" t="n">
-        <v>4.435605495926476</v>
+        <v>4.592773344816603</v>
       </c>
     </row>
     <row r="105">
@@ -3678,25 +3678,25 @@
         <v>975</v>
       </c>
       <c r="C105" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D105" t="n">
-        <v>-30.568359375</v>
+        <v>-44.34205627441406</v>
       </c>
       <c r="E105" t="n">
-        <v>22.20936584472656</v>
+        <v>35.90019226074219</v>
       </c>
       <c r="F105" t="n">
-        <v>-1156064.313446045</v>
+        <v>-31036257.70367432</v>
       </c>
       <c r="G105" t="n">
-        <v>-2.93255080550874</v>
+        <v>-3.095446671626996</v>
       </c>
       <c r="H105" t="n">
-        <v>23.34984234863069</v>
+        <v>25.17002160117967</v>
       </c>
       <c r="I105" t="n">
-        <v>4.832167458670145</v>
+        <v>5.016973350654721</v>
       </c>
     </row>
     <row r="106">
@@ -3709,25 +3709,25 @@
         <v>950</v>
       </c>
       <c r="C106" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D106" t="n">
-        <v>-32.83856201171875</v>
+        <v>-55.71876525878906</v>
       </c>
       <c r="E106" t="n">
-        <v>25.67814636230469</v>
+        <v>44.95748901367188</v>
       </c>
       <c r="F106" t="n">
-        <v>-1190303.111618042</v>
+        <v>-32511455.06626892</v>
       </c>
       <c r="G106" t="n">
-        <v>-3.019403253068206</v>
+        <v>-3.242577643718893</v>
       </c>
       <c r="H106" t="n">
-        <v>26.03895809434673</v>
+        <v>28.19293071790275</v>
       </c>
       <c r="I106" t="n">
-        <v>5.102838239092704</v>
+        <v>5.309701565804122</v>
       </c>
     </row>
     <row r="107">
@@ -3740,25 +3740,25 @@
         <v>925</v>
       </c>
       <c r="C107" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D107" t="n">
-        <v>-33.00567626953125</v>
+        <v>-58.72221374511719</v>
       </c>
       <c r="E107" t="n">
-        <v>27.86691284179688</v>
+        <v>49.02644348144531</v>
       </c>
       <c r="F107" t="n">
-        <v>-1152359.502197266</v>
+        <v>-32494862.96014404</v>
       </c>
       <c r="G107" t="n">
-        <v>-2.923152931112393</v>
+        <v>-3.240922805684942</v>
       </c>
       <c r="H107" t="n">
-        <v>27.25748554593234</v>
+        <v>29.73806395968585</v>
       </c>
       <c r="I107" t="n">
-        <v>5.220870190488588</v>
+        <v>5.453261772525307</v>
       </c>
     </row>
     <row r="108">
@@ -3771,25 +3771,25 @@
         <v>900</v>
       </c>
       <c r="C108" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D108" t="n">
-        <v>-32.19296264648438</v>
+        <v>-57.55891418457031</v>
       </c>
       <c r="E108" t="n">
-        <v>29.71080017089844</v>
+        <v>50.91188049316406</v>
       </c>
       <c r="F108" t="n">
-        <v>-1092860.501358032</v>
+        <v>-31972289.9831543</v>
       </c>
       <c r="G108" t="n">
-        <v>-2.772223747667616</v>
+        <v>-3.188803223557825</v>
       </c>
       <c r="H108" t="n">
-        <v>27.78987047241884</v>
+        <v>30.37371641299665</v>
       </c>
       <c r="I108" t="n">
-        <v>5.27160985586176</v>
+        <v>5.511235470654166</v>
       </c>
     </row>
     <row r="109">
@@ -3802,25 +3802,25 @@
         <v>875</v>
       </c>
       <c r="C109" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D109" t="n">
-        <v>-32.29544067382812</v>
+        <v>-55.08590698242188</v>
       </c>
       <c r="E109" t="n">
-        <v>30.33059692382812</v>
+        <v>52.4219970703125</v>
       </c>
       <c r="F109" t="n">
-        <v>-1032339.667633057</v>
+        <v>-31157462.40396118</v>
       </c>
       <c r="G109" t="n">
-        <v>-2.618702513921374</v>
+        <v>-3.107535200136789</v>
       </c>
       <c r="H109" t="n">
-        <v>28.30296020939144</v>
+        <v>30.78586801517007</v>
       </c>
       <c r="I109" t="n">
-        <v>5.320052650998055</v>
+        <v>5.548501420669375</v>
       </c>
     </row>
     <row r="110">
@@ -3833,25 +3833,25 @@
         <v>850</v>
       </c>
       <c r="C110" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D110" t="n">
-        <v>-31.87507629394531</v>
+        <v>-54.52687072753906</v>
       </c>
       <c r="E110" t="n">
-        <v>29.85150146484375</v>
+        <v>52.21392822265625</v>
       </c>
       <c r="F110" t="n">
-        <v>-979818.7085571289</v>
+        <v>-30273145.1541748</v>
       </c>
       <c r="G110" t="n">
-        <v>-2.485474302434515</v>
+        <v>-3.019336522524002</v>
       </c>
       <c r="H110" t="n">
-        <v>29.24737846511101</v>
+        <v>31.45466007862744</v>
       </c>
       <c r="I110" t="n">
-        <v>5.40808454677911</v>
+        <v>5.608445424413743</v>
       </c>
     </row>
     <row r="111">
@@ -3864,25 +3864,25 @@
         <v>825</v>
       </c>
       <c r="C111" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D111" t="n">
-        <v>-31.77372741699219</v>
+        <v>-53.82025146484375</v>
       </c>
       <c r="E111" t="n">
-        <v>28.90205383300781</v>
+        <v>53.10092163085938</v>
       </c>
       <c r="F111" t="n">
-        <v>-934385.2239379883</v>
+        <v>-29413944.10871887</v>
       </c>
       <c r="G111" t="n">
-        <v>-2.370224657265748</v>
+        <v>-2.933642846378917</v>
       </c>
       <c r="H111" t="n">
-        <v>30.75210616474475</v>
+        <v>32.57910105197477</v>
       </c>
       <c r="I111" t="n">
-        <v>5.54545815643259</v>
+        <v>5.707810530490195</v>
       </c>
     </row>
     <row r="112">
@@ -3895,25 +3895,25 @@
         <v>800</v>
       </c>
       <c r="C112" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D112" t="n">
-        <v>-32.03144836425781</v>
+        <v>-53.17196655273438</v>
       </c>
       <c r="E112" t="n">
-        <v>30.38276672363281</v>
+        <v>55.35334777832031</v>
       </c>
       <c r="F112" t="n">
-        <v>-895842.9237365723</v>
+        <v>-28605625.79428101</v>
       </c>
       <c r="G112" t="n">
-        <v>-2.272455655846694</v>
+        <v>-2.853024034023006</v>
       </c>
       <c r="H112" t="n">
-        <v>32.82717468121543</v>
+        <v>34.16042425945646</v>
       </c>
       <c r="I112" t="n">
-        <v>5.729500386701744</v>
+        <v>5.844691973017608</v>
       </c>
     </row>
     <row r="113">
@@ -3926,25 +3926,25 @@
         <v>775</v>
       </c>
       <c r="C113" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D113" t="n">
-        <v>-31.206298828125</v>
+        <v>-51.88919067382812</v>
       </c>
       <c r="E113" t="n">
-        <v>32.482666015625</v>
+        <v>57.48287963867188</v>
       </c>
       <c r="F113" t="n">
-        <v>-866018.369430542</v>
+        <v>-27833527.2855072</v>
       </c>
       <c r="G113" t="n">
-        <v>-2.196800677367706</v>
+        <v>-2.776017657095372</v>
       </c>
       <c r="H113" t="n">
-        <v>35.20803786353716</v>
+        <v>36.08159037987387</v>
       </c>
       <c r="I113" t="n">
-        <v>5.933636141822076</v>
+        <v>6.006795350257396</v>
       </c>
     </row>
     <row r="114">
@@ -3957,25 +3957,25 @@
         <v>750</v>
       </c>
       <c r="C114" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D114" t="n">
-        <v>-29.93806457519531</v>
+        <v>-50.31416320800781</v>
       </c>
       <c r="E114" t="n">
-        <v>34.19093322753906</v>
+        <v>58.69093322753906</v>
       </c>
       <c r="F114" t="n">
-        <v>-843392.5711517334</v>
+        <v>-26999438.57720947</v>
       </c>
       <c r="G114" t="n">
-        <v>-2.139406549553124</v>
+        <v>-2.692828596719821</v>
       </c>
       <c r="H114" t="n">
-        <v>37.60050338660189</v>
+        <v>38.14796134749733</v>
       </c>
       <c r="I114" t="n">
-        <v>6.131924933216477</v>
+        <v>6.176403593313615</v>
       </c>
     </row>
     <row r="115">
@@ -3988,25 +3988,25 @@
         <v>725</v>
       </c>
       <c r="C115" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D115" t="n">
-        <v>-27.82437133789062</v>
+        <v>-48.82179260253906</v>
       </c>
       <c r="E115" t="n">
-        <v>35.78532409667969</v>
+        <v>56.70549011230469</v>
       </c>
       <c r="F115" t="n">
-        <v>-803438.4392852783</v>
+        <v>-24917005.25315857</v>
       </c>
       <c r="G115" t="n">
-        <v>-2.038056200592763</v>
+        <v>-2.485134055600745</v>
       </c>
       <c r="H115" t="n">
-        <v>42.04104200022904</v>
+        <v>42.25084711657594</v>
       </c>
       <c r="I115" t="n">
-        <v>6.483906384289416</v>
+        <v>6.500065162486907</v>
       </c>
     </row>
     <row r="116">
@@ -4019,25 +4019,25 @@
         <v>700</v>
       </c>
       <c r="C116" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D116" t="n">
-        <v>-27.9178466796875</v>
+        <v>-48.69514465332031</v>
       </c>
       <c r="E116" t="n">
-        <v>35.87168884277344</v>
+        <v>54.64736938476562</v>
       </c>
       <c r="F116" t="n">
-        <v>-747700.9793548584</v>
+        <v>-22558606.70152283</v>
       </c>
       <c r="G116" t="n">
-        <v>-1.89666879583088</v>
+        <v>-2.24991571785099</v>
       </c>
       <c r="H116" t="n">
-        <v>45.82291409755237</v>
+        <v>45.94430222578744</v>
       </c>
       <c r="I116" t="n">
-        <v>6.769262448565011</v>
+        <v>6.778222645044012</v>
       </c>
     </row>
     <row r="117">
@@ -4050,25 +4050,25 @@
         <v>650</v>
       </c>
       <c r="C117" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D117" t="n">
-        <v>-28.03997802734375</v>
+        <v>-46.45986938476562</v>
       </c>
       <c r="E117" t="n">
-        <v>41.11424255371094</v>
+        <v>55.64677429199219</v>
       </c>
       <c r="F117" t="n">
-        <v>-672518.1488800049</v>
+        <v>-19913107.31484985</v>
       </c>
       <c r="G117" t="n">
-        <v>-1.705954951016963</v>
+        <v>-1.986062957332828</v>
       </c>
       <c r="H117" t="n">
-        <v>49.43485862156553</v>
+        <v>48.61532829265593</v>
       </c>
       <c r="I117" t="n">
-        <v>7.030992719493139</v>
+        <v>6.972469310987028</v>
       </c>
     </row>
     <row r="118">
@@ -4081,25 +4081,25 @@
         <v>600</v>
       </c>
       <c r="C118" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D118" t="n">
-        <v>-25.66099548339844</v>
+        <v>-42.60932922363281</v>
       </c>
       <c r="E118" t="n">
-        <v>45.2685546875</v>
+        <v>56.51473999023438</v>
       </c>
       <c r="F118" t="n">
-        <v>-584276.6830749512</v>
+        <v>-16863510.49951172</v>
       </c>
       <c r="G118" t="n">
-        <v>-1.482115689986127</v>
+        <v>-1.681906947224517</v>
       </c>
       <c r="H118" t="n">
-        <v>55.22782031366287</v>
+        <v>51.42436839154606</v>
       </c>
       <c r="I118" t="n">
-        <v>7.431542256736678</v>
+        <v>7.171078607263071</v>
       </c>
     </row>
     <row r="119">
@@ -4112,25 +4112,25 @@
         <v>550</v>
       </c>
       <c r="C119" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D119" t="n">
-        <v>-22.20646667480469</v>
+        <v>-44.61569213867188</v>
       </c>
       <c r="E119" t="n">
-        <v>48.92214965820312</v>
+        <v>63.27864074707031</v>
       </c>
       <c r="F119" t="n">
-        <v>-428689.1720123291</v>
+        <v>-13154174.16743469</v>
       </c>
       <c r="G119" t="n">
-        <v>-1.087441902734856</v>
+        <v>-1.311950849015109</v>
       </c>
       <c r="H119" t="n">
-        <v>62.7451744230825</v>
+        <v>56.20833926221006</v>
       </c>
       <c r="I119" t="n">
-        <v>7.921185165307178</v>
+        <v>7.497222103033233</v>
       </c>
     </row>
     <row r="120">
@@ -4143,25 +4143,25 @@
         <v>500</v>
       </c>
       <c r="C120" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D120" t="n">
-        <v>-22.81619262695312</v>
+        <v>-44.61308288574219</v>
       </c>
       <c r="E120" t="n">
-        <v>53.60504150390625</v>
+        <v>70.44790649414062</v>
       </c>
       <c r="F120" t="n">
-        <v>-165745.1889190674</v>
+        <v>-8158247.426391602</v>
       </c>
       <c r="G120" t="n">
-        <v>-0.4204404388411168</v>
+        <v>-0.8136747697949304</v>
       </c>
       <c r="H120" t="n">
-        <v>71.3584490946421</v>
+        <v>63.64295968479935</v>
       </c>
       <c r="I120" t="n">
-        <v>8.447393035406964</v>
+        <v>7.97765377067715</v>
       </c>
     </row>
     <row r="121">
@@ -4174,25 +4174,25 @@
         <v>450</v>
       </c>
       <c r="C121" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D121" t="n">
-        <v>-26.06614685058594</v>
+        <v>-48.41604614257812</v>
       </c>
       <c r="E121" t="n">
-        <v>52.83676147460938</v>
+        <v>77.19099426269531</v>
       </c>
       <c r="F121" t="n">
-        <v>162658.5317840576</v>
+        <v>-1540757.556732178</v>
       </c>
       <c r="G121" t="n">
-        <v>0.4126106159131689</v>
+        <v>-0.15366971418742</v>
       </c>
       <c r="H121" t="n">
-        <v>82.89229792420066</v>
+        <v>73.77414047976907</v>
       </c>
       <c r="I121" t="n">
-        <v>9.104520741049507</v>
+        <v>8.589187416733266</v>
       </c>
     </row>
     <row r="122">
@@ -4205,25 +4205,25 @@
         <v>400</v>
       </c>
       <c r="C122" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D122" t="n">
-        <v>-26.16886901855469</v>
+        <v>-51.37127685546875</v>
       </c>
       <c r="E122" t="n">
-        <v>53.19110107421875</v>
+        <v>81.51275634765625</v>
       </c>
       <c r="F122" t="n">
-        <v>467888.8819122314</v>
+        <v>6650853.389419556</v>
       </c>
       <c r="G122" t="n">
-        <v>1.186878533989395</v>
+        <v>0.6633326151728853</v>
       </c>
       <c r="H122" t="n">
-        <v>101.3479041423663</v>
+        <v>88.24840345671007</v>
       </c>
       <c r="I122" t="n">
-        <v>10.06716961923093</v>
+        <v>9.394062138218485</v>
       </c>
     </row>
     <row r="123">
@@ -4236,25 +4236,25 @@
         <v>350</v>
       </c>
       <c r="C123" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D123" t="n">
-        <v>-30.62335205078125</v>
+        <v>-52.45257568359375</v>
       </c>
       <c r="E123" t="n">
-        <v>56.08737182617188</v>
+        <v>84.01470947265625</v>
       </c>
       <c r="F123" t="n">
-        <v>790984.0880737305</v>
+        <v>17100744.74638367</v>
       </c>
       <c r="G123" t="n">
-        <v>2.006463652278004</v>
+        <v>1.705567852701174</v>
       </c>
       <c r="H123" t="n">
-        <v>128.6787739523889</v>
+        <v>109.7875129566108</v>
       </c>
       <c r="I123" t="n">
-        <v>11.34366668905557</v>
+        <v>10.47795366264858</v>
       </c>
     </row>
     <row r="124">
@@ -4267,25 +4267,25 @@
         <v>300</v>
       </c>
       <c r="C124" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D124" t="n">
-        <v>-30.83444213867188</v>
+        <v>-48.10688781738281</v>
       </c>
       <c r="E124" t="n">
-        <v>61.15377807617188</v>
+        <v>84.57643127441406</v>
       </c>
       <c r="F124" t="n">
-        <v>1248420.024703979</v>
+        <v>30142345.76089478</v>
       </c>
       <c r="G124" t="n">
-        <v>3.166826539386784</v>
+        <v>3.006291053239497</v>
       </c>
       <c r="H124" t="n">
-        <v>163.3740719189275</v>
+        <v>138.7934274237285</v>
       </c>
       <c r="I124" t="n">
-        <v>12.78178672639031</v>
+        <v>11.78106223664609</v>
       </c>
     </row>
     <row r="125">
@@ -4298,25 +4298,25 @@
         <v>250</v>
       </c>
       <c r="C125" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D125" t="n">
-        <v>-33.55961608886719</v>
+        <v>-46.27247619628906</v>
       </c>
       <c r="E125" t="n">
-        <v>67.1746826171875</v>
+        <v>82.59519958496094</v>
       </c>
       <c r="F125" t="n">
-        <v>1530951.221893311</v>
+        <v>37796574.24908447</v>
       </c>
       <c r="G125" t="n">
-        <v>3.883514253264211</v>
+        <v>3.769696755172261</v>
       </c>
       <c r="H125" t="n">
-        <v>177.9561213291026</v>
+        <v>153.5021143108031</v>
       </c>
       <c r="I125" t="n">
-        <v>13.340019540057</v>
+        <v>12.38959701970985</v>
       </c>
     </row>
     <row r="126">
@@ -4329,25 +4329,25 @@
         <v>200</v>
       </c>
       <c r="C126" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D126" t="n">
-        <v>-32.19941711425781</v>
+        <v>-44.70292663574219</v>
       </c>
       <c r="E126" t="n">
-        <v>77.09477233886719</v>
+        <v>83.59883117675781</v>
       </c>
       <c r="F126" t="n">
-        <v>1807116.12260437</v>
+        <v>46234103.39624023</v>
       </c>
       <c r="G126" t="n">
-        <v>4.584052789584362</v>
+        <v>4.611226096908199</v>
       </c>
       <c r="H126" t="n">
-        <v>182.9350741665307</v>
+        <v>161.9187947343962</v>
       </c>
       <c r="I126" t="n">
-        <v>13.52534931772672</v>
+        <v>12.7247316173818</v>
       </c>
     </row>
     <row r="127">
@@ -4360,25 +4360,25 @@
         <v>150</v>
       </c>
       <c r="C127" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D127" t="n">
-        <v>-30.49545288085938</v>
+        <v>-42.92500305175781</v>
       </c>
       <c r="E127" t="n">
-        <v>57.87493896484375</v>
+        <v>79.32940673828125</v>
       </c>
       <c r="F127" t="n">
-        <v>2017270.247619629</v>
+        <v>52524229.86404419</v>
       </c>
       <c r="G127" t="n">
-        <v>5.117143934624064</v>
+        <v>5.238581083607199</v>
       </c>
       <c r="H127" t="n">
-        <v>165.3858799559919</v>
+        <v>155.1328340536776</v>
       </c>
       <c r="I127" t="n">
-        <v>12.86024416393374</v>
+        <v>12.45523319948999</v>
       </c>
     </row>
     <row r="128">
@@ -4391,25 +4391,25 @@
         <v>100</v>
       </c>
       <c r="C128" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D128" t="n">
-        <v>-33.28498840332031</v>
+        <v>-38.6629638671875</v>
       </c>
       <c r="E128" t="n">
-        <v>52.16705322265625</v>
+        <v>72.023681640625</v>
       </c>
       <c r="F128" t="n">
-        <v>2011528.651062012</v>
+        <v>52531240.88981628</v>
       </c>
       <c r="G128" t="n">
-        <v>5.10257941307097</v>
+        <v>5.239280338543074</v>
       </c>
       <c r="H128" t="n">
-        <v>133.9225307353121</v>
+        <v>128.9300631317917</v>
       </c>
       <c r="I128" t="n">
-        <v>11.57249025643626</v>
+        <v>11.35473747524758</v>
       </c>
     </row>
     <row r="129">
@@ -4422,25 +4422,25 @@
         <v>1000</v>
       </c>
       <c r="C129" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D129" t="n">
-        <v>-21.50288391113281</v>
+        <v>-32.6859130859375</v>
       </c>
       <c r="E129" t="n">
-        <v>26.79173278808594</v>
+        <v>34.28530883789062</v>
       </c>
       <c r="F129" t="n">
-        <v>122155.1018066406</v>
+        <v>3020644.900299072</v>
       </c>
       <c r="G129" t="n">
-        <v>0.3098668802709176</v>
+        <v>0.3012684484086758</v>
       </c>
       <c r="H129" t="n">
-        <v>14.47832135783567</v>
+        <v>14.44922339250339</v>
       </c>
       <c r="I129" t="n">
-        <v>3.80503894301171</v>
+        <v>3.801213410544506</v>
       </c>
     </row>
     <row r="130">
@@ -4453,25 +4453,25 @@
         <v>975</v>
       </c>
       <c r="C130" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D130" t="n">
-        <v>-25.65390014648438</v>
+        <v>-38.95536804199219</v>
       </c>
       <c r="E130" t="n">
-        <v>31.99162292480469</v>
+        <v>40.86978149414062</v>
       </c>
       <c r="F130" t="n">
-        <v>150429.0801086426</v>
+        <v>3610669.231277466</v>
       </c>
       <c r="G130" t="n">
-        <v>0.3815885629490348</v>
+        <v>0.3601153902321367</v>
       </c>
       <c r="H130" t="n">
-        <v>17.33361680641011</v>
+        <v>17.07739181541644</v>
       </c>
       <c r="I130" t="n">
-        <v>4.163366042808404</v>
+        <v>4.132480104660691</v>
       </c>
     </row>
     <row r="131">
@@ -4484,25 +4484,25 @@
         <v>950</v>
       </c>
       <c r="C131" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D131" t="n">
-        <v>-27.82687377929688</v>
+        <v>-48.9976806640625</v>
       </c>
       <c r="E131" t="n">
-        <v>34.26536560058594</v>
+        <v>53.12228393554688</v>
       </c>
       <c r="F131" t="n">
-        <v>191057.3131561279</v>
+        <v>4672600.524200439</v>
       </c>
       <c r="G131" t="n">
-        <v>0.4846488824866646</v>
+        <v>0.4660286648788342</v>
       </c>
       <c r="H131" t="n">
-        <v>18.22655880730016</v>
+        <v>17.84978739926698</v>
       </c>
       <c r="I131" t="n">
-        <v>4.269257407008877</v>
+        <v>4.224900874490072</v>
       </c>
     </row>
     <row r="132">
@@ -4515,25 +4515,25 @@
         <v>925</v>
       </c>
       <c r="C132" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D132" t="n">
-        <v>-27.85169982910156</v>
+        <v>-54.05300903320312</v>
       </c>
       <c r="E132" t="n">
-        <v>36.278564453125</v>
+        <v>59.66902160644531</v>
       </c>
       <c r="F132" t="n">
-        <v>217398.091796875</v>
+        <v>5516435.754348755</v>
       </c>
       <c r="G132" t="n">
-        <v>0.5514666803567446</v>
+        <v>0.5501898089028102</v>
       </c>
       <c r="H132" t="n">
-        <v>17.56061721830091</v>
+        <v>17.27271407468447</v>
       </c>
       <c r="I132" t="n">
-        <v>4.19053901285991</v>
+        <v>4.156045485155867</v>
       </c>
     </row>
     <row r="133">
@@ -4546,25 +4546,25 @@
         <v>900</v>
       </c>
       <c r="C133" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D133" t="n">
-        <v>-27.69862365722656</v>
+        <v>-56.42100524902344</v>
       </c>
       <c r="E133" t="n">
-        <v>37.52203369140625</v>
+        <v>59.36355590820312</v>
       </c>
       <c r="F133" t="n">
-        <v>223706.2172088623</v>
+        <v>5868094.359527588</v>
       </c>
       <c r="G133" t="n">
-        <v>0.5674682972590354</v>
+        <v>0.5852629955396456</v>
       </c>
       <c r="H133" t="n">
-        <v>16.6898828121391</v>
+        <v>16.41085197056272</v>
       </c>
       <c r="I133" t="n">
-        <v>4.08532530065099</v>
+        <v>4.051030976253172</v>
       </c>
     </row>
     <row r="134">
@@ -4577,25 +4577,25 @@
         <v>875</v>
       </c>
       <c r="C134" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D134" t="n">
-        <v>-27.07244873046875</v>
+        <v>-56.56988525390625</v>
       </c>
       <c r="E134" t="n">
-        <v>37.88798522949219</v>
+        <v>60.85801696777344</v>
       </c>
       <c r="F134" t="n">
-        <v>218301.3333435059</v>
+        <v>5915523.936264038</v>
       </c>
       <c r="G134" t="n">
-        <v>0.5537579038590471</v>
+        <v>0.589993453923103</v>
       </c>
       <c r="H134" t="n">
-        <v>16.07907789580208</v>
+        <v>15.74153775086646</v>
       </c>
       <c r="I134" t="n">
-        <v>4.009872553561033</v>
+        <v>3.967560680174465</v>
       </c>
     </row>
     <row r="135">
@@ -4608,25 +4608,25 @@
         <v>850</v>
       </c>
       <c r="C135" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D135" t="n">
-        <v>-25.58905029296875</v>
+        <v>-54.69912719726562</v>
       </c>
       <c r="E135" t="n">
-        <v>37.35763549804688</v>
+        <v>60.85945129394531</v>
       </c>
       <c r="F135" t="n">
-        <v>211916.9646759033</v>
+        <v>5830283.297821045</v>
       </c>
       <c r="G135" t="n">
-        <v>0.5375628831659217</v>
+        <v>0.5814918538566606</v>
       </c>
       <c r="H135" t="n">
-        <v>15.69779626890539</v>
+        <v>15.38649233473598</v>
       </c>
       <c r="I135" t="n">
-        <v>3.96204445569524</v>
+        <v>3.922561960598708</v>
       </c>
     </row>
     <row r="136">
@@ -4639,25 +4639,25 @@
         <v>825</v>
       </c>
       <c r="C136" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D136" t="n">
-        <v>-24.31123352050781</v>
+        <v>-52.16448974609375</v>
       </c>
       <c r="E136" t="n">
-        <v>37.20388793945312</v>
+        <v>60.96000671386719</v>
       </c>
       <c r="F136" t="n">
-        <v>202725.1875610352</v>
+        <v>5679253.127593994</v>
       </c>
       <c r="G136" t="n">
-        <v>0.5142464006236023</v>
+        <v>0.5664286383682402</v>
       </c>
       <c r="H136" t="n">
-        <v>15.50413930792794</v>
+        <v>15.23839565059458</v>
       </c>
       <c r="I136" t="n">
-        <v>3.937529594546298</v>
+        <v>3.903638770505614</v>
       </c>
     </row>
     <row r="137">
@@ -4670,25 +4670,25 @@
         <v>800</v>
       </c>
       <c r="C137" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D137" t="n">
-        <v>-24.91856384277344</v>
+        <v>-50.418212890625</v>
       </c>
       <c r="E137" t="n">
-        <v>37.12962341308594</v>
+        <v>60.94770812988281</v>
       </c>
       <c r="F137" t="n">
-        <v>187470.9384918213</v>
+        <v>5515778.191925049</v>
       </c>
       <c r="G137" t="n">
-        <v>0.4755514423284105</v>
+        <v>0.5501242259502781</v>
       </c>
       <c r="H137" t="n">
-        <v>15.44156427300516</v>
+        <v>15.21273498515589</v>
       </c>
       <c r="I137" t="n">
-        <v>3.929575584335433</v>
+        <v>3.900350623361429</v>
       </c>
     </row>
     <row r="138">
@@ -4701,25 +4701,25 @@
         <v>775</v>
       </c>
       <c r="C138" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D138" t="n">
-        <v>-26.27743530273438</v>
+        <v>-49.16567993164062</v>
       </c>
       <c r="E138" t="n">
-        <v>36.5238037109375</v>
+        <v>60.76625061035156</v>
       </c>
       <c r="F138" t="n">
-        <v>165558.2007293701</v>
+        <v>5309552.364990234</v>
       </c>
       <c r="G138" t="n">
-        <v>0.4199661119719805</v>
+        <v>0.5295559907047843</v>
       </c>
       <c r="H138" t="n">
-        <v>15.51083362450106</v>
+        <v>15.29012520552146</v>
       </c>
       <c r="I138" t="n">
-        <v>3.938379568363246</v>
+        <v>3.910258969112079</v>
       </c>
     </row>
     <row r="139">
@@ -4732,25 +4732,25 @@
         <v>750</v>
       </c>
       <c r="C139" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D139" t="n">
-        <v>-27.48410034179688</v>
+        <v>-48.96044921875</v>
       </c>
       <c r="E139" t="n">
-        <v>35.51132202148438</v>
+        <v>59.72929382324219</v>
       </c>
       <c r="F139" t="n">
-        <v>136703.3706359863</v>
+        <v>5056341.021194458</v>
       </c>
       <c r="G139" t="n">
-        <v>0.3467710014154259</v>
+        <v>0.5043015860386549</v>
       </c>
       <c r="H139" t="n">
-        <v>15.77934587132553</v>
+        <v>15.47025486413227</v>
       </c>
       <c r="I139" t="n">
-        <v>3.972322478264514</v>
+        <v>3.933224486872351</v>
       </c>
     </row>
     <row r="140">
@@ -4763,25 +4763,25 @@
         <v>725</v>
       </c>
       <c r="C140" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D140" t="n">
-        <v>-30.44332885742188</v>
+        <v>-48.434814453125</v>
       </c>
       <c r="E140" t="n">
-        <v>33.33914184570312</v>
+        <v>56.40139770507812</v>
       </c>
       <c r="F140" t="n">
-        <v>82291.52346801758</v>
+        <v>4489154.588195801</v>
       </c>
       <c r="G140" t="n">
-        <v>0.208746235504258</v>
+        <v>0.4477324154582145</v>
       </c>
       <c r="H140" t="n">
-        <v>16.70092029726263</v>
+        <v>16.15148017788225</v>
       </c>
       <c r="I140" t="n">
-        <v>4.086675947180377</v>
+        <v>4.018890416256986</v>
       </c>
     </row>
     <row r="141">
@@ -4794,25 +4794,25 @@
         <v>700</v>
       </c>
       <c r="C141" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D141" t="n">
-        <v>-34.03253173828125</v>
+        <v>-45.97933959960938</v>
       </c>
       <c r="E141" t="n">
-        <v>30.89315795898438</v>
+        <v>54.9803466796875</v>
       </c>
       <c r="F141" t="n">
-        <v>61658.2776184082</v>
+        <v>3944211.800079346</v>
       </c>
       <c r="G141" t="n">
-        <v>0.1564065507369227</v>
+        <v>0.3933817474167355</v>
       </c>
       <c r="H141" t="n">
-        <v>17.49920420757357</v>
+        <v>17.14517794723772</v>
       </c>
       <c r="I141" t="n">
-        <v>4.183205016201521</v>
+        <v>4.140673610324498</v>
       </c>
     </row>
     <row r="142">
@@ -4825,25 +4825,25 @@
         <v>650</v>
       </c>
       <c r="C142" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D142" t="n">
-        <v>-37.7928466796875</v>
+        <v>-46.01249694824219</v>
       </c>
       <c r="E142" t="n">
-        <v>34.58541870117188</v>
+        <v>53.02639770507812</v>
       </c>
       <c r="F142" t="n">
-        <v>36972.93760681152</v>
+        <v>3028931.376663208</v>
       </c>
       <c r="G142" t="n">
-        <v>0.09378805028388243</v>
+        <v>0.3020949122796049</v>
       </c>
       <c r="H142" t="n">
-        <v>18.55893565900011</v>
+        <v>17.99249601527588</v>
       </c>
       <c r="I142" t="n">
-        <v>4.308008316960414</v>
+        <v>4.241756241850288</v>
       </c>
     </row>
     <row r="143">
@@ -4856,25 +4856,25 @@
         <v>600</v>
       </c>
       <c r="C143" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D143" t="n">
-        <v>-40.87567138671875</v>
+        <v>-45.54269409179688</v>
       </c>
       <c r="E143" t="n">
-        <v>37.80673217773438</v>
+        <v>51.60366821289062</v>
       </c>
       <c r="F143" t="n">
-        <v>-11294.0147857666</v>
+        <v>1591780.694747925</v>
       </c>
       <c r="G143" t="n">
-        <v>-0.0286491605806092</v>
+        <v>0.1587585816744345</v>
       </c>
       <c r="H143" t="n">
-        <v>20.70052591165241</v>
+        <v>18.90006331741872</v>
       </c>
       <c r="I143" t="n">
-        <v>4.549783062042894</v>
+        <v>4.347420306045726</v>
       </c>
     </row>
     <row r="144">
@@ -4887,25 +4887,25 @@
         <v>550</v>
       </c>
       <c r="C144" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D144" t="n">
         <v>-46.11848449707031</v>
       </c>
       <c r="E144" t="n">
-        <v>43.76499938964844</v>
+        <v>53.69560241699219</v>
       </c>
       <c r="F144" t="n">
-        <v>-36559.31307983398</v>
+        <v>646192.4318695068</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.09273882237704512</v>
+        <v>0.06444894972708659</v>
       </c>
       <c r="H144" t="n">
-        <v>23.95673633715635</v>
+        <v>20.68592604502885</v>
       </c>
       <c r="I144" t="n">
-        <v>4.894561914733161</v>
+        <v>4.548178321595235</v>
       </c>
     </row>
     <row r="145">
@@ -4918,25 +4918,25 @@
         <v>500</v>
       </c>
       <c r="C145" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D145" t="n">
-        <v>-50.27876281738281</v>
+        <v>-52.96994018554688</v>
       </c>
       <c r="E145" t="n">
-        <v>46.60466003417969</v>
+        <v>53.25816345214844</v>
       </c>
       <c r="F145" t="n">
-        <v>-64371.66847229004</v>
+        <v>162560.3520812988</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.1632895212098129</v>
+        <v>0.01621319508276266</v>
       </c>
       <c r="H145" t="n">
-        <v>29.15266824842865</v>
+        <v>24.29358574198843</v>
       </c>
       <c r="I145" t="n">
-        <v>5.399321091436279</v>
+        <v>4.928852375755277</v>
       </c>
     </row>
     <row r="146">
@@ -4949,25 +4949,25 @@
         <v>450</v>
       </c>
       <c r="C146" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D146" t="n">
-        <v>-52.30003356933594</v>
+        <v>-59.32827758789062</v>
       </c>
       <c r="E146" t="n">
-        <v>50.53709411621094</v>
+        <v>62.3621826171875</v>
       </c>
       <c r="F146" t="n">
-        <v>-56404.59408569336</v>
+        <v>-199866.6874542236</v>
       </c>
       <c r="G146" t="n">
-        <v>-0.1430797023111407</v>
+        <v>-0.01993399714476679</v>
       </c>
       <c r="H146" t="n">
-        <v>37.23316572790047</v>
+        <v>30.29919735649806</v>
       </c>
       <c r="I146" t="n">
-        <v>6.101898534710362</v>
+        <v>5.504470669964375</v>
       </c>
     </row>
     <row r="147">
@@ -4980,25 +4980,25 @@
         <v>400</v>
       </c>
       <c r="C147" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D147" t="n">
-        <v>-51.90702819824219</v>
+        <v>-64.51643371582031</v>
       </c>
       <c r="E147" t="n">
-        <v>60.72650146484375</v>
+        <v>67.37187194824219</v>
       </c>
       <c r="F147" t="n">
-        <v>-108295.0357208252</v>
+        <v>-1999696.746002197</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.2747085006793838</v>
+        <v>-0.1994426871878628</v>
       </c>
       <c r="H147" t="n">
-        <v>50.3531261543393</v>
+        <v>39.49901982341642</v>
       </c>
       <c r="I147" t="n">
-        <v>7.095993669271365</v>
+        <v>6.284824565842424</v>
       </c>
     </row>
     <row r="148">
@@ -5011,25 +5011,25 @@
         <v>350</v>
       </c>
       <c r="C148" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D148" t="n">
-        <v>-53.11598205566406</v>
+        <v>-73.39028930664062</v>
       </c>
       <c r="E148" t="n">
-        <v>56.94277954101562</v>
+        <v>71.73358154296875</v>
       </c>
       <c r="F148" t="n">
-        <v>-287418.049621582</v>
+        <v>-5368325.766494751</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.7290840337619844</v>
+        <v>-0.5354178420853304</v>
       </c>
       <c r="H148" t="n">
-        <v>69.04569877334433</v>
+        <v>53.91605239840818</v>
       </c>
       <c r="I148" t="n">
-        <v>8.309374150520863</v>
+        <v>7.342755095902912</v>
       </c>
     </row>
     <row r="149">
@@ -5042,25 +5042,25 @@
         <v>300</v>
       </c>
       <c r="C149" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D149" t="n">
-        <v>-59.845947265625</v>
+        <v>-70.07968139648438</v>
       </c>
       <c r="E149" t="n">
-        <v>59.96238708496094</v>
+        <v>72.16477966308594</v>
       </c>
       <c r="F149" t="n">
-        <v>-412831.1396484375</v>
+        <v>-8161206.19102478</v>
       </c>
       <c r="G149" t="n">
-        <v>-1.04721534696142</v>
+        <v>-0.8139698665241614</v>
       </c>
       <c r="H149" t="n">
-        <v>90.31000324082221</v>
+        <v>73.40046996390346</v>
       </c>
       <c r="I149" t="n">
-        <v>9.503157540566304</v>
+        <v>8.567407423713632</v>
       </c>
     </row>
     <row r="150">
@@ -5073,25 +5073,25 @@
         <v>250</v>
       </c>
       <c r="C150" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D150" t="n">
-        <v>-55.91635131835938</v>
+        <v>-74.46308898925781</v>
       </c>
       <c r="E150" t="n">
-        <v>56.62527465820312</v>
+        <v>71.28730773925781</v>
       </c>
       <c r="F150" t="n">
-        <v>-402047.4902038574</v>
+        <v>-8586156.153442383</v>
       </c>
       <c r="G150" t="n">
-        <v>-1.019860813569794</v>
+        <v>-0.8563528741448863</v>
       </c>
       <c r="H150" t="n">
-        <v>97.15111647242098</v>
+        <v>81.41272557321636</v>
       </c>
       <c r="I150" t="n">
-        <v>9.856526592690804</v>
+        <v>9.022900064459119</v>
       </c>
     </row>
     <row r="151">
@@ -5104,25 +5104,25 @@
         <v>200</v>
       </c>
       <c r="C151" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D151" t="n">
-        <v>-48.56727600097656</v>
+        <v>-67.33631896972656</v>
       </c>
       <c r="E151" t="n">
-        <v>54.89076232910156</v>
+        <v>68.48300170898438</v>
       </c>
       <c r="F151" t="n">
-        <v>-407099.5149383545</v>
+        <v>-8565346.925323486</v>
       </c>
       <c r="G151" t="n">
-        <v>-1.032676120670173</v>
+        <v>-0.8542774352651464</v>
       </c>
       <c r="H151" t="n">
-        <v>96.90526441648126</v>
+        <v>83.22094461297077</v>
       </c>
       <c r="I151" t="n">
-        <v>9.844047156351968</v>
+        <v>9.122551431094854</v>
       </c>
     </row>
     <row r="152">
@@ -5135,25 +5135,25 @@
         <v>150</v>
       </c>
       <c r="C152" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D152" t="n">
-        <v>-45.53550720214844</v>
+        <v>-58.65924072265625</v>
       </c>
       <c r="E152" t="n">
-        <v>51.41148376464844</v>
+        <v>59.37025451660156</v>
       </c>
       <c r="F152" t="n">
-        <v>-418274.9579162598</v>
+        <v>-8425962.950408936</v>
       </c>
       <c r="G152" t="n">
-        <v>-1.06102450399591</v>
+        <v>-0.8403757701434471</v>
       </c>
       <c r="H152" t="n">
-        <v>87.11365995888548</v>
+        <v>75.16175704335838</v>
       </c>
       <c r="I152" t="n">
-        <v>9.333469877751011</v>
+        <v>8.669588054997675</v>
       </c>
     </row>
     <row r="153">
@@ -5166,25 +5166,25 @@
         <v>100</v>
       </c>
       <c r="C153" t="n">
-        <v>394218</v>
+        <v>10026423</v>
       </c>
       <c r="D153" t="n">
-        <v>-36.68861389160156</v>
+        <v>-55.7503662109375</v>
       </c>
       <c r="E153" t="n">
-        <v>43.11709594726562</v>
+        <v>46.62557983398438</v>
       </c>
       <c r="F153" t="n">
-        <v>-413060.3690032959</v>
+        <v>-7540293.468109131</v>
       </c>
       <c r="G153" t="n">
-        <v>-1.047796825622615</v>
+        <v>-0.7520422256381086</v>
       </c>
       <c r="H153" t="n">
-        <v>69.06979997962975</v>
+        <v>57.84846532460295</v>
       </c>
       <c r="I153" t="n">
-        <v>8.310824265957605</v>
+        <v>7.605817860335794</v>
       </c>
     </row>
   </sheetData>

--- a/models/resnet18/data_train_statistics.xlsx
+++ b/models/resnet18/data_train_statistics.xlsx
@@ -485,25 +485,25 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D2" t="n">
-        <v>57244.16796875</v>
+        <v>57229.859375</v>
       </c>
       <c r="E2" t="n">
-        <v>104155.375</v>
+        <v>104148.953125</v>
       </c>
       <c r="F2" t="n">
-        <v>1010045075649.812</v>
+        <v>997938280727.6406</v>
       </c>
       <c r="G2" t="n">
-        <v>100738.3266843829</v>
+        <v>100756.5061103958</v>
       </c>
       <c r="H2" t="n">
-        <v>7189362.991270711</v>
+        <v>6872947.682027092</v>
       </c>
       <c r="I2" t="n">
-        <v>2681.298750842716</v>
+        <v>2621.630729532115</v>
       </c>
     </row>
     <row r="3">
@@ -516,25 +516,25 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>7751633</v>
+        <v>7665278</v>
       </c>
       <c r="D3" t="n">
-        <v>272.838134765625</v>
+        <v>273.029052734375</v>
       </c>
       <c r="E3" t="n">
-        <v>307.6376953125</v>
+        <v>307.64306640625</v>
       </c>
       <c r="F3" t="n">
-        <v>2324946528.585205</v>
+        <v>2299262388.786377</v>
       </c>
       <c r="G3" t="n">
-        <v>299.9299023296387</v>
+        <v>299.9581213866445</v>
       </c>
       <c r="H3" t="n">
-        <v>6.173281914396444</v>
+        <v>6.045553630239024</v>
       </c>
       <c r="I3" t="n">
-        <v>2.484609006342133</v>
+        <v>2.458770755934563</v>
       </c>
     </row>
     <row r="4">
@@ -547,25 +547,25 @@
         <v>1000</v>
       </c>
       <c r="C4" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D4" t="n">
-        <v>-4322.37109375</v>
+        <v>-5028.0546875</v>
       </c>
       <c r="E4" t="n">
-        <v>3362.25</v>
+        <v>3345.8203125</v>
       </c>
       <c r="F4" t="n">
-        <v>13020649555.28638</v>
+        <v>12890629541.0498</v>
       </c>
       <c r="G4" t="n">
-        <v>1298.633576030693</v>
+        <v>1301.498117872192</v>
       </c>
       <c r="H4" t="n">
-        <v>130661.1472207419</v>
+        <v>129566.1263183947</v>
       </c>
       <c r="I4" t="n">
-        <v>361.4708110217779</v>
+        <v>359.9529501454249</v>
       </c>
     </row>
     <row r="5">
@@ -578,25 +578,25 @@
         <v>975</v>
       </c>
       <c r="C5" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D5" t="n">
-        <v>-2161.78466796875</v>
+        <v>-2872.02001953125</v>
       </c>
       <c r="E5" t="n">
-        <v>5434.396484375</v>
+        <v>5412.08740234375</v>
       </c>
       <c r="F5" t="n">
-        <v>34770480594.78125</v>
+        <v>34377225323.5813</v>
       </c>
       <c r="G5" t="n">
-        <v>3467.884867293271</v>
+        <v>3470.885104085111</v>
       </c>
       <c r="H5" t="n">
-        <v>125153.9994691315</v>
+        <v>124054.0283873549</v>
       </c>
       <c r="I5" t="n">
-        <v>353.771111693891</v>
+        <v>352.2130440335152</v>
       </c>
     </row>
     <row r="6">
@@ -609,25 +609,25 @@
         <v>950</v>
       </c>
       <c r="C6" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D6" t="n">
-        <v>50.734619140625</v>
+        <v>-667.4052734375</v>
       </c>
       <c r="E6" t="n">
-        <v>7546.09375</v>
+        <v>7521.96826171875</v>
       </c>
       <c r="F6" t="n">
-        <v>56986195687.36523</v>
+        <v>56323154445.05591</v>
       </c>
       <c r="G6" t="n">
-        <v>5683.601787732804</v>
+        <v>5686.648527865045</v>
       </c>
       <c r="H6" t="n">
-        <v>118571.0881351793</v>
+        <v>117567.3584005246</v>
       </c>
       <c r="I6" t="n">
-        <v>344.3415283336869</v>
+        <v>342.8809682681799</v>
       </c>
     </row>
     <row r="7">
@@ -640,25 +640,25 @@
         <v>925</v>
       </c>
       <c r="C7" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D7" t="n">
-        <v>2381.0029296875</v>
+        <v>1636.52734375</v>
       </c>
       <c r="E7" t="n">
-        <v>9699.1630859375</v>
+        <v>9677.3974609375</v>
       </c>
       <c r="F7" t="n">
-        <v>79689262969.65063</v>
+        <v>78749802870.93628</v>
       </c>
       <c r="G7" t="n">
-        <v>7947.925493433777</v>
+        <v>7950.94761609158</v>
       </c>
       <c r="H7" t="n">
-        <v>112540.3054415104</v>
+        <v>111676.4764480491</v>
       </c>
       <c r="I7" t="n">
-        <v>335.4702750490875</v>
+        <v>334.1803052964808</v>
       </c>
     </row>
     <row r="8">
@@ -671,25 +671,25 @@
         <v>900</v>
       </c>
       <c r="C8" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D8" t="n">
-        <v>4762.21826171875</v>
+        <v>4009.0361328125</v>
       </c>
       <c r="E8" t="n">
-        <v>11911.2939453125</v>
+        <v>11898.005859375</v>
       </c>
       <c r="F8" t="n">
-        <v>102910447713.0308</v>
+        <v>101687648110.1216</v>
       </c>
       <c r="G8" t="n">
-        <v>10263.92440385074</v>
+        <v>10266.85952029883</v>
       </c>
       <c r="H8" t="n">
-        <v>107619.6883903062</v>
+        <v>106929.1387918027</v>
       </c>
       <c r="I8" t="n">
-        <v>328.0543985230287</v>
+        <v>327.000212219813</v>
       </c>
     </row>
     <row r="9">
@@ -702,25 +702,25 @@
         <v>875</v>
       </c>
       <c r="C9" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D9" t="n">
-        <v>7199.91796875</v>
+        <v>6452.4140625</v>
       </c>
       <c r="E9" t="n">
-        <v>14205.31640625</v>
+        <v>14181.26171875</v>
       </c>
       <c r="F9" t="n">
-        <v>126682940276.2607</v>
+        <v>125170208066.3564</v>
       </c>
       <c r="G9" t="n">
-        <v>12634.90880808245</v>
+        <v>12637.76836447405</v>
       </c>
       <c r="H9" t="n">
-        <v>104140.4987560865</v>
+        <v>103684.3255511515</v>
       </c>
       <c r="I9" t="n">
-        <v>322.7080704848989</v>
+        <v>322.0005055138136</v>
       </c>
     </row>
     <row r="10">
@@ -733,25 +733,25 @@
         <v>850</v>
       </c>
       <c r="C10" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D10" t="n">
-        <v>9703.72265625</v>
+        <v>8969.5859375</v>
       </c>
       <c r="E10" t="n">
-        <v>16554.390625</v>
+        <v>16519.91796875</v>
       </c>
       <c r="F10" t="n">
-        <v>151039716702.8516</v>
+        <v>149230516180.3008</v>
       </c>
       <c r="G10" t="n">
-        <v>15064.16762018232</v>
+        <v>15067.00935895018</v>
       </c>
       <c r="H10" t="n">
-        <v>102285.027405662</v>
+        <v>102149.0819664164</v>
       </c>
       <c r="I10" t="n">
-        <v>319.8203048676897</v>
+        <v>319.6077001050138</v>
       </c>
     </row>
     <row r="11">
@@ -764,25 +764,25 @@
         <v>825</v>
       </c>
       <c r="C11" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D11" t="n">
-        <v>12279.2109375</v>
+        <v>11560.8359375</v>
       </c>
       <c r="E11" t="n">
-        <v>18961.08203125</v>
+        <v>18918.2578125</v>
       </c>
       <c r="F11" t="n">
-        <v>176012794504.0391</v>
+        <v>173900176066.1172</v>
       </c>
       <c r="G11" t="n">
-        <v>17554.8941535819</v>
+        <v>17557.77335210444</v>
       </c>
       <c r="H11" t="n">
-        <v>101978.000511229</v>
+        <v>102250.6331069149</v>
       </c>
       <c r="I11" t="n">
-        <v>319.3399450604778</v>
+        <v>319.7665290597421</v>
       </c>
     </row>
     <row r="12">
@@ -795,25 +795,25 @@
         <v>800</v>
       </c>
       <c r="C12" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D12" t="n">
-        <v>14931.76171875</v>
+        <v>14227.22265625</v>
       </c>
       <c r="E12" t="n">
-        <v>21428.171875</v>
+        <v>21444.80078125</v>
       </c>
       <c r="F12" t="n">
-        <v>201632890778.4531</v>
+        <v>199209313744.3711</v>
       </c>
       <c r="G12" t="n">
-        <v>20110.1520231545</v>
+        <v>20113.10200756849</v>
       </c>
       <c r="H12" t="n">
-        <v>103094.8214974809</v>
+        <v>103851.1754513517</v>
       </c>
       <c r="I12" t="n">
-        <v>321.0838231637977</v>
+        <v>322.2594846569324</v>
       </c>
     </row>
     <row r="13">
@@ -826,25 +826,25 @@
         <v>775</v>
       </c>
       <c r="C13" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D13" t="n">
-        <v>17671.6328125</v>
+        <v>16971.20703125</v>
       </c>
       <c r="E13" t="n">
-        <v>24017.8671875</v>
+        <v>24061.49609375</v>
       </c>
       <c r="F13" t="n">
-        <v>227932347971.168</v>
+        <v>225189781031.6055</v>
       </c>
       <c r="G13" t="n">
-        <v>22733.16695008448</v>
+        <v>22736.21123338989</v>
       </c>
       <c r="H13" t="n">
-        <v>105363.2186831624</v>
+        <v>106679.7179003661</v>
       </c>
       <c r="I13" t="n">
-        <v>324.5970096645415</v>
+        <v>326.6186122993699</v>
       </c>
     </row>
     <row r="14">
@@ -857,25 +857,25 @@
         <v>750</v>
       </c>
       <c r="C14" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D14" t="n">
-        <v>20502.62890625</v>
+        <v>19797.12890625</v>
       </c>
       <c r="E14" t="n">
-        <v>26709.1796875</v>
+        <v>26747.9296875</v>
       </c>
       <c r="F14" t="n">
-        <v>254948868587.6484</v>
+        <v>251878898091.3867</v>
       </c>
       <c r="G14" t="n">
-        <v>25427.69924903916</v>
+        <v>25430.86904745248</v>
       </c>
       <c r="H14" t="n">
-        <v>108630.7976827274</v>
+        <v>110585.1471466864</v>
       </c>
       <c r="I14" t="n">
-        <v>329.5918653163749</v>
+        <v>332.5434515167701</v>
       </c>
     </row>
     <row r="15">
@@ -888,25 +888,25 @@
         <v>725</v>
       </c>
       <c r="C15" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D15" t="n">
-        <v>26421.2265625</v>
+        <v>25710.22265625</v>
       </c>
       <c r="E15" t="n">
         <v>32365.8828125</v>
       </c>
       <c r="F15" t="n">
-        <v>311301878224.5312</v>
+        <v>307549809113.6016</v>
       </c>
       <c r="G15" t="n">
-        <v>31048.14929756414</v>
+        <v>31051.66403538624</v>
       </c>
       <c r="H15" t="n">
-        <v>117349.6627435521</v>
+        <v>120749.3029137534</v>
       </c>
       <c r="I15" t="n">
-        <v>342.5633704054654</v>
+        <v>347.4900040486826</v>
       </c>
     </row>
     <row r="16">
@@ -919,25 +919,25 @@
         <v>700</v>
       </c>
       <c r="C16" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D16" t="n">
-        <v>31926.1953125</v>
+        <v>31469.72265625</v>
       </c>
       <c r="E16" t="n">
         <v>38350.328125</v>
       </c>
       <c r="F16" t="n">
-        <v>371069337126.7852</v>
+        <v>366593897988.8125</v>
       </c>
       <c r="G16" t="n">
-        <v>37009.14445029756</v>
+        <v>37013.0308016758</v>
       </c>
       <c r="H16" t="n">
-        <v>128424.704750733</v>
+        <v>133374.725734805</v>
       </c>
       <c r="I16" t="n">
-        <v>358.3639278034732</v>
+        <v>365.2050461518913</v>
       </c>
     </row>
     <row r="17">
@@ -950,25 +950,25 @@
         <v>650</v>
       </c>
       <c r="C17" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D17" t="n">
-        <v>37639.1796875</v>
+        <v>37117.0859375</v>
       </c>
       <c r="E17" t="n">
         <v>44689.9921875</v>
       </c>
       <c r="F17" t="n">
-        <v>434745270714.0078</v>
+        <v>429497314583.6523</v>
       </c>
       <c r="G17" t="n">
-        <v>43359.95705686945</v>
+        <v>43364.05330567436</v>
       </c>
       <c r="H17" t="n">
-        <v>142390.2501690685</v>
+        <v>148908.0236428283</v>
       </c>
       <c r="I17" t="n">
-        <v>377.3463265609836</v>
+        <v>385.8860241610576</v>
       </c>
     </row>
     <row r="18">
@@ -981,25 +981,25 @@
         <v>600</v>
       </c>
       <c r="C18" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D18" t="n">
-        <v>43742.5234375</v>
+        <v>43194.83203125</v>
       </c>
       <c r="E18" t="n">
-        <v>51450.26171875</v>
+        <v>51453.01171875</v>
       </c>
       <c r="F18" t="n">
-        <v>503014445019.2148</v>
+        <v>496935239204</v>
       </c>
       <c r="G18" t="n">
-        <v>50168.88326167911</v>
+        <v>50172.9009020689</v>
       </c>
       <c r="H18" t="n">
-        <v>161298.3398765762</v>
+        <v>169492.1050305835</v>
       </c>
       <c r="I18" t="n">
-        <v>401.6196457801539</v>
+        <v>411.6941887257864</v>
       </c>
     </row>
     <row r="19">
@@ -1012,25 +1012,25 @@
         <v>550</v>
       </c>
       <c r="C19" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D19" t="n">
-        <v>50245.98046875</v>
+        <v>49794.546875</v>
       </c>
       <c r="E19" t="n">
-        <v>58780.80859375</v>
+        <v>58785.05859375</v>
       </c>
       <c r="F19" t="n">
-        <v>576675784358.5039</v>
+        <v>569698475965.9414</v>
       </c>
       <c r="G19" t="n">
-        <v>57515.60495288333</v>
+        <v>57519.41686503104</v>
       </c>
       <c r="H19" t="n">
-        <v>189168.9907577027</v>
+        <v>199384.3246899957</v>
       </c>
       <c r="I19" t="n">
-        <v>434.9356167959836</v>
+        <v>446.5247190133999</v>
       </c>
     </row>
     <row r="20">
@@ -1043,25 +1043,25 @@
         <v>500</v>
       </c>
       <c r="C20" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D20" t="n">
-        <v>57320.828125</v>
+        <v>56983.375</v>
       </c>
       <c r="E20" t="n">
-        <v>66800.484375</v>
+        <v>66756.84375</v>
       </c>
       <c r="F20" t="n">
-        <v>656691741613.0039</v>
+        <v>648738657477.2188</v>
       </c>
       <c r="G20" t="n">
-        <v>65496.1137798598</v>
+        <v>65499.68246382237</v>
       </c>
       <c r="H20" t="n">
-        <v>231301.7860214092</v>
+        <v>244193.607674709</v>
       </c>
       <c r="I20" t="n">
-        <v>480.9384430687666</v>
+        <v>494.1594961899539</v>
       </c>
     </row>
     <row r="21">
@@ -1074,25 +1074,25 @@
         <v>450</v>
       </c>
       <c r="C21" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D21" t="n">
-        <v>65214.02734375</v>
+        <v>64909.421875</v>
       </c>
       <c r="E21" t="n">
-        <v>75588.890625</v>
+        <v>75491.3515625</v>
       </c>
       <c r="F21" t="n">
-        <v>744277001351.5781</v>
+        <v>735253276934.9453</v>
       </c>
       <c r="G21" t="n">
-        <v>74231.55808921905</v>
+        <v>74234.60220021645</v>
       </c>
       <c r="H21" t="n">
-        <v>294324.2188584534</v>
+        <v>310793.5513581467</v>
       </c>
       <c r="I21" t="n">
-        <v>542.5165609070874</v>
+        <v>557.4886109672077</v>
       </c>
     </row>
     <row r="22">
@@ -1105,25 +1105,25 @@
         <v>400</v>
       </c>
       <c r="C22" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D22" t="n">
-        <v>74065</v>
+        <v>73570</v>
       </c>
       <c r="E22" t="n">
-        <v>85314.6875</v>
+        <v>85183.5625</v>
       </c>
       <c r="F22" t="n">
-        <v>841055358257.5859</v>
+        <v>830846485381.6719</v>
       </c>
       <c r="G22" t="n">
-        <v>83883.88942473142</v>
+        <v>83886.13864989745</v>
       </c>
       <c r="H22" t="n">
-        <v>386642.5306040271</v>
+        <v>407808.8253914824</v>
       </c>
       <c r="I22" t="n">
-        <v>621.8058624715813</v>
+        <v>638.5991116431986</v>
       </c>
     </row>
     <row r="23">
@@ -1136,25 +1136,25 @@
         <v>350</v>
       </c>
       <c r="C23" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D23" t="n">
-        <v>83836.4375</v>
+        <v>83467.6875</v>
       </c>
       <c r="E23" t="n">
-        <v>96179.8125</v>
+        <v>96108.6875</v>
       </c>
       <c r="F23" t="n">
-        <v>949323544593</v>
+        <v>937788418727.625</v>
       </c>
       <c r="G23" t="n">
-        <v>94682.17574632539</v>
+        <v>94683.49532888229</v>
       </c>
       <c r="H23" t="n">
-        <v>516897.0087338662</v>
+        <v>543792.2484778526</v>
       </c>
       <c r="I23" t="n">
-        <v>718.9554984377448</v>
+        <v>737.4227067821091</v>
       </c>
     </row>
     <row r="24">
@@ -1167,25 +1167,25 @@
         <v>300</v>
       </c>
       <c r="C24" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D24" t="n">
-        <v>95370.125</v>
+        <v>95173.625</v>
       </c>
       <c r="E24" t="n">
         <v>108594.3125</v>
       </c>
       <c r="F24" t="n">
-        <v>1072548696688.875</v>
+        <v>1059507117999.188</v>
       </c>
       <c r="G24" t="n">
-        <v>106972.2169799613</v>
+        <v>106972.7832575529</v>
       </c>
       <c r="H24" t="n">
-        <v>686421.3064129201</v>
+        <v>718045.5007289799</v>
       </c>
       <c r="I24" t="n">
-        <v>828.5054655299023</v>
+        <v>847.37565502496</v>
       </c>
     </row>
     <row r="25">
@@ -1198,25 +1198,25 @@
         <v>250</v>
       </c>
       <c r="C25" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D25" t="n">
-        <v>102082.0625</v>
+        <v>101950.5625</v>
       </c>
       <c r="E25" t="n">
         <v>115556.1875</v>
       </c>
       <c r="F25" t="n">
-        <v>1141391854346</v>
+        <v>1127511967707.625</v>
       </c>
       <c r="G25" t="n">
-        <v>113838.390256026</v>
+        <v>113838.8702566292</v>
       </c>
       <c r="H25" t="n">
-        <v>775708.1545666415</v>
+        <v>807606.2457732505</v>
       </c>
       <c r="I25" t="n">
-        <v>880.7429560130705</v>
+        <v>898.669152565754</v>
       </c>
     </row>
     <row r="26">
@@ -1229,25 +1229,25 @@
         <v>200</v>
       </c>
       <c r="C26" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D26" t="n">
-        <v>109609.875</v>
+        <v>109531.375</v>
       </c>
       <c r="E26" t="n">
         <v>123144.6875</v>
       </c>
       <c r="F26" t="n">
-        <v>1216395987873.125</v>
+        <v>1201605377631.812</v>
       </c>
       <c r="G26" t="n">
-        <v>121319.0374945407</v>
+        <v>121319.6867098505</v>
       </c>
       <c r="H26" t="n">
-        <v>846740.6260925599</v>
+        <v>876553.8941034599</v>
       </c>
       <c r="I26" t="n">
-        <v>920.1851042548776</v>
+        <v>936.2445695989162</v>
       </c>
     </row>
     <row r="27">
@@ -1260,25 +1260,25 @@
         <v>150</v>
       </c>
       <c r="C27" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D27" t="n">
-        <v>118110.75</v>
+        <v>118047.75</v>
       </c>
       <c r="E27" t="n">
         <v>131516.5625</v>
       </c>
       <c r="F27" t="n">
-        <v>1299099068600.562</v>
+        <v>1283308347025.375</v>
       </c>
       <c r="G27" t="n">
-        <v>129567.5505213141</v>
+        <v>129568.7998002286</v>
       </c>
       <c r="H27" t="n">
-        <v>865795.0590049953</v>
+        <v>891515.1865617182</v>
       </c>
       <c r="I27" t="n">
-        <v>930.4810900845838</v>
+        <v>944.2008189795846</v>
       </c>
     </row>
     <row r="28">
@@ -1291,25 +1291,25 @@
         <v>100</v>
       </c>
       <c r="C28" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D28" t="n">
-        <v>127869.875</v>
+        <v>127832.875</v>
       </c>
       <c r="E28" t="n">
-        <v>140866.1875</v>
+        <v>140910.1875</v>
       </c>
       <c r="F28" t="n">
-        <v>1391879173863.688</v>
+        <v>1374969015143.625</v>
       </c>
       <c r="G28" t="n">
-        <v>138821.1103664469</v>
+        <v>138823.2886255346</v>
       </c>
       <c r="H28" t="n">
-        <v>791618.533078799</v>
+        <v>813139.4504046426</v>
       </c>
       <c r="I28" t="n">
-        <v>889.7294718501793</v>
+        <v>901.7424523691022</v>
       </c>
     </row>
     <row r="29">
@@ -1322,25 +1322,25 @@
         <v>1000</v>
       </c>
       <c r="C29" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D29" t="n">
-        <v>-2.138814926147461</v>
+        <v>-2.018579483032227</v>
       </c>
       <c r="E29" t="n">
-        <v>1.7308349609375</v>
+        <v>1.798852920532227</v>
       </c>
       <c r="F29" t="n">
-        <v>-2422.814295768738</v>
+        <v>-2545.117341995239</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0002416429364459035</v>
+        <v>-0.0002569669246813929</v>
       </c>
       <c r="H29" t="n">
-        <v>0.003718447210900799</v>
+        <v>0.003622592962962754</v>
       </c>
       <c r="I29" t="n">
-        <v>0.060979071909146</v>
+        <v>0.06018798021999704</v>
       </c>
     </row>
     <row r="30">
@@ -1353,25 +1353,25 @@
         <v>975</v>
       </c>
       <c r="C30" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D30" t="n">
-        <v>-2.400935173034668</v>
+        <v>-2.665791511535645</v>
       </c>
       <c r="E30" t="n">
-        <v>2.099066734313965</v>
+        <v>2.307659149169922</v>
       </c>
       <c r="F30" t="n">
-        <v>-11428.87547302246</v>
+        <v>-10187.47474384308</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.001139875653862042</v>
+        <v>-0.001028574994166067</v>
       </c>
       <c r="H30" t="n">
-        <v>0.008556248384394498</v>
+        <v>0.008391431594142275</v>
       </c>
       <c r="I30" t="n">
-        <v>0.09249999126699687</v>
+        <v>0.09160475748640065</v>
       </c>
     </row>
     <row r="31">
@@ -1384,25 +1384,25 @@
         <v>950</v>
       </c>
       <c r="C31" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D31" t="n">
-        <v>-4.727029800415039</v>
+        <v>-4.483035087585449</v>
       </c>
       <c r="E31" t="n">
         <v>2.412403106689453</v>
       </c>
       <c r="F31" t="n">
-        <v>-23667.27976608276</v>
+        <v>-21250.07687282562</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.002360490851631011</v>
+        <v>-0.002145506933276555</v>
       </c>
       <c r="H31" t="n">
-        <v>0.01652364976495156</v>
+        <v>0.01629225734534536</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1285443494088774</v>
+        <v>0.1276411271704593</v>
       </c>
     </row>
     <row r="32">
@@ -1415,25 +1415,25 @@
         <v>925</v>
       </c>
       <c r="C32" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D32" t="n">
-        <v>-6.604527473449707</v>
+        <v>-6.002691268920898</v>
       </c>
       <c r="E32" t="n">
-        <v>2.899991035461426</v>
+        <v>2.613036155700684</v>
       </c>
       <c r="F32" t="n">
-        <v>-34448.7924823761</v>
+        <v>-30916.20142173767</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.003435800831699997</v>
+        <v>-0.003121443978667936</v>
       </c>
       <c r="H32" t="n">
-        <v>0.02449627987137436</v>
+        <v>0.02425014423273291</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1565128744588584</v>
+        <v>0.1557245781266814</v>
       </c>
     </row>
     <row r="33">
@@ -1446,25 +1446,25 @@
         <v>900</v>
       </c>
       <c r="C33" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D33" t="n">
-        <v>-7.907404899597168</v>
+        <v>-7.213781356811523</v>
       </c>
       <c r="E33" t="n">
-        <v>3.30113410949707</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="F33" t="n">
-        <v>-42482.3123884201</v>
+        <v>-37831.50194644928</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.004237035719360724</v>
+        <v>-0.003819644992727925</v>
       </c>
       <c r="H33" t="n">
-        <v>0.03083903847651879</v>
+        <v>0.03058255758319868</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1756104737096247</v>
+        <v>0.1748786939086597</v>
       </c>
     </row>
     <row r="34">
@@ -1477,25 +1477,25 @@
         <v>875</v>
       </c>
       <c r="C34" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D34" t="n">
-        <v>-8.800127029418945</v>
+        <v>-8.089030265808105</v>
       </c>
       <c r="E34" t="n">
-        <v>3.340728759765625</v>
+        <v>4.389358520507812</v>
       </c>
       <c r="F34" t="n">
-        <v>-47918.9500875473</v>
+        <v>-42149.72807216644</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.004779266752215353</v>
+        <v>-0.004255633255153008</v>
       </c>
       <c r="H34" t="n">
-        <v>0.03531862348755055</v>
+        <v>0.03500458133462445</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1879324971566933</v>
+        <v>0.187095113069862</v>
       </c>
     </row>
     <row r="35">
@@ -1508,25 +1508,25 @@
         <v>850</v>
       </c>
       <c r="C35" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D35" t="n">
-        <v>-9.277047157287598</v>
+        <v>-9.663198471069336</v>
       </c>
       <c r="E35" t="n">
-        <v>3.411510467529297</v>
+        <v>5.186410903930664</v>
       </c>
       <c r="F35" t="n">
-        <v>-51821.69149208069</v>
+        <v>-44967.81840610504</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.005168512388922798</v>
+        <v>-0.004540160807041402</v>
       </c>
       <c r="H35" t="n">
-        <v>0.03841090067414073</v>
+        <v>0.03799295427840122</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1959869910839511</v>
+        <v>0.1949178141638194</v>
       </c>
     </row>
     <row r="36">
@@ -1539,25 +1539,25 @@
         <v>825</v>
       </c>
       <c r="C36" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D36" t="n">
-        <v>-11.21321201324463</v>
+        <v>-10.84944725036621</v>
       </c>
       <c r="E36" t="n">
-        <v>3.772537231445312</v>
+        <v>5.845376968383789</v>
       </c>
       <c r="F36" t="n">
-        <v>-55127.48630332947</v>
+        <v>-47130.8146314621</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.00549822068182539</v>
+        <v>-0.004758547000462133</v>
       </c>
       <c r="H36" t="n">
-        <v>0.04066114822639713</v>
+        <v>0.04013955172505033</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2016460964819233</v>
+        <v>0.2003485755503401</v>
       </c>
     </row>
     <row r="37">
@@ -1570,25 +1570,25 @@
         <v>800</v>
       </c>
       <c r="C37" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D37" t="n">
-        <v>-12.87025260925293</v>
+        <v>-11.63267517089844</v>
       </c>
       <c r="E37" t="n">
-        <v>4.08746337890625</v>
+        <v>6.301895141601562</v>
       </c>
       <c r="F37" t="n">
-        <v>-57937.18080806732</v>
+        <v>-48777.04995441437</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.005778449683208786</v>
+        <v>-0.004924758601499451</v>
       </c>
       <c r="H37" t="n">
-        <v>0.04220286075598235</v>
+        <v>0.0416425576762125</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2054333486948562</v>
+        <v>0.2040650819621341</v>
       </c>
     </row>
     <row r="38">
@@ -1601,25 +1601,25 @@
         <v>775</v>
       </c>
       <c r="C38" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D38" t="n">
-        <v>-13.91684150695801</v>
+        <v>-12.10081577301025</v>
       </c>
       <c r="E38" t="n">
-        <v>4.463313102722168</v>
+        <v>6.637953758239746</v>
       </c>
       <c r="F38" t="n">
-        <v>-59398.15040111542</v>
+        <v>-49135.34728908539</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.005924161627842294</v>
+        <v>-0.004960933972549249</v>
       </c>
       <c r="H38" t="n">
-        <v>0.04342311519861047</v>
+        <v>0.04284451436138358</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2083821374269169</v>
+        <v>0.2069891648405384</v>
       </c>
     </row>
     <row r="39">
@@ -1632,25 +1632,25 @@
         <v>750</v>
       </c>
       <c r="C39" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D39" t="n">
-        <v>-14.50279140472412</v>
+        <v>-12.29857349395752</v>
       </c>
       <c r="E39" t="n">
-        <v>4.735078811645508</v>
+        <v>6.95191478729248</v>
       </c>
       <c r="F39" t="n">
-        <v>-60723.82324504852</v>
+        <v>-49356.79205036163</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.006056379552812455</v>
+        <v>-0.004983292069110488</v>
       </c>
       <c r="H39" t="n">
-        <v>0.04459916147186013</v>
+        <v>0.0439999258187638</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2111851355371872</v>
+        <v>0.2097615928113719</v>
       </c>
     </row>
     <row r="40">
@@ -1663,25 +1663,25 @@
         <v>725</v>
       </c>
       <c r="C40" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D40" t="n">
-        <v>-14.14280891418457</v>
+        <v>-13.4630069732666</v>
       </c>
       <c r="E40" t="n">
-        <v>6.10694408416748</v>
+        <v>7.426641464233398</v>
       </c>
       <c r="F40" t="n">
-        <v>-62648.70530414581</v>
+        <v>-48921.56094264984</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.006248360487498465</v>
+        <v>-0.004939349105291446</v>
       </c>
       <c r="H40" t="n">
-        <v>0.04701351997328641</v>
+        <v>0.04641202569741818</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2168260131379222</v>
+        <v>0.2154345044263295</v>
       </c>
     </row>
     <row r="41">
@@ -1694,25 +1694,25 @@
         <v>700</v>
       </c>
       <c r="C41" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D41" t="n">
-        <v>-14.72065544128418</v>
+        <v>-14.41956996917725</v>
       </c>
       <c r="E41" t="n">
-        <v>5.051517486572266</v>
+        <v>7.039414405822754</v>
       </c>
       <c r="F41" t="n">
-        <v>-65569.61175251007</v>
+        <v>-49406.89451408386</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.006539681375153486</v>
+        <v>-0.004988350647671554</v>
       </c>
       <c r="H41" t="n">
-        <v>0.04905054993134285</v>
+        <v>0.04848868350143795</v>
       </c>
       <c r="I41" t="n">
-        <v>0.2214735874350322</v>
+        <v>0.2202014611700793</v>
       </c>
     </row>
     <row r="42">
@@ -1725,25 +1725,25 @@
         <v>650</v>
       </c>
       <c r="C42" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D42" t="n">
-        <v>-15.0778169631958</v>
+        <v>-14.66117763519287</v>
       </c>
       <c r="E42" t="n">
-        <v>4.582921981811523</v>
+        <v>5.498002052307129</v>
       </c>
       <c r="F42" t="n">
-        <v>-67779.94095611572</v>
+        <v>-49743.17499542236</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.006760131799358101</v>
+        <v>-0.005022303094458242</v>
       </c>
       <c r="H42" t="n">
-        <v>0.04832009215640842</v>
+        <v>0.04790965919091781</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2198183162441393</v>
+        <v>0.218882752154933</v>
       </c>
     </row>
     <row r="43">
@@ -1756,25 +1756,25 @@
         <v>600</v>
       </c>
       <c r="C43" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D43" t="n">
-        <v>-14.58753776550293</v>
+        <v>-14.94180870056152</v>
       </c>
       <c r="E43" t="n">
-        <v>3.555633544921875</v>
+        <v>6.040891647338867</v>
       </c>
       <c r="F43" t="n">
-        <v>-70852.97952270508</v>
+        <v>-51427.74940872192</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.007066625806900938</v>
+        <v>-0.005192385588982109</v>
       </c>
       <c r="H43" t="n">
-        <v>0.04741564897971055</v>
+        <v>0.04690278074480758</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2177513466771458</v>
+        <v>0.2165704983251587</v>
       </c>
     </row>
     <row r="44">
@@ -1787,25 +1787,25 @@
         <v>550</v>
       </c>
       <c r="C44" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D44" t="n">
-        <v>-14.42328262329102</v>
+        <v>-15.25595188140869</v>
       </c>
       <c r="E44" t="n">
-        <v>2.957959175109863</v>
+        <v>6.178739547729492</v>
       </c>
       <c r="F44" t="n">
-        <v>-71383.06396961212</v>
+        <v>-51414.62700843811</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.007119494556494621</v>
+        <v>-0.005191060690208411</v>
       </c>
       <c r="H44" t="n">
-        <v>0.04685177605657885</v>
+        <v>0.04604575138372741</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2164527109014319</v>
+        <v>0.2145827378512247</v>
       </c>
     </row>
     <row r="45">
@@ -1818,25 +1818,25 @@
         <v>500</v>
       </c>
       <c r="C45" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D45" t="n">
-        <v>-14.67950439453125</v>
+        <v>-14.8433780670166</v>
       </c>
       <c r="E45" t="n">
-        <v>2.667131423950195</v>
+        <v>5.498003005981445</v>
       </c>
       <c r="F45" t="n">
-        <v>-72032.88622665405</v>
+        <v>-51868.24850749969</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.007184305532157776</v>
+        <v>-0.005236860433764368</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0460781127435935</v>
+        <v>0.04495171849315378</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2146581299266196</v>
+        <v>0.2120182032117851</v>
       </c>
     </row>
     <row r="46">
@@ -1849,25 +1849,25 @@
         <v>450</v>
       </c>
       <c r="C46" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D46" t="n">
-        <v>-14.51239013671875</v>
+        <v>-14.42695903778076</v>
       </c>
       <c r="E46" t="n">
-        <v>2.369221687316895</v>
+        <v>3.790817260742188</v>
       </c>
       <c r="F46" t="n">
-        <v>-73099.54794216156</v>
+        <v>-52945.61805725098</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.007290690602437312</v>
+        <v>-0.005345636691494003</v>
       </c>
       <c r="H46" t="n">
-        <v>0.04292757610627798</v>
+        <v>0.04164679652687933</v>
       </c>
       <c r="I46" t="n">
-        <v>0.207189710425682</v>
+        <v>0.2040754677242694</v>
       </c>
     </row>
     <row r="47">
@@ -1880,25 +1880,25 @@
         <v>400</v>
       </c>
       <c r="C47" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D47" t="n">
         <v>-13.51175689697266</v>
       </c>
       <c r="E47" t="n">
-        <v>1.987301826477051</v>
+        <v>2.974142074584961</v>
       </c>
       <c r="F47" t="n">
-        <v>-71394.13938236237</v>
+        <v>-52356.18314743042</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.007120599179025518</v>
+        <v>-0.005286124592158797</v>
       </c>
       <c r="H47" t="n">
-        <v>0.03697289233558221</v>
+        <v>0.03573288526472417</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1922833646875938</v>
+        <v>0.18903143988428</v>
       </c>
     </row>
     <row r="48">
@@ -1911,25 +1911,25 @@
         <v>350</v>
       </c>
       <c r="C48" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D48" t="n">
         <v>-11.9915885925293</v>
       </c>
       <c r="E48" t="n">
-        <v>1.664351463317871</v>
+        <v>2.847209930419922</v>
       </c>
       <c r="F48" t="n">
-        <v>-62053.81642627716</v>
+        <v>-45868.96747303009</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.006189028372957861</v>
+        <v>-0.004631145022419724</v>
       </c>
       <c r="H48" t="n">
-        <v>0.02904300422453121</v>
+        <v>0.02806401425373653</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1704200816351501</v>
+        <v>0.1675231752735619</v>
       </c>
     </row>
     <row r="49">
@@ -1942,25 +1942,25 @@
         <v>300</v>
       </c>
       <c r="C49" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D49" t="n">
-        <v>-9.580441474914551</v>
+        <v>-10.08780384063721</v>
       </c>
       <c r="E49" t="n">
-        <v>1.486281394958496</v>
+        <v>2.621424674987793</v>
       </c>
       <c r="F49" t="n">
-        <v>-43618.08973026276</v>
+        <v>-32174.1876077652</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.004350314137979509</v>
+        <v>-0.003248456134917587</v>
       </c>
       <c r="H49" t="n">
-        <v>0.02057371278655632</v>
+        <v>0.0198978685735314</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1434353958636303</v>
+        <v>0.1410598049535423</v>
       </c>
     </row>
     <row r="50">
@@ -1973,25 +1973,25 @@
         <v>250</v>
       </c>
       <c r="C50" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D50" t="n">
-        <v>-8.87787914276123</v>
+        <v>-9.601442337036133</v>
       </c>
       <c r="E50" t="n">
-        <v>1.505794525146484</v>
+        <v>2.766477584838867</v>
       </c>
       <c r="F50" t="n">
-        <v>-33490.62929344177</v>
+        <v>-24422.53395557404</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.003340237021063417</v>
+        <v>-0.002465813005922479</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0160246975916697</v>
+        <v>0.01550333379751017</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1265886945649954</v>
+        <v>0.1245123841130278</v>
       </c>
     </row>
     <row r="51">
@@ -2004,25 +2004,25 @@
         <v>200</v>
       </c>
       <c r="C51" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D51" t="n">
-        <v>-7.655767440795898</v>
+        <v>-8.764391899108887</v>
       </c>
       <c r="E51" t="n">
-        <v>1.579972267150879</v>
+        <v>3.319348335266113</v>
       </c>
       <c r="F51" t="n">
-        <v>-24104.18044757843</v>
+        <v>-17577.10592746735</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.002404065781742746</v>
+        <v>-0.001774666645208374</v>
       </c>
       <c r="H51" t="n">
-        <v>0.01105741416900901</v>
+        <v>0.01069777299772647</v>
       </c>
       <c r="I51" t="n">
-        <v>0.105154239900296</v>
+        <v>0.1034300391459197</v>
       </c>
     </row>
     <row r="52">
@@ -2035,25 +2035,25 @@
         <v>150</v>
       </c>
       <c r="C52" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D52" t="n">
-        <v>-5.896099090576172</v>
+        <v>-7.643311500549316</v>
       </c>
       <c r="E52" t="n">
-        <v>1.70118522644043</v>
+        <v>3.166014671325684</v>
       </c>
       <c r="F52" t="n">
-        <v>-15835.83107471466</v>
+        <v>-12195.98041915894</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.001579409832870084</v>
+        <v>-0.001231363100661162</v>
       </c>
       <c r="H52" t="n">
-        <v>0.006414038617623939</v>
+        <v>0.006217648357252597</v>
       </c>
       <c r="I52" t="n">
-        <v>0.08008769329693508</v>
+        <v>0.07885206628397633</v>
       </c>
     </row>
     <row r="53">
@@ -2066,25 +2066,25 @@
         <v>100</v>
       </c>
       <c r="C53" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D53" t="n">
-        <v>-3.676130294799805</v>
+        <v>-6.201698303222656</v>
       </c>
       <c r="E53" t="n">
-        <v>1.266777038574219</v>
+        <v>2.209678649902344</v>
       </c>
       <c r="F53" t="n">
-        <v>-8666.518324315548</v>
+        <v>-7296.581416249275</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.0008643679130947845</v>
+        <v>-0.0007366969122732421</v>
       </c>
       <c r="H53" t="n">
-        <v>0.003069765605709968</v>
+        <v>0.003006586844945881</v>
       </c>
       <c r="I53" t="n">
-        <v>0.05540546548590642</v>
+        <v>0.05483235217411233</v>
       </c>
     </row>
     <row r="54">
@@ -2097,25 +2097,25 @@
         <v>1000</v>
       </c>
       <c r="C54" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D54" t="n">
-        <v>5.437365531921387</v>
+        <v>5.067600250244141</v>
       </c>
       <c r="E54" t="n">
-        <v>108.203727722168</v>
+        <v>116.6183471679688</v>
       </c>
       <c r="F54" t="n">
-        <v>799480648.9655766</v>
+        <v>788589479.3050032</v>
       </c>
       <c r="G54" t="n">
-        <v>79.73737483104152</v>
+        <v>79.61967410675287</v>
       </c>
       <c r="H54" t="n">
-        <v>141.5479151988288</v>
+        <v>140.606027165696</v>
       </c>
       <c r="I54" t="n">
-        <v>11.89739110892925</v>
+        <v>11.85774123371294</v>
       </c>
     </row>
     <row r="55">
@@ -2128,25 +2128,25 @@
         <v>975</v>
       </c>
       <c r="C55" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D55" t="n">
-        <v>4.126392364501953</v>
+        <v>5.196361541748047</v>
       </c>
       <c r="E55" t="n">
-        <v>108.0694427490234</v>
+        <v>116.6277618408203</v>
       </c>
       <c r="F55" t="n">
-        <v>845822823.3023</v>
+        <v>835021803.2158451</v>
       </c>
       <c r="G55" t="n">
-        <v>84.35937954166702</v>
+        <v>84.30769822426825</v>
       </c>
       <c r="H55" t="n">
-        <v>165.8345788801995</v>
+        <v>163.5782981486893</v>
       </c>
       <c r="I55" t="n">
-        <v>12.87767754217349</v>
+        <v>12.78977318597516</v>
       </c>
     </row>
     <row r="56">
@@ -2159,25 +2159,25 @@
         <v>950</v>
       </c>
       <c r="C56" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D56" t="n">
-        <v>0.02105144038796425</v>
+        <v>1.62249755859375</v>
       </c>
       <c r="E56" t="n">
-        <v>108.5846328735352</v>
+        <v>117.5825347900391</v>
       </c>
       <c r="F56" t="n">
-        <v>846053103.6325303</v>
+        <v>835802388.3034761</v>
       </c>
       <c r="G56" t="n">
-        <v>84.38234688807047</v>
+        <v>84.38650973763586</v>
       </c>
       <c r="H56" t="n">
-        <v>184.7366466254045</v>
+        <v>179.4135952790548</v>
       </c>
       <c r="I56" t="n">
-        <v>13.59178599836697</v>
+        <v>13.39453602328408</v>
       </c>
     </row>
     <row r="57">
@@ -2190,25 +2190,25 @@
         <v>925</v>
       </c>
       <c r="C57" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D57" t="n">
-        <v>0.4477879405021667</v>
+        <v>0.09112149477005005</v>
       </c>
       <c r="E57" t="n">
-        <v>109.2074737548828</v>
+        <v>117.4900207519531</v>
       </c>
       <c r="F57" t="n">
-        <v>806131517.6582989</v>
+        <v>797110613.5747745</v>
       </c>
       <c r="G57" t="n">
-        <v>80.40070897251194</v>
+        <v>80.48000758999579</v>
       </c>
       <c r="H57" t="n">
-        <v>211.5394880794512</v>
+        <v>204.369187329616</v>
       </c>
       <c r="I57" t="n">
-        <v>14.54439713702329</v>
+        <v>14.29577515665436</v>
       </c>
     </row>
     <row r="58">
@@ -2221,25 +2221,25 @@
         <v>900</v>
       </c>
       <c r="C58" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.9287099838256836</v>
+        <v>-0.2024116516113281</v>
       </c>
       <c r="E58" t="n">
-        <v>110.0415496826172</v>
+        <v>117.3299407958984</v>
       </c>
       <c r="F58" t="n">
-        <v>767206354.0854805</v>
+        <v>758518382.7094388</v>
       </c>
       <c r="G58" t="n">
-        <v>76.5184507062467</v>
+        <v>76.58355585536411</v>
       </c>
       <c r="H58" t="n">
-        <v>262.6125286123836</v>
+        <v>256.7416559077095</v>
       </c>
       <c r="I58" t="n">
-        <v>16.20532408230035</v>
+        <v>16.02315998508751</v>
       </c>
     </row>
     <row r="59">
@@ -2252,25 +2252,25 @@
         <v>875</v>
       </c>
       <c r="C59" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D59" t="n">
         <v>-0.9581308364868164</v>
       </c>
       <c r="E59" t="n">
-        <v>110.1420669555664</v>
+        <v>114.7705993652344</v>
       </c>
       <c r="F59" t="n">
-        <v>726642248.4071285</v>
+        <v>717247450.6439204</v>
       </c>
       <c r="G59" t="n">
-        <v>72.47273014584832</v>
+        <v>72.41664994630355</v>
       </c>
       <c r="H59" t="n">
-        <v>336.8494977824636</v>
+        <v>336.570999226416</v>
       </c>
       <c r="I59" t="n">
-        <v>18.35346010381867</v>
+        <v>18.34587144908674</v>
       </c>
     </row>
     <row r="60">
@@ -2283,25 +2283,25 @@
         <v>850</v>
       </c>
       <c r="C60" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D60" t="n">
         <v>-3.572824478149414</v>
       </c>
       <c r="E60" t="n">
-        <v>122.3688888549805</v>
+        <v>115.5573806762695</v>
       </c>
       <c r="F60" t="n">
-        <v>684961951.1587551</v>
+        <v>675139288.3842309</v>
       </c>
       <c r="G60" t="n">
-        <v>68.31568458250334</v>
+        <v>68.16521336956298</v>
       </c>
       <c r="H60" t="n">
-        <v>416.3709013661519</v>
+        <v>419.277882977458</v>
       </c>
       <c r="I60" t="n">
-        <v>20.40516849639208</v>
+        <v>20.47627610131925</v>
       </c>
     </row>
     <row r="61">
@@ -2314,25 +2314,25 @@
         <v>825</v>
       </c>
       <c r="C61" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D61" t="n">
-        <v>-4.339694976806641</v>
+        <v>-5.618928909301758</v>
       </c>
       <c r="E61" t="n">
-        <v>115.7575988769531</v>
+        <v>116.4183731079102</v>
       </c>
       <c r="F61" t="n">
-        <v>646965462.1959532</v>
+        <v>637129889.2165781</v>
       </c>
       <c r="G61" t="n">
-        <v>64.52604904021635</v>
+        <v>64.3276070431514</v>
       </c>
       <c r="H61" t="n">
-        <v>476.3767486871807</v>
+        <v>479.7062667121182</v>
       </c>
       <c r="I61" t="n">
-        <v>21.82605664537643</v>
+        <v>21.90219775986233</v>
       </c>
     </row>
     <row r="62">
@@ -2345,25 +2345,25 @@
         <v>800</v>
       </c>
       <c r="C62" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D62" t="n">
-        <v>-5.542159080505371</v>
+        <v>-3.283346176147461</v>
       </c>
       <c r="E62" t="n">
-        <v>115.3020858764648</v>
+        <v>116.4541397094727</v>
       </c>
       <c r="F62" t="n">
-        <v>614790993.5980947</v>
+        <v>605409706.1707394</v>
       </c>
       <c r="G62" t="n">
-        <v>61.31708123605928</v>
+        <v>61.12498932760446</v>
       </c>
       <c r="H62" t="n">
-        <v>513.1041442007436</v>
+        <v>514.3013910427478</v>
       </c>
       <c r="I62" t="n">
-        <v>22.65180222853677</v>
+        <v>22.67821401792363</v>
       </c>
     </row>
     <row r="63">
@@ -2376,25 +2376,25 @@
         <v>775</v>
       </c>
       <c r="C63" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D63" t="n">
-        <v>-3.032523155212402</v>
+        <v>-5.978819847106934</v>
       </c>
       <c r="E63" t="n">
-        <v>112.8669815063477</v>
+        <v>120.837776184082</v>
       </c>
       <c r="F63" t="n">
-        <v>586976379.7173281</v>
+        <v>577915154.0804738</v>
       </c>
       <c r="G63" t="n">
-        <v>58.54294993511908</v>
+        <v>58.34901103397174</v>
       </c>
       <c r="H63" t="n">
-        <v>536.4232597026821</v>
+        <v>535.9126250883144</v>
       </c>
       <c r="I63" t="n">
-        <v>23.16081301903459</v>
+        <v>23.14978671798758</v>
       </c>
     </row>
     <row r="64">
@@ -2407,25 +2407,25 @@
         <v>750</v>
       </c>
       <c r="C64" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D64" t="n">
-        <v>-5.241782188415527</v>
+        <v>-5.913242340087891</v>
       </c>
       <c r="E64" t="n">
-        <v>114.5705184936523</v>
+        <v>115.3855743408203</v>
       </c>
       <c r="F64" t="n">
-        <v>561572819.367018</v>
+        <v>552534237.0440724</v>
       </c>
       <c r="G64" t="n">
-        <v>56.00928859345133</v>
+        <v>55.78643519952108</v>
       </c>
       <c r="H64" t="n">
-        <v>545.0898531239231</v>
+        <v>543.2771864136471</v>
       </c>
       <c r="I64" t="n">
-        <v>23.34715942302025</v>
+        <v>23.30830724041639</v>
       </c>
     </row>
     <row r="65">
@@ -2438,25 +2438,25 @@
         <v>725</v>
       </c>
       <c r="C65" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D65" t="n">
         <v>-6.19677734375</v>
       </c>
       <c r="E65" t="n">
-        <v>114.904670715332</v>
+        <v>112.7630233764648</v>
       </c>
       <c r="F65" t="n">
-        <v>519284117.4072941</v>
+        <v>509840291.6445113</v>
       </c>
       <c r="G65" t="n">
-        <v>51.7915628940942</v>
+        <v>51.47585522318095</v>
       </c>
       <c r="H65" t="n">
-        <v>545.8643188104913</v>
+        <v>540.5429482536663</v>
       </c>
       <c r="I65" t="n">
-        <v>23.36373940127075</v>
+        <v>23.24957952853484</v>
       </c>
     </row>
     <row r="66">
@@ -2469,7 +2469,7 @@
         <v>700</v>
       </c>
       <c r="C66" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D66" t="n">
         <v>-9.847058296203613</v>
@@ -2478,16 +2478,16 @@
         <v>119.0913238525391</v>
       </c>
       <c r="F66" t="n">
-        <v>494826096.3200818</v>
+        <v>485400263.5296825</v>
       </c>
       <c r="G66" t="n">
-        <v>49.35220629730875</v>
+        <v>49.00827592529642</v>
       </c>
       <c r="H66" t="n">
-        <v>608.5433735509779</v>
+        <v>596.7649932855552</v>
       </c>
       <c r="I66" t="n">
-        <v>24.66867190488734</v>
+        <v>24.42877388011022</v>
       </c>
     </row>
     <row r="67">
@@ -2500,25 +2500,25 @@
         <v>650</v>
       </c>
       <c r="C67" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D67" t="n">
-        <v>-5.791181564331055</v>
+        <v>-9.189784049987793</v>
       </c>
       <c r="E67" t="n">
-        <v>114.8564529418945</v>
+        <v>117.3552017211914</v>
       </c>
       <c r="F67" t="n">
-        <v>476936631.3311185</v>
+        <v>467880795.5822323</v>
       </c>
       <c r="G67" t="n">
-        <v>47.56797427468587</v>
+        <v>47.23942867954186</v>
       </c>
       <c r="H67" t="n">
-        <v>750.9843119148078</v>
+        <v>732.6056884215355</v>
       </c>
       <c r="I67" t="n">
-        <v>27.40409297741503</v>
+        <v>27.06668964652928</v>
       </c>
     </row>
     <row r="68">
@@ -2531,25 +2531,25 @@
         <v>600</v>
       </c>
       <c r="C68" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D68" t="n">
-        <v>-7.655652046203613</v>
+        <v>-6.82654857635498</v>
       </c>
       <c r="E68" t="n">
-        <v>114.9189147949219</v>
+        <v>132.5256805419922</v>
       </c>
       <c r="F68" t="n">
-        <v>434971300.7473565</v>
+        <v>426225859.3938842</v>
       </c>
       <c r="G68" t="n">
-        <v>43.38250049368125</v>
+        <v>43.03375192212842</v>
       </c>
       <c r="H68" t="n">
-        <v>809.973580038239</v>
+        <v>791.3816306882889</v>
       </c>
       <c r="I68" t="n">
-        <v>28.46003478631463</v>
+        <v>28.13150601528985</v>
       </c>
     </row>
     <row r="69">
@@ -2562,25 +2562,25 @@
         <v>550</v>
       </c>
       <c r="C69" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D69" t="n">
-        <v>-4.89570140838623</v>
+        <v>-5.642542839050293</v>
       </c>
       <c r="E69" t="n">
-        <v>118.9282073974609</v>
+        <v>128.0203857421875</v>
       </c>
       <c r="F69" t="n">
-        <v>384949060.2008683</v>
+        <v>376152582.7525846</v>
       </c>
       <c r="G69" t="n">
-        <v>38.39345898341495</v>
+        <v>37.97812022494792</v>
       </c>
       <c r="H69" t="n">
-        <v>749.8189669638443</v>
+        <v>731.8469821666702</v>
       </c>
       <c r="I69" t="n">
-        <v>27.38282247986581</v>
+        <v>27.05267051820707</v>
       </c>
     </row>
     <row r="70">
@@ -2593,25 +2593,25 @@
         <v>500</v>
       </c>
       <c r="C70" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D70" t="n">
         <v>-8.479220390319824</v>
       </c>
       <c r="E70" t="n">
-        <v>131.3380889892578</v>
+        <v>133.5879058837891</v>
       </c>
       <c r="F70" t="n">
-        <v>361184774.0162191</v>
+        <v>352205976.3473574</v>
       </c>
       <c r="G70" t="n">
-        <v>36.02329305438413</v>
+        <v>35.56035908561936</v>
       </c>
       <c r="H70" t="n">
-        <v>725.6675188043481</v>
+        <v>706.7285190077654</v>
       </c>
       <c r="I70" t="n">
-        <v>26.93821669681102</v>
+        <v>26.58436606368046</v>
       </c>
     </row>
     <row r="71">
@@ -2624,25 +2624,25 @@
         <v>450</v>
       </c>
       <c r="C71" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D71" t="n">
         <v>-10.94512271881104</v>
       </c>
       <c r="E71" t="n">
-        <v>139.7909698486328</v>
+        <v>133.7244262695312</v>
       </c>
       <c r="F71" t="n">
-        <v>373099676.9571382</v>
+        <v>363179030.1803893</v>
       </c>
       <c r="G71" t="n">
-        <v>37.21164337043614</v>
+        <v>36.66824981085693</v>
       </c>
       <c r="H71" t="n">
-        <v>764.8233707592289</v>
+        <v>745.7641346622869</v>
       </c>
       <c r="I71" t="n">
-        <v>27.65544016571114</v>
+        <v>27.30868240436157</v>
       </c>
     </row>
     <row r="72">
@@ -2655,25 +2655,25 @@
         <v>400</v>
       </c>
       <c r="C72" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D72" t="n">
-        <v>-8.509300231933594</v>
+        <v>-8.745258331298828</v>
       </c>
       <c r="E72" t="n">
-        <v>139.2088928222656</v>
+        <v>133.2915802001953</v>
       </c>
       <c r="F72" t="n">
-        <v>409373090.4784034</v>
+        <v>398037181.6062763</v>
       </c>
       <c r="G72" t="n">
-        <v>40.82942545695533</v>
+        <v>40.18769145866931</v>
       </c>
       <c r="H72" t="n">
-        <v>819.3016539773708</v>
+        <v>802.7754258543857</v>
       </c>
       <c r="I72" t="n">
-        <v>28.62344587881359</v>
+        <v>28.33329182877248</v>
       </c>
     </row>
     <row r="73">
@@ -2686,25 +2686,25 @@
         <v>350</v>
       </c>
       <c r="C73" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D73" t="n">
-        <v>-5.738934516906738</v>
+        <v>-5.27549934387207</v>
       </c>
       <c r="E73" t="n">
-        <v>129.5653686523438</v>
+        <v>134.7029724121094</v>
       </c>
       <c r="F73" t="n">
-        <v>466342569.2067576</v>
+        <v>455176111.9500782</v>
       </c>
       <c r="G73" t="n">
-        <v>46.51135995426869</v>
+        <v>45.95670452842477</v>
       </c>
       <c r="H73" t="n">
-        <v>867.4816007377142</v>
+        <v>857.248276339919</v>
       </c>
       <c r="I73" t="n">
-        <v>29.45304060258829</v>
+        <v>29.27880250863958</v>
       </c>
     </row>
     <row r="74">
@@ -2717,25 +2717,25 @@
         <v>300</v>
       </c>
       <c r="C74" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D74" t="n">
-        <v>-5.420136451721191</v>
+        <v>-3.193296432495117</v>
       </c>
       <c r="E74" t="n">
-        <v>133.7701568603516</v>
+        <v>149.8188629150391</v>
       </c>
       <c r="F74" t="n">
-        <v>552663292.5238219</v>
+        <v>542160537.4497203</v>
       </c>
       <c r="G74" t="n">
-        <v>55.12068386939426</v>
+        <v>54.73905807535306</v>
       </c>
       <c r="H74" t="n">
-        <v>903.9253678769517</v>
+        <v>900.8690202394084</v>
       </c>
       <c r="I74" t="n">
-        <v>30.06535161738428</v>
+        <v>30.01448017606516</v>
       </c>
     </row>
     <row r="75">
@@ -2748,25 +2748,25 @@
         <v>250</v>
       </c>
       <c r="C75" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D75" t="n">
-        <v>-4.314042091369629</v>
+        <v>-5.87335205078125</v>
       </c>
       <c r="E75" t="n">
-        <v>168.4070892333984</v>
+        <v>154.9700012207031</v>
       </c>
       <c r="F75" t="n">
-        <v>593370526.130264</v>
+        <v>582965196.7388428</v>
       </c>
       <c r="G75" t="n">
-        <v>59.18067950357418</v>
+        <v>58.85888690885515</v>
       </c>
       <c r="H75" t="n">
-        <v>886.4656914189896</v>
+        <v>884.0042290190599</v>
       </c>
       <c r="I75" t="n">
-        <v>29.77357370923064</v>
+        <v>29.73220861320363</v>
       </c>
     </row>
     <row r="76">
@@ -2779,25 +2779,25 @@
         <v>200</v>
       </c>
       <c r="C76" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D76" t="n">
-        <v>-4.440022468566895</v>
+        <v>-2.776803016662598</v>
       </c>
       <c r="E76" t="n">
-        <v>148.8643646240234</v>
+        <v>142.6777648925781</v>
       </c>
       <c r="F76" t="n">
-        <v>618388394.1481723</v>
+        <v>607928662.6627564</v>
       </c>
       <c r="G76" t="n">
-        <v>61.67587325491589</v>
+        <v>61.37931493078182</v>
       </c>
       <c r="H76" t="n">
-        <v>831.5248213876281</v>
+        <v>828.1461726687463</v>
       </c>
       <c r="I76" t="n">
-        <v>28.83617210011808</v>
+        <v>28.77752895348637</v>
       </c>
     </row>
     <row r="77">
@@ -2810,25 +2810,25 @@
         <v>150</v>
       </c>
       <c r="C77" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.075922966003418</v>
+        <v>-1.261675834655762</v>
       </c>
       <c r="E77" t="n">
-        <v>147.6380920410156</v>
+        <v>151.2321319580078</v>
       </c>
       <c r="F77" t="n">
-        <v>632354903.6394479</v>
+        <v>621660019.269586</v>
       </c>
       <c r="G77" t="n">
-        <v>63.06884355860989</v>
+        <v>62.76569677681254</v>
       </c>
       <c r="H77" t="n">
-        <v>795.9576664455182</v>
+        <v>794.2579538336554</v>
       </c>
       <c r="I77" t="n">
-        <v>28.21272171282874</v>
+        <v>28.18258245501386</v>
       </c>
     </row>
     <row r="78">
@@ -2841,25 +2841,25 @@
         <v>100</v>
       </c>
       <c r="C78" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D78" t="n">
-        <v>-19.89750671386719</v>
+        <v>-13.85577201843262</v>
       </c>
       <c r="E78" t="n">
-        <v>168.4141845703125</v>
+        <v>163.2067260742188</v>
       </c>
       <c r="F78" t="n">
-        <v>632863170.6179223</v>
+        <v>622995978.0552262</v>
       </c>
       <c r="G78" t="n">
-        <v>63.11953631099761</v>
+        <v>62.90058141061036</v>
       </c>
       <c r="H78" t="n">
-        <v>854.9545310584356</v>
+        <v>852.6120465842278</v>
       </c>
       <c r="I78" t="n">
-        <v>29.23960552159409</v>
+        <v>29.19952134169716</v>
       </c>
     </row>
     <row r="79">
@@ -2872,25 +2872,25 @@
         <v>1000</v>
       </c>
       <c r="C79" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D79" t="n">
-        <v>255.1848907470703</v>
+        <v>254.3196563720703</v>
       </c>
       <c r="E79" t="n">
-        <v>318.2398071289062</v>
+        <v>317.78955078125</v>
       </c>
       <c r="F79" t="n">
-        <v>2982892580.056778</v>
+        <v>2946632435.486938</v>
       </c>
       <c r="G79" t="n">
-        <v>297.5031653917632</v>
+        <v>297.5057623551161</v>
       </c>
       <c r="H79" t="n">
-        <v>10.29535471809472</v>
+        <v>10.47361501275375</v>
       </c>
       <c r="I79" t="n">
-        <v>3.208637517404345</v>
+        <v>3.236296496422068</v>
       </c>
     </row>
     <row r="80">
@@ -2903,25 +2903,25 @@
         <v>975</v>
       </c>
       <c r="C80" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D80" t="n">
-        <v>253.9454193115234</v>
+        <v>253.1016693115234</v>
       </c>
       <c r="E80" t="n">
-        <v>316.7802124023438</v>
+        <v>316.5765380859375</v>
       </c>
       <c r="F80" t="n">
-        <v>2964174687.582321</v>
+        <v>2928093826.634644</v>
       </c>
       <c r="G80" t="n">
-        <v>295.636308939122</v>
+        <v>295.63401788737</v>
       </c>
       <c r="H80" t="n">
-        <v>10.29164871898972</v>
+        <v>10.44498327302808</v>
       </c>
       <c r="I80" t="n">
-        <v>3.208059961875669</v>
+        <v>3.231869934423117</v>
       </c>
     </row>
     <row r="81">
@@ -2934,25 +2934,25 @@
         <v>950</v>
       </c>
       <c r="C81" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D81" t="n">
-        <v>252.6427001953125</v>
+        <v>251.9278564453125</v>
       </c>
       <c r="E81" t="n">
-        <v>315.1768798828125</v>
+        <v>314.1771240234375</v>
       </c>
       <c r="F81" t="n">
-        <v>2949466694.461182</v>
+        <v>2913503548.240021</v>
       </c>
       <c r="G81" t="n">
-        <v>294.1693856783398</v>
+        <v>294.160915289133</v>
       </c>
       <c r="H81" t="n">
-        <v>10.57754093144271</v>
+        <v>10.722842444887</v>
       </c>
       <c r="I81" t="n">
-        <v>3.252313166262239</v>
+        <v>3.274575154869255</v>
       </c>
     </row>
     <row r="82">
@@ -2965,25 +2965,25 @@
         <v>925</v>
       </c>
       <c r="C82" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D82" t="n">
-        <v>251.3966522216797</v>
+        <v>250.6466522216797</v>
       </c>
       <c r="E82" t="n">
-        <v>312.859130859375</v>
+        <v>311.7510986328125</v>
       </c>
       <c r="F82" t="n">
-        <v>2937569284.775055</v>
+        <v>2901670959.49234</v>
       </c>
       <c r="G82" t="n">
-        <v>292.982780077706</v>
+        <v>292.9662419075396</v>
       </c>
       <c r="H82" t="n">
-        <v>10.77418475424225</v>
+        <v>10.96182917689805</v>
       </c>
       <c r="I82" t="n">
-        <v>3.28240533058339</v>
+        <v>3.310865321467796</v>
       </c>
     </row>
     <row r="83">
@@ -2996,25 +2996,25 @@
         <v>900</v>
       </c>
       <c r="C83" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D83" t="n">
-        <v>250.0228271484375</v>
+        <v>249.2161865234375</v>
       </c>
       <c r="E83" t="n">
-        <v>310.3804931640625</v>
+        <v>309.3198547363281</v>
       </c>
       <c r="F83" t="n">
-        <v>2926298693.782501</v>
+        <v>2890517331.167633</v>
       </c>
       <c r="G83" t="n">
-        <v>291.8586911586017</v>
+        <v>291.8401195388983</v>
       </c>
       <c r="H83" t="n">
-        <v>10.51822467950567</v>
+        <v>10.74370414270511</v>
       </c>
       <c r="I83" t="n">
-        <v>3.243181259119766</v>
+        <v>3.277759012298664</v>
       </c>
     </row>
     <row r="84">
@@ -3027,25 +3027,25 @@
         <v>875</v>
       </c>
       <c r="C84" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D84" t="n">
-        <v>248.6092681884766</v>
+        <v>247.9276275634766</v>
       </c>
       <c r="E84" t="n">
-        <v>307.8746643066406</v>
+        <v>306.8099365234375</v>
       </c>
       <c r="F84" t="n">
-        <v>2915426337.656647</v>
+        <v>2879879374.901581</v>
       </c>
       <c r="G84" t="n">
-        <v>290.774320777872</v>
+        <v>290.7660618278929</v>
       </c>
       <c r="H84" t="n">
-        <v>10.06184956860948</v>
+        <v>10.30541099230571</v>
       </c>
       <c r="I84" t="n">
-        <v>3.172041861106104</v>
+        <v>3.210204197914162</v>
       </c>
     </row>
     <row r="85">
@@ -3058,25 +3058,25 @@
         <v>850</v>
       </c>
       <c r="C85" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D85" t="n">
         <v>247.3075866699219</v>
       </c>
       <c r="E85" t="n">
-        <v>305.3089599609375</v>
+        <v>304.2629699707031</v>
       </c>
       <c r="F85" t="n">
-        <v>2904454260.914337</v>
+        <v>2869131315.764175</v>
       </c>
       <c r="G85" t="n">
-        <v>289.6800046152406</v>
+        <v>289.6808876171564</v>
       </c>
       <c r="H85" t="n">
-        <v>9.398639052206656</v>
+        <v>9.655725942591474</v>
       </c>
       <c r="I85" t="n">
-        <v>3.065719989204275</v>
+        <v>3.107366399797661</v>
       </c>
     </row>
     <row r="86">
@@ -3089,25 +3089,25 @@
         <v>825</v>
       </c>
       <c r="C86" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D86" t="n">
         <v>247.0019073486328</v>
       </c>
       <c r="E86" t="n">
-        <v>302.8648681640625</v>
+        <v>302.1187133789062</v>
       </c>
       <c r="F86" t="n">
-        <v>2892697740.646317</v>
+        <v>2857589458.447571</v>
       </c>
       <c r="G86" t="n">
-        <v>288.5074508273095</v>
+        <v>288.5155678376628</v>
       </c>
       <c r="H86" t="n">
-        <v>8.455037033638115</v>
+        <v>8.730867258283723</v>
       </c>
       <c r="I86" t="n">
-        <v>2.907754637798402</v>
+        <v>2.954804098122873</v>
       </c>
     </row>
     <row r="87">
@@ -3120,25 +3120,25 @@
         <v>800</v>
       </c>
       <c r="C87" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D87" t="n">
         <v>246.7183990478516</v>
       </c>
       <c r="E87" t="n">
-        <v>301.2190551757812</v>
+        <v>300.1513977050781</v>
       </c>
       <c r="F87" t="n">
-        <v>2879884617.562988</v>
+        <v>2844960479.480789</v>
       </c>
       <c r="G87" t="n">
-        <v>287.2295152082643</v>
+        <v>287.2404871828671</v>
       </c>
       <c r="H87" t="n">
-        <v>7.488181342029197</v>
+        <v>7.793389339404394</v>
       </c>
       <c r="I87" t="n">
-        <v>2.736454154929184</v>
+        <v>2.791664259792784</v>
       </c>
     </row>
     <row r="88">
@@ -3151,25 +3151,25 @@
         <v>775</v>
       </c>
       <c r="C88" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D88" t="n">
-        <v>246.04736328125</v>
+        <v>245.77685546875</v>
       </c>
       <c r="E88" t="n">
-        <v>299.0550537109375</v>
+        <v>297.8041381835938</v>
       </c>
       <c r="F88" t="n">
-        <v>2866125498.536865</v>
+        <v>2831397659.48967</v>
       </c>
       <c r="G88" t="n">
-        <v>285.8572292967155</v>
+        <v>285.8711215801037</v>
       </c>
       <c r="H88" t="n">
-        <v>6.661261281562805</v>
+        <v>6.984014800767743</v>
       </c>
       <c r="I88" t="n">
-        <v>2.580941936883278</v>
+        <v>2.642728665748291</v>
       </c>
     </row>
     <row r="89">
@@ -3182,25 +3182,25 @@
         <v>750</v>
       </c>
       <c r="C89" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D89" t="n">
-        <v>246.3654022216797</v>
+        <v>244.6638641357422</v>
       </c>
       <c r="E89" t="n">
         <v>297.671630859375</v>
       </c>
       <c r="F89" t="n">
-        <v>2851552502.29895</v>
+        <v>2817037931.251205</v>
       </c>
       <c r="G89" t="n">
-        <v>284.4037701480342</v>
+        <v>284.4212964015895</v>
       </c>
       <c r="H89" t="n">
-        <v>5.974969541316645</v>
+        <v>6.28295059186824</v>
       </c>
       <c r="I89" t="n">
-        <v>2.444375081961982</v>
+        <v>2.506581455262972</v>
       </c>
     </row>
     <row r="90">
@@ -3213,25 +3213,25 @@
         <v>725</v>
       </c>
       <c r="C90" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D90" t="n">
-        <v>242.462158203125</v>
+        <v>241.5117797851562</v>
       </c>
       <c r="E90" t="n">
-        <v>294.1692504882812</v>
+        <v>294.9127807617188</v>
       </c>
       <c r="F90" t="n">
-        <v>2819645475.68222</v>
+        <v>2785567990.744934</v>
       </c>
       <c r="G90" t="n">
-        <v>281.2214760620246</v>
+        <v>281.2439443406974</v>
       </c>
       <c r="H90" t="n">
-        <v>4.945534566297511</v>
+        <v>5.183560536247198</v>
       </c>
       <c r="I90" t="n">
-        <v>2.223855788107114</v>
+        <v>2.276743405886398</v>
       </c>
     </row>
     <row r="91">
@@ -3244,25 +3244,25 @@
         <v>700</v>
       </c>
       <c r="C91" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D91" t="n">
-        <v>239.9819946289062</v>
+        <v>239.3909912109375</v>
       </c>
       <c r="E91" t="n">
-        <v>289.8150634765625</v>
+        <v>292.1351928710938</v>
       </c>
       <c r="F91" t="n">
-        <v>2783950845.061508</v>
+        <v>2750267628.544312</v>
       </c>
       <c r="G91" t="n">
-        <v>277.661419736782</v>
+        <v>277.6798550293093</v>
       </c>
       <c r="H91" t="n">
-        <v>4.40748699557196</v>
+        <v>4.577352300679132</v>
       </c>
       <c r="I91" t="n">
-        <v>2.099401580349019</v>
+        <v>2.139474772153</v>
       </c>
     </row>
     <row r="92">
@@ -3275,25 +3275,25 @@
         <v>650</v>
       </c>
       <c r="C92" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D92" t="n">
-        <v>238.6626434326172</v>
+        <v>238.0354156494141</v>
       </c>
       <c r="E92" t="n">
-        <v>286.2237548828125</v>
+        <v>288.7566223144531</v>
       </c>
       <c r="F92" t="n">
-        <v>2747194936.990646</v>
+        <v>2713834135.602066</v>
       </c>
       <c r="G92" t="n">
-        <v>273.9955153488576</v>
+        <v>274.0013595500276</v>
       </c>
       <c r="H92" t="n">
-        <v>4.273986207056101</v>
+        <v>4.409659398916618</v>
       </c>
       <c r="I92" t="n">
-        <v>2.067362137376057</v>
+        <v>2.099918902938068</v>
       </c>
     </row>
     <row r="93">
@@ -3306,25 +3306,25 @@
         <v>600</v>
       </c>
       <c r="C93" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D93" t="n">
-        <v>236.7375946044922</v>
+        <v>234.7569122314453</v>
       </c>
       <c r="E93" t="n">
-        <v>281.2777099609375</v>
+        <v>283.3309326171875</v>
       </c>
       <c r="F93" t="n">
-        <v>2709923650.035248</v>
+        <v>2676915473.054916</v>
       </c>
       <c r="G93" t="n">
-        <v>270.2782088921709</v>
+        <v>270.2738790831924</v>
       </c>
       <c r="H93" t="n">
-        <v>4.871282870012011</v>
+        <v>5.008298228264893</v>
       </c>
       <c r="I93" t="n">
-        <v>2.207098291878278</v>
+        <v>2.23792274850248</v>
       </c>
     </row>
     <row r="94">
@@ -3337,25 +3337,25 @@
         <v>550</v>
       </c>
       <c r="C94" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D94" t="n">
-        <v>233.0751647949219</v>
+        <v>231.8300323486328</v>
       </c>
       <c r="E94" t="n">
-        <v>278.5971069335938</v>
+        <v>279.7101440429688</v>
       </c>
       <c r="F94" t="n">
-        <v>2667786780.278778</v>
+        <v>2635290789.360687</v>
       </c>
       <c r="G94" t="n">
-        <v>266.0756264002401</v>
+        <v>266.0712567587726</v>
       </c>
       <c r="H94" t="n">
-        <v>5.68423344348288</v>
+        <v>5.856825407494704</v>
       </c>
       <c r="I94" t="n">
-        <v>2.384163048846047</v>
+        <v>2.420087892514382</v>
       </c>
     </row>
     <row r="95">
@@ -3368,25 +3368,25 @@
         <v>500</v>
       </c>
       <c r="C95" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D95" t="n">
-        <v>229.6830139160156</v>
+        <v>228.6268768310547</v>
       </c>
       <c r="E95" t="n">
-        <v>274.2037963867188</v>
+        <v>276.3261108398438</v>
       </c>
       <c r="F95" t="n">
-        <v>2618367403.070099</v>
+        <v>2586434360.782028</v>
       </c>
       <c r="G95" t="n">
-        <v>261.1467123489696</v>
+        <v>261.1384837209135</v>
       </c>
       <c r="H95" t="n">
-        <v>6.68986304673547</v>
+        <v>6.899376076590056</v>
       </c>
       <c r="I95" t="n">
-        <v>2.586476956544455</v>
+        <v>2.626666342836497</v>
       </c>
     </row>
     <row r="96">
@@ -3399,25 +3399,25 @@
         <v>450</v>
       </c>
       <c r="C96" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D96" t="n">
-        <v>225.9030609130859</v>
+        <v>225.0690765380859</v>
       </c>
       <c r="E96" t="n">
-        <v>267.074951171875</v>
+        <v>270.71875</v>
       </c>
       <c r="F96" t="n">
-        <v>2559050547.163849</v>
+        <v>2527744478.127563</v>
       </c>
       <c r="G96" t="n">
-        <v>255.2306587467777</v>
+        <v>255.2128792677195</v>
       </c>
       <c r="H96" t="n">
-        <v>7.493912165690227</v>
+        <v>7.705515311810009</v>
       </c>
       <c r="I96" t="n">
-        <v>2.737501080491152</v>
+        <v>2.775880997415057</v>
       </c>
     </row>
     <row r="97">
@@ -3430,25 +3430,25 @@
         <v>400</v>
       </c>
       <c r="C97" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D97" t="n">
         <v>221.6041412353516</v>
       </c>
       <c r="E97" t="n">
-        <v>261.0946044921875</v>
+        <v>263.681640625</v>
       </c>
       <c r="F97" t="n">
-        <v>2488197158.048065</v>
+        <v>2457732863.997284</v>
       </c>
       <c r="G97" t="n">
-        <v>248.1639920885112</v>
+        <v>248.1441799672258</v>
       </c>
       <c r="H97" t="n">
-        <v>7.876223627061692</v>
+        <v>8.092607266499595</v>
       </c>
       <c r="I97" t="n">
-        <v>2.80646105033754</v>
+        <v>2.844750826785994</v>
       </c>
     </row>
     <row r="98">
@@ -3461,25 +3461,25 @@
         <v>350</v>
       </c>
       <c r="C98" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D98" t="n">
-        <v>216.825927734375</v>
+        <v>216.7074432373047</v>
       </c>
       <c r="E98" t="n">
-        <v>253.9608917236328</v>
+        <v>255.7990875244141</v>
       </c>
       <c r="F98" t="n">
-        <v>2403975695.42659</v>
+        <v>2374541560.531219</v>
       </c>
       <c r="G98" t="n">
-        <v>239.764041017079</v>
+        <v>239.7447977229657</v>
       </c>
       <c r="H98" t="n">
-        <v>7.575955226003828</v>
+        <v>7.722623300677319</v>
       </c>
       <c r="I98" t="n">
-        <v>2.752445317531999</v>
+        <v>2.778960831080085</v>
       </c>
     </row>
     <row r="99">
@@ -3492,25 +3492,25 @@
         <v>300</v>
       </c>
       <c r="C99" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D99" t="n">
-        <v>210.1175231933594</v>
+        <v>209.8344573974609</v>
       </c>
       <c r="E99" t="n">
-        <v>243.81591796875</v>
+        <v>245.8572235107422</v>
       </c>
       <c r="F99" t="n">
-        <v>2304446570.033173</v>
+        <v>2276344154.098923</v>
       </c>
       <c r="G99" t="n">
-        <v>229.8373577529269</v>
+        <v>229.8303292911035</v>
       </c>
       <c r="H99" t="n">
-        <v>6.10071474178661</v>
+        <v>6.110700129219928</v>
       </c>
       <c r="I99" t="n">
-        <v>2.469962498052675</v>
+        <v>2.471983035787246</v>
       </c>
     </row>
     <row r="100">
@@ -3523,25 +3523,25 @@
         <v>250</v>
       </c>
       <c r="C100" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D100" t="n">
-        <v>205.1709289550781</v>
+        <v>206.8453216552734</v>
       </c>
       <c r="E100" t="n">
-        <v>238.6356811523438</v>
+        <v>239.6231536865234</v>
       </c>
       <c r="F100" t="n">
-        <v>2248466244.028961</v>
+        <v>2221121307.007431</v>
       </c>
       <c r="G100" t="n">
-        <v>224.2540778529853</v>
+        <v>224.25477292869</v>
       </c>
       <c r="H100" t="n">
-        <v>4.79171467876384</v>
+        <v>4.74228599998435</v>
       </c>
       <c r="I100" t="n">
-        <v>2.188998556135622</v>
+        <v>2.177679039708182</v>
       </c>
     </row>
     <row r="101">
@@ -3554,25 +3554,25 @@
         <v>200</v>
       </c>
       <c r="C101" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D101" t="n">
-        <v>202.6686401367188</v>
+        <v>203.9869079589844</v>
       </c>
       <c r="E101" t="n">
-        <v>235.3539276123047</v>
+        <v>235.3334808349609</v>
       </c>
       <c r="F101" t="n">
-        <v>2188973182.29628</v>
+        <v>2162443892.994141</v>
       </c>
       <c r="G101" t="n">
-        <v>218.3204501043177</v>
+        <v>218.3304273676994</v>
       </c>
       <c r="H101" t="n">
-        <v>3.513912503862053</v>
+        <v>3.456563859657978</v>
       </c>
       <c r="I101" t="n">
-        <v>1.874543278738065</v>
+        <v>1.85918365409606</v>
       </c>
     </row>
     <row r="102">
@@ -3585,25 +3585,25 @@
         <v>150</v>
       </c>
       <c r="C102" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D102" t="n">
         <v>199.7282409667969</v>
       </c>
       <c r="E102" t="n">
-        <v>231.593505859375</v>
+        <v>231.5911560058594</v>
       </c>
       <c r="F102" t="n">
-        <v>2127541516.277298</v>
+        <v>2101854445.244751</v>
       </c>
       <c r="G102" t="n">
-        <v>212.1934728145124</v>
+        <v>212.2130339574209</v>
       </c>
       <c r="H102" t="n">
-        <v>3.717591481198834</v>
+        <v>3.727950877535779</v>
       </c>
       <c r="I102" t="n">
-        <v>1.928105671688882</v>
+        <v>1.930790221006875</v>
       </c>
     </row>
     <row r="103">
@@ -3616,25 +3616,25 @@
         <v>100</v>
       </c>
       <c r="C103" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D103" t="n">
-        <v>197.075439453125</v>
+        <v>197.5082550048828</v>
       </c>
       <c r="E103" t="n">
-        <v>229.3795166015625</v>
+        <v>228.7249298095703</v>
       </c>
       <c r="F103" t="n">
-        <v>2067850418.73085</v>
+        <v>2042909904.433975</v>
       </c>
       <c r="G103" t="n">
-        <v>206.2400936735711</v>
+        <v>206.2617180282992</v>
       </c>
       <c r="H103" t="n">
-        <v>7.949036296630696</v>
+        <v>7.957001502644427</v>
       </c>
       <c r="I103" t="n">
-        <v>2.81940353561364</v>
+        <v>2.820815751275582</v>
       </c>
     </row>
     <row r="104">
@@ -3647,25 +3647,25 @@
         <v>1000</v>
       </c>
       <c r="C104" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D104" t="n">
-        <v>-35.444091796875</v>
+        <v>-38.69720458984375</v>
       </c>
       <c r="E104" t="n">
-        <v>31.78263854980469</v>
+        <v>30.55911254882812</v>
       </c>
       <c r="F104" t="n">
-        <v>-28661084.70574951</v>
+        <v>-28485397.36917114</v>
       </c>
       <c r="G104" t="n">
-        <v>-2.85855530987966</v>
+        <v>-2.876018657177108</v>
       </c>
       <c r="H104" t="n">
-        <v>21.09356699685789</v>
+        <v>20.81096202419509</v>
       </c>
       <c r="I104" t="n">
-        <v>4.592773344816603</v>
+        <v>4.561903333499636</v>
       </c>
     </row>
     <row r="105">
@@ -3678,25 +3678,25 @@
         <v>975</v>
       </c>
       <c r="C105" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D105" t="n">
         <v>-44.34205627441406</v>
       </c>
       <c r="E105" t="n">
-        <v>35.90019226074219</v>
+        <v>36.06578063964844</v>
       </c>
       <c r="F105" t="n">
-        <v>-31036257.70367432</v>
+        <v>-30828405.46591187</v>
       </c>
       <c r="G105" t="n">
-        <v>-3.095446671626996</v>
+        <v>-3.112579689231937</v>
       </c>
       <c r="H105" t="n">
-        <v>25.17002160117967</v>
+        <v>24.87714970616775</v>
       </c>
       <c r="I105" t="n">
-        <v>5.016973350654721</v>
+        <v>4.987699841226188</v>
       </c>
     </row>
     <row r="106">
@@ -3709,25 +3709,25 @@
         <v>950</v>
       </c>
       <c r="C106" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D106" t="n">
-        <v>-55.71876525878906</v>
+        <v>-55.7569580078125</v>
       </c>
       <c r="E106" t="n">
-        <v>44.95748901367188</v>
+        <v>46.89558410644531</v>
       </c>
       <c r="F106" t="n">
-        <v>-32511455.06626892</v>
+        <v>-32300441.23620605</v>
       </c>
       <c r="G106" t="n">
-        <v>-3.242577643718893</v>
+        <v>-3.26120329045931</v>
       </c>
       <c r="H106" t="n">
-        <v>28.19293071790275</v>
+        <v>27.89172639003009</v>
       </c>
       <c r="I106" t="n">
-        <v>5.309701565804122</v>
+        <v>5.281261817977791</v>
       </c>
     </row>
     <row r="107">
@@ -3740,25 +3740,25 @@
         <v>925</v>
       </c>
       <c r="C107" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D107" t="n">
-        <v>-58.72221374511719</v>
+        <v>-61.9556884765625</v>
       </c>
       <c r="E107" t="n">
-        <v>49.02644348144531</v>
+        <v>51.88597106933594</v>
       </c>
       <c r="F107" t="n">
-        <v>-32494862.96014404</v>
+        <v>-32347670.70326233</v>
       </c>
       <c r="G107" t="n">
-        <v>-3.240922805684942</v>
+        <v>-3.265971797868959</v>
       </c>
       <c r="H107" t="n">
-        <v>29.73806395968585</v>
+        <v>29.44244765134103</v>
       </c>
       <c r="I107" t="n">
-        <v>5.453261772525307</v>
+        <v>5.426089535875817</v>
       </c>
     </row>
     <row r="108">
@@ -3771,25 +3771,25 @@
         <v>900</v>
       </c>
       <c r="C108" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D108" t="n">
-        <v>-57.55891418457031</v>
+        <v>-62.35000610351562</v>
       </c>
       <c r="E108" t="n">
-        <v>50.91188049316406</v>
+        <v>51.50082397460938</v>
       </c>
       <c r="F108" t="n">
-        <v>-31972289.9831543</v>
+        <v>-31893965.07331848</v>
       </c>
       <c r="G108" t="n">
-        <v>-3.188803223557825</v>
+        <v>-3.220163560066508</v>
       </c>
       <c r="H108" t="n">
-        <v>30.37371641299665</v>
+        <v>30.12949181280628</v>
       </c>
       <c r="I108" t="n">
-        <v>5.511235470654166</v>
+        <v>5.489033777706809</v>
       </c>
     </row>
     <row r="109">
@@ -3802,25 +3802,25 @@
         <v>875</v>
       </c>
       <c r="C109" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D109" t="n">
-        <v>-55.08590698242188</v>
+        <v>-63.30732727050781</v>
       </c>
       <c r="E109" t="n">
-        <v>52.4219970703125</v>
+        <v>51.68013000488281</v>
       </c>
       <c r="F109" t="n">
-        <v>-31157462.40396118</v>
+        <v>-31132721.64068604</v>
       </c>
       <c r="G109" t="n">
-        <v>-3.107535200136789</v>
+        <v>-3.143304870453351</v>
       </c>
       <c r="H109" t="n">
-        <v>30.78586801517007</v>
+        <v>30.61963203249524</v>
       </c>
       <c r="I109" t="n">
-        <v>5.548501420669375</v>
+        <v>5.533500883933717</v>
       </c>
     </row>
     <row r="110">
@@ -3833,25 +3833,25 @@
         <v>850</v>
       </c>
       <c r="C110" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D110" t="n">
-        <v>-54.52687072753906</v>
+        <v>-63.0902099609375</v>
       </c>
       <c r="E110" t="n">
-        <v>52.21392822265625</v>
+        <v>50.84359741210938</v>
       </c>
       <c r="F110" t="n">
-        <v>-30273145.1541748</v>
+        <v>-30294053.06414795</v>
       </c>
       <c r="G110" t="n">
-        <v>-3.019336522524002</v>
+        <v>-3.058628976975302</v>
       </c>
       <c r="H110" t="n">
-        <v>31.45466007862744</v>
+        <v>31.36525652958391</v>
       </c>
       <c r="I110" t="n">
-        <v>5.608445424413743</v>
+        <v>5.600469313332939</v>
       </c>
     </row>
     <row r="111">
@@ -3864,25 +3864,25 @@
         <v>825</v>
       </c>
       <c r="C111" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D111" t="n">
-        <v>-53.82025146484375</v>
+        <v>-62.351318359375</v>
       </c>
       <c r="E111" t="n">
-        <v>53.10092163085938</v>
+        <v>50.95205688476562</v>
       </c>
       <c r="F111" t="n">
-        <v>-29413944.10871887</v>
+        <v>-29476024.06838989</v>
       </c>
       <c r="G111" t="n">
-        <v>-2.933642846378917</v>
+        <v>-2.976036951895874</v>
       </c>
       <c r="H111" t="n">
-        <v>32.57910105197477</v>
+        <v>32.54356938871108</v>
       </c>
       <c r="I111" t="n">
-        <v>5.707810530490195</v>
+        <v>5.704697133828498</v>
       </c>
     </row>
     <row r="112">
@@ -3895,25 +3895,25 @@
         <v>800</v>
       </c>
       <c r="C112" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D112" t="n">
-        <v>-53.17196655273438</v>
+        <v>-61.39985656738281</v>
       </c>
       <c r="E112" t="n">
-        <v>55.35334777832031</v>
+        <v>50.50736999511719</v>
       </c>
       <c r="F112" t="n">
-        <v>-28605625.79428101</v>
+        <v>-28722261.02346802</v>
       </c>
       <c r="G112" t="n">
-        <v>-2.853024034023006</v>
+        <v>-2.899933517136269</v>
       </c>
       <c r="H112" t="n">
-        <v>34.16042425945646</v>
+        <v>34.17599223637693</v>
       </c>
       <c r="I112" t="n">
-        <v>5.844691973017608</v>
+        <v>5.846023626053604</v>
       </c>
     </row>
     <row r="113">
@@ -3926,25 +3926,25 @@
         <v>775</v>
       </c>
       <c r="C113" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D113" t="n">
-        <v>-51.88919067382812</v>
+        <v>-60.44361877441406</v>
       </c>
       <c r="E113" t="n">
-        <v>57.48287963867188</v>
+        <v>49.86827087402344</v>
       </c>
       <c r="F113" t="n">
-        <v>-27833527.2855072</v>
+        <v>-28023921.97550964</v>
       </c>
       <c r="G113" t="n">
-        <v>-2.776017657095372</v>
+        <v>-2.829425947768919</v>
       </c>
       <c r="H113" t="n">
-        <v>36.08159037987387</v>
+        <v>36.17797611460743</v>
       </c>
       <c r="I113" t="n">
-        <v>6.006795350257396</v>
+        <v>6.014813057328335</v>
       </c>
     </row>
     <row r="114">
@@ -3957,25 +3957,25 @@
         <v>750</v>
       </c>
       <c r="C114" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D114" t="n">
-        <v>-50.31416320800781</v>
+        <v>-59.44984436035156</v>
       </c>
       <c r="E114" t="n">
-        <v>58.69093322753906</v>
+        <v>50.59733581542969</v>
       </c>
       <c r="F114" t="n">
-        <v>-26999438.57720947</v>
+        <v>-27282928.5418396</v>
       </c>
       <c r="G114" t="n">
-        <v>-2.692828596719821</v>
+        <v>-2.754611792555941</v>
       </c>
       <c r="H114" t="n">
-        <v>38.14796134749733</v>
+        <v>38.35974345009902</v>
       </c>
       <c r="I114" t="n">
-        <v>6.176403593313615</v>
+        <v>6.193524315775229</v>
       </c>
     </row>
     <row r="115">
@@ -3988,25 +3988,25 @@
         <v>725</v>
       </c>
       <c r="C115" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D115" t="n">
-        <v>-48.82179260253906</v>
+        <v>-57.47085571289062</v>
       </c>
       <c r="E115" t="n">
-        <v>56.70549011230469</v>
+        <v>53.33103942871094</v>
       </c>
       <c r="F115" t="n">
-        <v>-24917005.25315857</v>
+        <v>-25333419.78370667</v>
       </c>
       <c r="G115" t="n">
-        <v>-2.485134055600745</v>
+        <v>-2.557780290152926</v>
       </c>
       <c r="H115" t="n">
-        <v>42.25084711657594</v>
+        <v>42.79226711108313</v>
       </c>
       <c r="I115" t="n">
-        <v>6.500065162486907</v>
+        <v>6.541579863540851</v>
       </c>
     </row>
     <row r="116">
@@ -4019,25 +4019,25 @@
         <v>700</v>
       </c>
       <c r="C116" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D116" t="n">
-        <v>-48.69514465332031</v>
+        <v>-55.18896484375</v>
       </c>
       <c r="E116" t="n">
-        <v>54.64736938476562</v>
+        <v>53.3035888671875</v>
       </c>
       <c r="F116" t="n">
-        <v>-22558606.70152283</v>
+        <v>-23018280.27198792</v>
       </c>
       <c r="G116" t="n">
-        <v>-2.24991571785099</v>
+        <v>-2.324033000502087</v>
       </c>
       <c r="H116" t="n">
-        <v>45.94430222578744</v>
+        <v>46.95038988771768</v>
       </c>
       <c r="I116" t="n">
-        <v>6.778222645044012</v>
+        <v>6.852035455812942</v>
       </c>
     </row>
     <row r="117">
@@ -4050,25 +4050,25 @@
         <v>650</v>
       </c>
       <c r="C117" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D117" t="n">
-        <v>-46.45986938476562</v>
+        <v>-52.69477844238281</v>
       </c>
       <c r="E117" t="n">
-        <v>55.64677429199219</v>
+        <v>56.28604125976562</v>
       </c>
       <c r="F117" t="n">
-        <v>-19913107.31484985</v>
+        <v>-20272360.38645935</v>
       </c>
       <c r="G117" t="n">
-        <v>-1.986062957332828</v>
+        <v>-2.046792113898176</v>
       </c>
       <c r="H117" t="n">
-        <v>48.61532829265593</v>
+        <v>49.88764361165846</v>
       </c>
       <c r="I117" t="n">
-        <v>6.972469310987028</v>
+        <v>7.063118547189935</v>
       </c>
     </row>
     <row r="118">
@@ -4081,25 +4081,25 @@
         <v>600</v>
       </c>
       <c r="C118" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D118" t="n">
-        <v>-42.60932922363281</v>
+        <v>-49.88926696777344</v>
       </c>
       <c r="E118" t="n">
-        <v>56.51473999023438</v>
+        <v>59.70863342285156</v>
       </c>
       <c r="F118" t="n">
-        <v>-16863510.49951172</v>
+        <v>-17092248.7870636</v>
       </c>
       <c r="G118" t="n">
-        <v>-1.681906947224517</v>
+        <v>-1.725713205528586</v>
       </c>
       <c r="H118" t="n">
-        <v>51.42436839154606</v>
+        <v>52.7351273484099</v>
       </c>
       <c r="I118" t="n">
-        <v>7.171078607263071</v>
+        <v>7.261895575427252</v>
       </c>
     </row>
     <row r="119">
@@ -4112,25 +4112,25 @@
         <v>550</v>
       </c>
       <c r="C119" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D119" t="n">
-        <v>-44.61569213867188</v>
+        <v>-47.72129821777344</v>
       </c>
       <c r="E119" t="n">
-        <v>63.27864074707031</v>
+        <v>63.10870361328125</v>
       </c>
       <c r="F119" t="n">
-        <v>-13154174.16743469</v>
+        <v>-13342884.38479614</v>
       </c>
       <c r="G119" t="n">
-        <v>-1.311950849015109</v>
+        <v>-1.347159877529471</v>
       </c>
       <c r="H119" t="n">
-        <v>56.20833926221006</v>
+        <v>57.59203663136957</v>
       </c>
       <c r="I119" t="n">
-        <v>7.497222103033233</v>
+        <v>7.588941733296519</v>
       </c>
     </row>
     <row r="120">
@@ -4143,25 +4143,25 @@
         <v>500</v>
       </c>
       <c r="C120" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D120" t="n">
-        <v>-44.61308288574219</v>
+        <v>-45.96467590332031</v>
       </c>
       <c r="E120" t="n">
-        <v>70.44790649414062</v>
+        <v>68.8433837890625</v>
       </c>
       <c r="F120" t="n">
-        <v>-8158247.426391602</v>
+        <v>-8081665.683181763</v>
       </c>
       <c r="G120" t="n">
-        <v>-0.8136747697949304</v>
+        <v>-0.8159626837803535</v>
       </c>
       <c r="H120" t="n">
-        <v>63.64295968479935</v>
+        <v>64.79807183038747</v>
       </c>
       <c r="I120" t="n">
-        <v>7.97765377067715</v>
+        <v>8.049724953710374</v>
       </c>
     </row>
     <row r="121">
@@ -4174,25 +4174,25 @@
         <v>450</v>
       </c>
       <c r="C121" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D121" t="n">
-        <v>-48.41604614257812</v>
+        <v>-44.16006469726562</v>
       </c>
       <c r="E121" t="n">
-        <v>77.19099426269531</v>
+        <v>75.38790893554688</v>
       </c>
       <c r="F121" t="n">
-        <v>-1540757.556732178</v>
+        <v>-1392350.452362061</v>
       </c>
       <c r="G121" t="n">
-        <v>-0.15366971418742</v>
+        <v>-0.1405781996447121</v>
       </c>
       <c r="H121" t="n">
-        <v>73.77414047976907</v>
+        <v>75.03823965913674</v>
       </c>
       <c r="I121" t="n">
-        <v>8.589187416733266</v>
+        <v>8.66246152425145</v>
       </c>
     </row>
     <row r="122">
@@ -4205,25 +4205,25 @@
         <v>400</v>
       </c>
       <c r="C122" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D122" t="n">
-        <v>-51.37127685546875</v>
+        <v>-42.07801818847656</v>
       </c>
       <c r="E122" t="n">
-        <v>81.51275634765625</v>
+        <v>77.19903564453125</v>
       </c>
       <c r="F122" t="n">
-        <v>6650853.389419556</v>
+        <v>6677834.168365479</v>
       </c>
       <c r="G122" t="n">
-        <v>0.6633326151728853</v>
+        <v>0.6742253024891826</v>
       </c>
       <c r="H122" t="n">
-        <v>88.24840345671007</v>
+        <v>89.72428834889688</v>
       </c>
       <c r="I122" t="n">
-        <v>9.394062138218485</v>
+        <v>9.472290554501424</v>
       </c>
     </row>
     <row r="123">
@@ -4236,25 +4236,25 @@
         <v>350</v>
       </c>
       <c r="C123" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D123" t="n">
-        <v>-52.45257568359375</v>
+        <v>-43.08665466308594</v>
       </c>
       <c r="E123" t="n">
-        <v>84.01470947265625</v>
+        <v>84.96342468261719</v>
       </c>
       <c r="F123" t="n">
-        <v>17100744.74638367</v>
+        <v>17055716.34919739</v>
       </c>
       <c r="G123" t="n">
-        <v>1.705567852701174</v>
+        <v>1.72202472010801</v>
       </c>
       <c r="H123" t="n">
-        <v>109.7875129566108</v>
+        <v>110.8579537774895</v>
       </c>
       <c r="I123" t="n">
-        <v>10.47795366264858</v>
+        <v>10.52891037940249</v>
       </c>
     </row>
     <row r="124">
@@ -4267,25 +4267,25 @@
         <v>300</v>
       </c>
       <c r="C124" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D124" t="n">
-        <v>-48.10688781738281</v>
+        <v>-48.26020812988281</v>
       </c>
       <c r="E124" t="n">
-        <v>84.57643127441406</v>
+        <v>87.12361145019531</v>
       </c>
       <c r="F124" t="n">
-        <v>30142345.76089478</v>
+        <v>30137028.19355774</v>
       </c>
       <c r="G124" t="n">
-        <v>3.006291053239497</v>
+        <v>3.042775013219585</v>
       </c>
       <c r="H124" t="n">
-        <v>138.7934274237285</v>
+        <v>139.3159406519879</v>
       </c>
       <c r="I124" t="n">
-        <v>11.78106223664609</v>
+        <v>11.80321738561092</v>
       </c>
     </row>
     <row r="125">
@@ -4298,25 +4298,25 @@
         <v>250</v>
       </c>
       <c r="C125" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D125" t="n">
-        <v>-46.27247619628906</v>
+        <v>-47.76541137695312</v>
       </c>
       <c r="E125" t="n">
         <v>82.59519958496094</v>
       </c>
       <c r="F125" t="n">
-        <v>37796574.24908447</v>
+        <v>37787374.69078064</v>
       </c>
       <c r="G125" t="n">
-        <v>3.769696755172261</v>
+        <v>3.815189699057711</v>
       </c>
       <c r="H125" t="n">
-        <v>153.5021143108031</v>
+        <v>154.0149336731059</v>
       </c>
       <c r="I125" t="n">
-        <v>12.38959701970985</v>
+        <v>12.41027532624099</v>
       </c>
     </row>
     <row r="126">
@@ -4329,25 +4329,25 @@
         <v>200</v>
       </c>
       <c r="C126" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D126" t="n">
-        <v>-44.70292663574219</v>
+        <v>-42.19203186035156</v>
       </c>
       <c r="E126" t="n">
-        <v>83.59883117675781</v>
+        <v>84.77070617675781</v>
       </c>
       <c r="F126" t="n">
-        <v>46234103.39624023</v>
+        <v>46038909.79142761</v>
       </c>
       <c r="G126" t="n">
-        <v>4.611226096908199</v>
+        <v>4.648303191990639</v>
       </c>
       <c r="H126" t="n">
-        <v>161.9187947343962</v>
+        <v>162.6779853278291</v>
       </c>
       <c r="I126" t="n">
-        <v>12.7247316173818</v>
+        <v>12.75452803234322</v>
       </c>
     </row>
     <row r="127">
@@ -4360,25 +4360,25 @@
         <v>150</v>
       </c>
       <c r="C127" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D127" t="n">
-        <v>-42.92500305175781</v>
+        <v>-41.26174926757812</v>
       </c>
       <c r="E127" t="n">
-        <v>79.32940673828125</v>
+        <v>79.56495666503906</v>
       </c>
       <c r="F127" t="n">
-        <v>52524229.86404419</v>
+        <v>51891153.00796509</v>
       </c>
       <c r="G127" t="n">
-        <v>5.238581083607199</v>
+        <v>5.239172979024613</v>
       </c>
       <c r="H127" t="n">
-        <v>155.1328340536776</v>
+        <v>155.8666527236148</v>
       </c>
       <c r="I127" t="n">
-        <v>12.45523319948999</v>
+        <v>12.4846566922609</v>
       </c>
     </row>
     <row r="128">
@@ -4391,25 +4391,25 @@
         <v>100</v>
       </c>
       <c r="C128" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D128" t="n">
-        <v>-38.6629638671875</v>
+        <v>-41.47625732421875</v>
       </c>
       <c r="E128" t="n">
         <v>72.023681640625</v>
       </c>
       <c r="F128" t="n">
-        <v>52531240.88981628</v>
+        <v>51835718.18338013</v>
       </c>
       <c r="G128" t="n">
-        <v>5.239280338543074</v>
+        <v>5.233576020425165</v>
       </c>
       <c r="H128" t="n">
-        <v>128.9300631317917</v>
+        <v>130.229618442277</v>
       </c>
       <c r="I128" t="n">
-        <v>11.35473747524758</v>
+        <v>11.411819243323</v>
       </c>
     </row>
     <row r="129">
@@ -4422,25 +4422,25 @@
         <v>1000</v>
       </c>
       <c r="C129" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D129" t="n">
-        <v>-32.6859130859375</v>
+        <v>-37.298583984375</v>
       </c>
       <c r="E129" t="n">
         <v>34.28530883789062</v>
       </c>
       <c r="F129" t="n">
-        <v>3020644.900299072</v>
+        <v>2722053.059677124</v>
       </c>
       <c r="G129" t="n">
-        <v>0.3012684484086758</v>
+        <v>0.2748311804816246</v>
       </c>
       <c r="H129" t="n">
-        <v>14.44922339250339</v>
+        <v>14.30414320368521</v>
       </c>
       <c r="I129" t="n">
-        <v>3.801213410544506</v>
+        <v>3.782081861050235</v>
       </c>
     </row>
     <row r="130">
@@ -4453,25 +4453,25 @@
         <v>975</v>
       </c>
       <c r="C130" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D130" t="n">
-        <v>-38.95536804199219</v>
+        <v>-39.46832275390625</v>
       </c>
       <c r="E130" t="n">
-        <v>40.86978149414062</v>
+        <v>41.77491760253906</v>
       </c>
       <c r="F130" t="n">
-        <v>3610669.231277466</v>
+        <v>3317250.00680542</v>
       </c>
       <c r="G130" t="n">
-        <v>0.3601153902321367</v>
+        <v>0.334925041994276</v>
       </c>
       <c r="H130" t="n">
-        <v>17.07739181541644</v>
+        <v>16.9563766958445</v>
       </c>
       <c r="I130" t="n">
-        <v>4.132480104660691</v>
+        <v>4.117812124884343</v>
       </c>
     </row>
     <row r="131">
@@ -4484,25 +4484,25 @@
         <v>950</v>
       </c>
       <c r="C131" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D131" t="n">
-        <v>-48.9976806640625</v>
+        <v>-54.18948364257812</v>
       </c>
       <c r="E131" t="n">
-        <v>53.12228393554688</v>
+        <v>59.4952392578125</v>
       </c>
       <c r="F131" t="n">
-        <v>4672600.524200439</v>
+        <v>4336245.421279907</v>
       </c>
       <c r="G131" t="n">
-        <v>0.4660286648788342</v>
+        <v>0.4378075745995006</v>
       </c>
       <c r="H131" t="n">
-        <v>17.84978739926698</v>
+        <v>17.72748990822002</v>
       </c>
       <c r="I131" t="n">
-        <v>4.224900874490072</v>
+        <v>4.210402582677816</v>
       </c>
     </row>
     <row r="132">
@@ -4515,25 +4515,25 @@
         <v>925</v>
       </c>
       <c r="C132" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D132" t="n">
-        <v>-54.05300903320312</v>
+        <v>-61.78614807128906</v>
       </c>
       <c r="E132" t="n">
-        <v>59.66902160644531</v>
+        <v>64.50277709960938</v>
       </c>
       <c r="F132" t="n">
-        <v>5516435.754348755</v>
+        <v>5148640.639938354</v>
       </c>
       <c r="G132" t="n">
-        <v>0.5501898089028102</v>
+        <v>0.5198307872506207</v>
       </c>
       <c r="H132" t="n">
-        <v>17.27271407468447</v>
+        <v>17.07536442418462</v>
       </c>
       <c r="I132" t="n">
-        <v>4.156045485155867</v>
+        <v>4.132234797804285</v>
       </c>
     </row>
     <row r="133">
@@ -4546,25 +4546,25 @@
         <v>900</v>
       </c>
       <c r="C133" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D133" t="n">
-        <v>-56.42100524902344</v>
+        <v>-62.3619384765625</v>
       </c>
       <c r="E133" t="n">
-        <v>59.36355590820312</v>
+        <v>65.13273620605469</v>
       </c>
       <c r="F133" t="n">
-        <v>5868094.359527588</v>
+        <v>5514459.938323975</v>
       </c>
       <c r="G133" t="n">
-        <v>0.5852629955396456</v>
+        <v>0.5567656108613738</v>
       </c>
       <c r="H133" t="n">
-        <v>16.41085197056272</v>
+        <v>16.14136307614882</v>
       </c>
       <c r="I133" t="n">
-        <v>4.051030976253172</v>
+        <v>4.01763152568137</v>
       </c>
     </row>
     <row r="134">
@@ -4577,25 +4577,25 @@
         <v>875</v>
       </c>
       <c r="C134" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D134" t="n">
-        <v>-56.56988525390625</v>
+        <v>-60.04344177246094</v>
       </c>
       <c r="E134" t="n">
-        <v>60.85801696777344</v>
+        <v>66.50411987304688</v>
       </c>
       <c r="F134" t="n">
-        <v>5915523.936264038</v>
+        <v>5589507.06791687</v>
       </c>
       <c r="G134" t="n">
-        <v>0.589993453923103</v>
+        <v>0.564342719303268</v>
       </c>
       <c r="H134" t="n">
-        <v>15.74153775086646</v>
+        <v>15.45974643937352</v>
       </c>
       <c r="I134" t="n">
-        <v>3.967560680174465</v>
+        <v>3.931888406271663</v>
       </c>
     </row>
     <row r="135">
@@ -4608,25 +4608,25 @@
         <v>850</v>
       </c>
       <c r="C135" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D135" t="n">
-        <v>-54.69912719726562</v>
+        <v>-58.49705505371094</v>
       </c>
       <c r="E135" t="n">
-        <v>60.85945129394531</v>
+        <v>66.01028442382812</v>
       </c>
       <c r="F135" t="n">
-        <v>5830283.297821045</v>
+        <v>5510976.213912964</v>
       </c>
       <c r="G135" t="n">
-        <v>0.5814918538566606</v>
+        <v>0.5564138777866089</v>
       </c>
       <c r="H135" t="n">
-        <v>15.38649233473598</v>
+        <v>15.12214828476894</v>
       </c>
       <c r="I135" t="n">
-        <v>3.922561960598708</v>
+        <v>3.888720648846988</v>
       </c>
     </row>
     <row r="136">
@@ -4639,25 +4639,25 @@
         <v>825</v>
       </c>
       <c r="C136" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D136" t="n">
-        <v>-52.16448974609375</v>
+        <v>-57.33427429199219</v>
       </c>
       <c r="E136" t="n">
-        <v>60.96000671386719</v>
+        <v>64.4208984375</v>
       </c>
       <c r="F136" t="n">
-        <v>5679253.127593994</v>
+        <v>5350445.757858276</v>
       </c>
       <c r="G136" t="n">
-        <v>0.5664286383682402</v>
+        <v>0.540205973762137</v>
       </c>
       <c r="H136" t="n">
-        <v>15.23839565059458</v>
+        <v>15.01834188021675</v>
       </c>
       <c r="I136" t="n">
-        <v>3.903638770505614</v>
+        <v>3.875350549333151</v>
       </c>
     </row>
     <row r="137">
@@ -4670,25 +4670,25 @@
         <v>800</v>
       </c>
       <c r="C137" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D137" t="n">
-        <v>-50.418212890625</v>
+        <v>-56.57296752929688</v>
       </c>
       <c r="E137" t="n">
-        <v>60.94770812988281</v>
+        <v>62.50079345703125</v>
       </c>
       <c r="F137" t="n">
-        <v>5515778.191925049</v>
+        <v>5195667.209335327</v>
       </c>
       <c r="G137" t="n">
-        <v>0.5501242259502781</v>
+        <v>0.5245788091657099</v>
       </c>
       <c r="H137" t="n">
-        <v>15.21273498515589</v>
+        <v>15.05579209600858</v>
       </c>
       <c r="I137" t="n">
-        <v>3.900350623361429</v>
+        <v>3.880179389668548</v>
       </c>
     </row>
     <row r="138">
@@ -4701,25 +4701,25 @@
         <v>775</v>
       </c>
       <c r="C138" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D138" t="n">
-        <v>-49.16567993164062</v>
+        <v>-55.9935302734375</v>
       </c>
       <c r="E138" t="n">
-        <v>60.76625061035156</v>
+        <v>60.65386962890625</v>
       </c>
       <c r="F138" t="n">
-        <v>5309552.364990234</v>
+        <v>5040895.727371216</v>
       </c>
       <c r="G138" t="n">
-        <v>0.5295559907047843</v>
+        <v>0.5089523580420352</v>
       </c>
       <c r="H138" t="n">
-        <v>15.29012520552146</v>
+        <v>15.19906026417564</v>
       </c>
       <c r="I138" t="n">
-        <v>3.910258969112079</v>
+        <v>3.898597217484212</v>
       </c>
     </row>
     <row r="139">
@@ -4732,25 +4732,25 @@
         <v>750</v>
       </c>
       <c r="C139" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D139" t="n">
-        <v>-48.96044921875</v>
+        <v>-54.71180725097656</v>
       </c>
       <c r="E139" t="n">
-        <v>59.72929382324219</v>
+        <v>60.21696472167969</v>
       </c>
       <c r="F139" t="n">
-        <v>5056341.021194458</v>
+        <v>4870023.809310913</v>
       </c>
       <c r="G139" t="n">
-        <v>0.5043015860386549</v>
+        <v>0.4917003317508046</v>
       </c>
       <c r="H139" t="n">
-        <v>15.47025486413227</v>
+        <v>15.43317483305329</v>
       </c>
       <c r="I139" t="n">
-        <v>3.933224486872351</v>
+        <v>3.928507965252621</v>
       </c>
     </row>
     <row r="140">
@@ -4763,25 +4763,25 @@
         <v>725</v>
       </c>
       <c r="C140" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D140" t="n">
-        <v>-48.434814453125</v>
+        <v>-50.73023986816406</v>
       </c>
       <c r="E140" t="n">
-        <v>56.40139770507812</v>
+        <v>59.89950561523438</v>
       </c>
       <c r="F140" t="n">
-        <v>4489154.588195801</v>
+        <v>4468144.072311401</v>
       </c>
       <c r="G140" t="n">
-        <v>0.4477324154582145</v>
+        <v>0.4511246779667738</v>
       </c>
       <c r="H140" t="n">
-        <v>16.15148017788225</v>
+        <v>16.1600652836442</v>
       </c>
       <c r="I140" t="n">
-        <v>4.018890416256986</v>
+        <v>4.019958368396892</v>
       </c>
     </row>
     <row r="141">
@@ -4794,25 +4794,25 @@
         <v>700</v>
       </c>
       <c r="C141" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D141" t="n">
-        <v>-45.97933959960938</v>
+        <v>-45.50639343261719</v>
       </c>
       <c r="E141" t="n">
-        <v>54.9803466796875</v>
+        <v>58.38702392578125</v>
       </c>
       <c r="F141" t="n">
-        <v>3944211.800079346</v>
+        <v>4015814.099975586</v>
       </c>
       <c r="G141" t="n">
-        <v>0.3933817474167355</v>
+        <v>0.405455332976482</v>
       </c>
       <c r="H141" t="n">
-        <v>17.14517794723772</v>
+        <v>17.17154041476632</v>
       </c>
       <c r="I141" t="n">
-        <v>4.140673610324498</v>
+        <v>4.143855742514007</v>
       </c>
     </row>
     <row r="142">
@@ -4825,25 +4825,25 @@
         <v>650</v>
       </c>
       <c r="C142" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D142" t="n">
-        <v>-46.01249694824219</v>
+        <v>-43.6400146484375</v>
       </c>
       <c r="E142" t="n">
-        <v>53.02639770507812</v>
+        <v>56.6099853515625</v>
       </c>
       <c r="F142" t="n">
-        <v>3028931.376663208</v>
+        <v>3096296.016693115</v>
       </c>
       <c r="G142" t="n">
-        <v>0.3020949122796049</v>
+        <v>0.3126164959801551</v>
       </c>
       <c r="H142" t="n">
-        <v>17.99249601527588</v>
+        <v>17.99134883299492</v>
       </c>
       <c r="I142" t="n">
-        <v>4.241756241850288</v>
+        <v>4.241621014776652</v>
       </c>
     </row>
     <row r="143">
@@ -4856,25 +4856,25 @@
         <v>600</v>
       </c>
       <c r="C143" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D143" t="n">
-        <v>-45.54269409179688</v>
+        <v>-43.83694458007812</v>
       </c>
       <c r="E143" t="n">
-        <v>51.60366821289062</v>
+        <v>54.10940551757812</v>
       </c>
       <c r="F143" t="n">
-        <v>1591780.694747925</v>
+        <v>1683393.780944824</v>
       </c>
       <c r="G143" t="n">
-        <v>0.1587585816744345</v>
+        <v>0.1699632923714456</v>
       </c>
       <c r="H143" t="n">
-        <v>18.90006331741872</v>
+        <v>18.88071287889355</v>
       </c>
       <c r="I143" t="n">
-        <v>4.347420306045726</v>
+        <v>4.345194227982628</v>
       </c>
     </row>
     <row r="144">
@@ -4887,25 +4887,25 @@
         <v>550</v>
       </c>
       <c r="C144" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D144" t="n">
         <v>-46.11848449707031</v>
       </c>
       <c r="E144" t="n">
-        <v>53.69560241699219</v>
+        <v>51.68350219726562</v>
       </c>
       <c r="F144" t="n">
-        <v>646192.4318695068</v>
+        <v>876209.2996063232</v>
       </c>
       <c r="G144" t="n">
-        <v>0.06444894972708659</v>
+        <v>0.08846618007818947</v>
       </c>
       <c r="H144" t="n">
-        <v>20.68592604502885</v>
+        <v>20.73150990335025</v>
       </c>
       <c r="I144" t="n">
-        <v>4.548178321595235</v>
+        <v>4.553186785466884</v>
       </c>
     </row>
     <row r="145">
@@ -4918,25 +4918,25 @@
         <v>500</v>
       </c>
       <c r="C145" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D145" t="n">
-        <v>-52.96994018554688</v>
+        <v>-53.49273681640625</v>
       </c>
       <c r="E145" t="n">
-        <v>53.25816345214844</v>
+        <v>55.87313842773438</v>
       </c>
       <c r="F145" t="n">
-        <v>162560.3520812988</v>
+        <v>606624.3642425537</v>
       </c>
       <c r="G145" t="n">
-        <v>0.01621319508276266</v>
+        <v>0.06124762687523455</v>
       </c>
       <c r="H145" t="n">
-        <v>24.29358574198843</v>
+        <v>24.43359387259374</v>
       </c>
       <c r="I145" t="n">
-        <v>4.928852375755277</v>
+        <v>4.94303488482468</v>
       </c>
     </row>
     <row r="146">
@@ -4949,25 +4949,25 @@
         <v>450</v>
       </c>
       <c r="C146" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D146" t="n">
-        <v>-59.32827758789062</v>
+        <v>-60.30949401855469</v>
       </c>
       <c r="E146" t="n">
-        <v>62.3621826171875</v>
+        <v>60.88302612304688</v>
       </c>
       <c r="F146" t="n">
-        <v>-199866.6874542236</v>
+        <v>442040.8657684326</v>
       </c>
       <c r="G146" t="n">
-        <v>-0.01993399714476679</v>
+        <v>0.04463050877291382</v>
       </c>
       <c r="H146" t="n">
-        <v>30.29919735649806</v>
+        <v>30.59825982524179</v>
       </c>
       <c r="I146" t="n">
-        <v>5.504470669964375</v>
+        <v>5.531569381761544</v>
       </c>
     </row>
     <row r="147">
@@ -4980,25 +4980,25 @@
         <v>400</v>
       </c>
       <c r="C147" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D147" t="n">
-        <v>-64.51643371582031</v>
+        <v>-65.55380249023438</v>
       </c>
       <c r="E147" t="n">
-        <v>67.37187194824219</v>
+        <v>69.10142517089844</v>
       </c>
       <c r="F147" t="n">
-        <v>-1999696.746002197</v>
+        <v>-1297944.910583496</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.1994426871878628</v>
+        <v>-0.1310465755645817</v>
       </c>
       <c r="H147" t="n">
-        <v>39.49901982341642</v>
+        <v>39.86690231730142</v>
       </c>
       <c r="I147" t="n">
-        <v>6.284824565842424</v>
+        <v>6.314024256945915</v>
       </c>
     </row>
     <row r="148">
@@ -5011,25 +5011,25 @@
         <v>350</v>
       </c>
       <c r="C148" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D148" t="n">
-        <v>-73.39028930664062</v>
+        <v>-68.04991149902344</v>
       </c>
       <c r="E148" t="n">
-        <v>71.73358154296875</v>
+        <v>75.79129028320312</v>
       </c>
       <c r="F148" t="n">
-        <v>-5368325.766494751</v>
+        <v>-4485034.063308716</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.5354178420853304</v>
+        <v>-0.4528299702819311</v>
       </c>
       <c r="H148" t="n">
-        <v>53.91605239840818</v>
+        <v>54.34302113850518</v>
       </c>
       <c r="I148" t="n">
-        <v>7.342755095902912</v>
+        <v>7.371771913082036</v>
       </c>
     </row>
     <row r="149">
@@ -5042,25 +5042,25 @@
         <v>300</v>
       </c>
       <c r="C149" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D149" t="n">
-        <v>-70.07968139648438</v>
+        <v>-75.88917541503906</v>
       </c>
       <c r="E149" t="n">
-        <v>72.16477966308594</v>
+        <v>76.22332763671875</v>
       </c>
       <c r="F149" t="n">
-        <v>-8161206.19102478</v>
+        <v>-7393021.889068604</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.8139698665241614</v>
+        <v>-0.7464339924880878</v>
       </c>
       <c r="H149" t="n">
-        <v>73.40046996390346</v>
+        <v>74.46044016084734</v>
       </c>
       <c r="I149" t="n">
-        <v>8.567407423713632</v>
+        <v>8.629046306565247</v>
       </c>
     </row>
     <row r="150">
@@ -5073,25 +5073,25 @@
         <v>250</v>
       </c>
       <c r="C150" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D150" t="n">
-        <v>-74.46308898925781</v>
+        <v>-75.75390625</v>
       </c>
       <c r="E150" t="n">
-        <v>71.28730773925781</v>
+        <v>76.65879821777344</v>
       </c>
       <c r="F150" t="n">
-        <v>-8586156.153442383</v>
+        <v>-7878754.465148926</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.8563528741448863</v>
+        <v>-0.7954758202393685</v>
       </c>
       <c r="H150" t="n">
-        <v>81.41272557321636</v>
+        <v>82.81196684952947</v>
       </c>
       <c r="I150" t="n">
-        <v>9.022900064459119</v>
+        <v>9.100108068013778</v>
       </c>
     </row>
     <row r="151">
@@ -5104,25 +5104,25 @@
         <v>200</v>
       </c>
       <c r="C151" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D151" t="n">
-        <v>-67.33631896972656</v>
+        <v>-73.10708618164062</v>
       </c>
       <c r="E151" t="n">
-        <v>68.48300170898438</v>
+        <v>73.15193176269531</v>
       </c>
       <c r="F151" t="n">
-        <v>-8565346.925323486</v>
+        <v>-7850755.585342407</v>
       </c>
       <c r="G151" t="n">
-        <v>-0.8542774352651464</v>
+        <v>-0.7926489226658529</v>
       </c>
       <c r="H151" t="n">
-        <v>83.22094461297077</v>
+        <v>84.7807729290198</v>
       </c>
       <c r="I151" t="n">
-        <v>9.122551431094854</v>
+        <v>9.207647524151856</v>
       </c>
     </row>
     <row r="152">
@@ -5135,25 +5135,25 @@
         <v>150</v>
       </c>
       <c r="C152" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D152" t="n">
-        <v>-58.65924072265625</v>
+        <v>-67.24429321289062</v>
       </c>
       <c r="E152" t="n">
-        <v>59.37025451660156</v>
+        <v>68.32243347167969</v>
       </c>
       <c r="F152" t="n">
-        <v>-8425962.950408936</v>
+        <v>-7648084.759048462</v>
       </c>
       <c r="G152" t="n">
-        <v>-0.8403757701434471</v>
+        <v>-0.7721863301967119</v>
       </c>
       <c r="H152" t="n">
-        <v>75.16175704335838</v>
+        <v>76.23530081738039</v>
       </c>
       <c r="I152" t="n">
-        <v>8.669588054997675</v>
+        <v>8.731282884970593</v>
       </c>
     </row>
     <row r="153">
@@ -5166,25 +5166,25 @@
         <v>100</v>
       </c>
       <c r="C153" t="n">
-        <v>10026423</v>
+        <v>9904455</v>
       </c>
       <c r="D153" t="n">
-        <v>-55.7503662109375</v>
+        <v>-56.85836791992188</v>
       </c>
       <c r="E153" t="n">
-        <v>46.62557983398438</v>
+        <v>53.3455810546875</v>
       </c>
       <c r="F153" t="n">
-        <v>-7540293.468109131</v>
+        <v>-6530851.576309204</v>
       </c>
       <c r="G153" t="n">
-        <v>-0.7520422256381086</v>
+        <v>-0.6593852540406531</v>
       </c>
       <c r="H153" t="n">
-        <v>57.84846532460295</v>
+        <v>58.35943216376103</v>
       </c>
       <c r="I153" t="n">
-        <v>7.605817860335794</v>
+        <v>7.639334536709401</v>
       </c>
     </row>
   </sheetData>

--- a/models/resnet18/data_train_statistics.xlsx
+++ b/models/resnet18/data_train_statistics.xlsx
@@ -485,25 +485,25 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D2" t="n">
-        <v>57229.859375</v>
+        <v>51329.703125</v>
       </c>
       <c r="E2" t="n">
-        <v>104148.953125</v>
+        <v>103777.0625</v>
       </c>
       <c r="F2" t="n">
-        <v>997938280727.6406</v>
+        <v>498470619825.625</v>
       </c>
       <c r="G2" t="n">
-        <v>100756.5061103958</v>
+        <v>100050.8050852539</v>
       </c>
       <c r="H2" t="n">
-        <v>6872947.682027092</v>
+        <v>20242757.64096022</v>
       </c>
       <c r="I2" t="n">
-        <v>2621.630729532115</v>
+        <v>4499.195221476861</v>
       </c>
     </row>
     <row r="3">
@@ -516,25 +516,25 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>7665278</v>
+        <v>4301572</v>
       </c>
       <c r="D3" t="n">
-        <v>273.029052734375</v>
+        <v>275.96533203125</v>
       </c>
       <c r="E3" t="n">
-        <v>307.64306640625</v>
+        <v>309.525634765625</v>
       </c>
       <c r="F3" t="n">
-        <v>2299262388.786377</v>
+        <v>1295042626.272461</v>
       </c>
       <c r="G3" t="n">
-        <v>299.9581213866445</v>
+        <v>301.0626408839527</v>
       </c>
       <c r="H3" t="n">
-        <v>6.045553630239024</v>
+        <v>8.558369416061568</v>
       </c>
       <c r="I3" t="n">
-        <v>2.458770755934563</v>
+        <v>2.925469093335558</v>
       </c>
     </row>
     <row r="4">
@@ -547,25 +547,25 @@
         <v>1000</v>
       </c>
       <c r="C4" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D4" t="n">
-        <v>-5028.0546875</v>
+        <v>-4724.3671875</v>
       </c>
       <c r="E4" t="n">
-        <v>3345.8203125</v>
+        <v>3131.7890625</v>
       </c>
       <c r="F4" t="n">
-        <v>12890629541.0498</v>
+        <v>4710889782.286377</v>
       </c>
       <c r="G4" t="n">
-        <v>1301.498117872192</v>
+        <v>945.5488380649792</v>
       </c>
       <c r="H4" t="n">
-        <v>129566.1263183947</v>
+        <v>135223.9644293178</v>
       </c>
       <c r="I4" t="n">
-        <v>359.9529501454249</v>
+        <v>367.728112100935</v>
       </c>
     </row>
     <row r="5">
@@ -578,25 +578,25 @@
         <v>975</v>
       </c>
       <c r="C5" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D5" t="n">
-        <v>-2872.02001953125</v>
+        <v>-2562.73291015625</v>
       </c>
       <c r="E5" t="n">
-        <v>5412.08740234375</v>
+        <v>5215.2578125</v>
       </c>
       <c r="F5" t="n">
-        <v>34377225323.5813</v>
+        <v>15557286197.95728</v>
       </c>
       <c r="G5" t="n">
-        <v>3470.885104085111</v>
+        <v>3122.589270340216</v>
       </c>
       <c r="H5" t="n">
-        <v>124054.0283873549</v>
+        <v>126885.3131877541</v>
       </c>
       <c r="I5" t="n">
-        <v>352.2130440335152</v>
+        <v>356.2096478027429</v>
       </c>
     </row>
     <row r="6">
@@ -609,25 +609,25 @@
         <v>950</v>
       </c>
       <c r="C6" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D6" t="n">
-        <v>-667.4052734375</v>
+        <v>-352.664306640625</v>
       </c>
       <c r="E6" t="n">
-        <v>7521.96826171875</v>
+        <v>7342.3134765625</v>
       </c>
       <c r="F6" t="n">
-        <v>56323154445.05591</v>
+        <v>26626256690.39969</v>
       </c>
       <c r="G6" t="n">
-        <v>5686.648527865045</v>
+        <v>5344.30378105942</v>
       </c>
       <c r="H6" t="n">
-        <v>117567.3584005246</v>
+        <v>119068.9830524094</v>
       </c>
       <c r="I6" t="n">
-        <v>342.8809682681799</v>
+        <v>345.0637376665496</v>
       </c>
     </row>
     <row r="7">
@@ -640,25 +640,25 @@
         <v>925</v>
       </c>
       <c r="C7" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D7" t="n">
-        <v>1636.52734375</v>
+        <v>1970.926025390625</v>
       </c>
       <c r="E7" t="n">
-        <v>9677.3974609375</v>
+        <v>9515.4921875</v>
       </c>
       <c r="F7" t="n">
-        <v>78749802870.93628</v>
+        <v>37938881020.47412</v>
       </c>
       <c r="G7" t="n">
-        <v>7950.94761609158</v>
+        <v>7614.923406037345</v>
       </c>
       <c r="H7" t="n">
-        <v>111676.4764480491</v>
+        <v>112036.4509717468</v>
       </c>
       <c r="I7" t="n">
-        <v>334.1803052964808</v>
+        <v>334.718465238694</v>
       </c>
     </row>
     <row r="8">
@@ -671,25 +671,25 @@
         <v>900</v>
       </c>
       <c r="C8" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D8" t="n">
-        <v>4009.0361328125</v>
+        <v>4352.50048828125</v>
       </c>
       <c r="E8" t="n">
-        <v>11898.005859375</v>
+        <v>11736.40234375</v>
       </c>
       <c r="F8" t="n">
-        <v>101687648110.1216</v>
+        <v>49511657133.33691</v>
       </c>
       <c r="G8" t="n">
-        <v>10266.85952029883</v>
+        <v>9937.759539425433</v>
       </c>
       <c r="H8" t="n">
-        <v>106929.1387918027</v>
+        <v>106102.8324595189</v>
       </c>
       <c r="I8" t="n">
-        <v>327.000212219813</v>
+        <v>325.7342973337608</v>
       </c>
     </row>
     <row r="9">
@@ -702,25 +702,25 @@
         <v>875</v>
       </c>
       <c r="C9" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D9" t="n">
-        <v>6452.4140625</v>
+        <v>6789.9375</v>
       </c>
       <c r="E9" t="n">
-        <v>14181.26171875</v>
+        <v>14007.95703125</v>
       </c>
       <c r="F9" t="n">
-        <v>125170208066.3564</v>
+        <v>61359234707.36035</v>
       </c>
       <c r="G9" t="n">
-        <v>12637.76836447405</v>
+        <v>12315.75259948927</v>
       </c>
       <c r="H9" t="n">
-        <v>103684.3255511515</v>
+        <v>101553.4830358049</v>
       </c>
       <c r="I9" t="n">
-        <v>322.0005055138136</v>
+        <v>318.6745723081854</v>
       </c>
     </row>
     <row r="10">
@@ -733,25 +733,25 @@
         <v>850</v>
       </c>
       <c r="C10" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D10" t="n">
-        <v>8969.5859375</v>
+        <v>9287.32421875</v>
       </c>
       <c r="E10" t="n">
-        <v>16519.91796875</v>
+        <v>16332.9140625</v>
       </c>
       <c r="F10" t="n">
-        <v>149230516180.3008</v>
+        <v>73496506153.52734</v>
       </c>
       <c r="G10" t="n">
-        <v>15067.00935895018</v>
+        <v>14751.891724704</v>
       </c>
       <c r="H10" t="n">
-        <v>102149.0819664164</v>
+        <v>98549.18561099053</v>
       </c>
       <c r="I10" t="n">
-        <v>319.6077001050138</v>
+        <v>313.9254459437631</v>
       </c>
     </row>
     <row r="11">
@@ -764,25 +764,25 @@
         <v>825</v>
       </c>
       <c r="C11" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D11" t="n">
-        <v>11560.8359375</v>
+        <v>11847.14453125</v>
       </c>
       <c r="E11" t="n">
-        <v>18918.2578125</v>
+        <v>18714.35546875</v>
       </c>
       <c r="F11" t="n">
-        <v>173900176066.1172</v>
+        <v>85939836116.83203</v>
       </c>
       <c r="G11" t="n">
-        <v>17557.77335210444</v>
+        <v>17249.46155380568</v>
       </c>
       <c r="H11" t="n">
-        <v>102250.6331069149</v>
+        <v>97145.57859346416</v>
       </c>
       <c r="I11" t="n">
-        <v>319.7665290597421</v>
+        <v>311.6818547709574</v>
       </c>
     </row>
     <row r="12">
@@ -795,25 +795,25 @@
         <v>800</v>
       </c>
       <c r="C12" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D12" t="n">
-        <v>14227.22265625</v>
+        <v>14474.73828125</v>
       </c>
       <c r="E12" t="n">
-        <v>21444.80078125</v>
+        <v>21221.42578125</v>
       </c>
       <c r="F12" t="n">
-        <v>199209313744.3711</v>
+        <v>98706603288.00781</v>
       </c>
       <c r="G12" t="n">
-        <v>20113.10200756849</v>
+        <v>19811.95026027936</v>
       </c>
       <c r="H12" t="n">
-        <v>103851.1754513517</v>
+        <v>97371.95130074142</v>
       </c>
       <c r="I12" t="n">
-        <v>322.2594846569324</v>
+        <v>312.0447905361367</v>
       </c>
     </row>
     <row r="13">
@@ -826,25 +826,25 @@
         <v>775</v>
       </c>
       <c r="C13" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D13" t="n">
-        <v>16971.20703125</v>
+        <v>17175.86328125</v>
       </c>
       <c r="E13" t="n">
-        <v>24061.49609375</v>
+        <v>23821.51171875</v>
       </c>
       <c r="F13" t="n">
-        <v>225189781031.6055</v>
+        <v>111815786193.1406</v>
       </c>
       <c r="G13" t="n">
-        <v>22736.21123338989</v>
+        <v>22443.16712944465</v>
       </c>
       <c r="H13" t="n">
-        <v>106679.7179003661</v>
+        <v>99127.99463358421</v>
       </c>
       <c r="I13" t="n">
-        <v>326.6186122993699</v>
+        <v>314.8459855764152</v>
       </c>
     </row>
     <row r="14">
@@ -857,25 +857,25 @@
         <v>750</v>
       </c>
       <c r="C14" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D14" t="n">
-        <v>19797.12890625</v>
+        <v>19954.48828125</v>
       </c>
       <c r="E14" t="n">
-        <v>26747.9296875</v>
+        <v>26489.453125</v>
       </c>
       <c r="F14" t="n">
-        <v>251878898091.3867</v>
+        <v>125286568723.418</v>
       </c>
       <c r="G14" t="n">
-        <v>25430.86904745248</v>
+        <v>25146.96266659001</v>
       </c>
       <c r="H14" t="n">
-        <v>110585.1471466864</v>
+        <v>102429.4628460816</v>
       </c>
       <c r="I14" t="n">
-        <v>332.5434515167701</v>
+        <v>320.0460323860954</v>
       </c>
     </row>
     <row r="15">
@@ -888,25 +888,25 @@
         <v>725</v>
       </c>
       <c r="C15" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D15" t="n">
-        <v>25710.22265625</v>
+        <v>25616.14453125</v>
       </c>
       <c r="E15" t="n">
-        <v>32365.8828125</v>
+        <v>32068.33203125</v>
       </c>
       <c r="F15" t="n">
-        <v>307549809113.6016</v>
+        <v>153402371506.3203</v>
       </c>
       <c r="G15" t="n">
-        <v>31051.66403538624</v>
+        <v>30790.24151225522</v>
       </c>
       <c r="H15" t="n">
-        <v>120749.3029137534</v>
+        <v>113442.6767897982</v>
       </c>
       <c r="I15" t="n">
-        <v>347.4900040486826</v>
+        <v>336.8125246925925</v>
       </c>
     </row>
     <row r="16">
@@ -919,25 +919,25 @@
         <v>700</v>
       </c>
       <c r="C16" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D16" t="n">
-        <v>31469.72265625</v>
+        <v>31160.58203125</v>
       </c>
       <c r="E16" t="n">
-        <v>38350.328125</v>
+        <v>38042.484375</v>
       </c>
       <c r="F16" t="n">
-        <v>366593897988.8125</v>
+        <v>183243111915.8594</v>
       </c>
       <c r="G16" t="n">
-        <v>37013.0308016758</v>
+        <v>36779.74216398663</v>
       </c>
       <c r="H16" t="n">
-        <v>133374.725734805</v>
+        <v>130354.9986290255</v>
       </c>
       <c r="I16" t="n">
-        <v>365.2050461518913</v>
+        <v>361.0470864430642</v>
       </c>
     </row>
     <row r="17">
@@ -950,25 +950,25 @@
         <v>650</v>
       </c>
       <c r="C17" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D17" t="n">
-        <v>37117.0859375</v>
+        <v>37047.14453125</v>
       </c>
       <c r="E17" t="n">
-        <v>44689.9921875</v>
+        <v>44390.50390625</v>
       </c>
       <c r="F17" t="n">
-        <v>429497314583.6523</v>
+        <v>215043777338.8867</v>
       </c>
       <c r="G17" t="n">
-        <v>43364.05330567436</v>
+        <v>43162.63024459947</v>
       </c>
       <c r="H17" t="n">
-        <v>148908.0236428283</v>
+        <v>153912.5354150584</v>
       </c>
       <c r="I17" t="n">
-        <v>385.8860241610576</v>
+        <v>392.3168813791454</v>
       </c>
     </row>
     <row r="18">
@@ -981,25 +981,25 @@
         <v>600</v>
       </c>
       <c r="C18" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D18" t="n">
-        <v>43194.83203125</v>
+        <v>43330.4609375</v>
       </c>
       <c r="E18" t="n">
-        <v>51453.01171875</v>
+        <v>51185.453125</v>
       </c>
       <c r="F18" t="n">
-        <v>496935239204</v>
+        <v>249148588409.5234</v>
       </c>
       <c r="G18" t="n">
-        <v>50172.9009020689</v>
+        <v>50007.99618831608</v>
       </c>
       <c r="H18" t="n">
-        <v>169492.1050305835</v>
+        <v>186175.9738702641</v>
       </c>
       <c r="I18" t="n">
-        <v>411.6941887257864</v>
+        <v>431.4811396460615</v>
       </c>
     </row>
     <row r="19">
@@ -1012,25 +1012,25 @@
         <v>550</v>
       </c>
       <c r="C19" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D19" t="n">
-        <v>49794.546875</v>
+        <v>50076.4765625</v>
       </c>
       <c r="E19" t="n">
-        <v>58785.05859375</v>
+        <v>58530.30078125</v>
       </c>
       <c r="F19" t="n">
-        <v>569698475965.9414</v>
+        <v>285969644434.293</v>
       </c>
       <c r="G19" t="n">
-        <v>57519.41686503104</v>
+        <v>57398.55473448706</v>
       </c>
       <c r="H19" t="n">
-        <v>199384.3246899957</v>
+        <v>229995.7013311065</v>
       </c>
       <c r="I19" t="n">
-        <v>446.5247190133999</v>
+        <v>479.5786706382036</v>
       </c>
     </row>
     <row r="20">
@@ -1043,25 +1043,25 @@
         <v>500</v>
       </c>
       <c r="C20" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D20" t="n">
-        <v>56983.375</v>
+        <v>57385.5234375</v>
       </c>
       <c r="E20" t="n">
-        <v>66756.84375</v>
+        <v>66572.796875</v>
       </c>
       <c r="F20" t="n">
-        <v>648738657477.2188</v>
+        <v>325985178109.2344</v>
       </c>
       <c r="G20" t="n">
-        <v>65499.68246382237</v>
+        <v>65430.2946221749</v>
       </c>
       <c r="H20" t="n">
-        <v>244193.607674709</v>
+        <v>290079.5636418526</v>
       </c>
       <c r="I20" t="n">
-        <v>494.1594961899539</v>
+        <v>538.5903486341475</v>
       </c>
     </row>
     <row r="21">
@@ -1074,25 +1074,25 @@
         <v>450</v>
       </c>
       <c r="C21" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D21" t="n">
-        <v>64909.421875</v>
+        <v>65415.04296875</v>
       </c>
       <c r="E21" t="n">
-        <v>75491.3515625</v>
+        <v>75412.703125</v>
       </c>
       <c r="F21" t="n">
-        <v>735253276934.9453</v>
+        <v>369829086869.2031</v>
       </c>
       <c r="G21" t="n">
-        <v>74234.60220021645</v>
+        <v>74230.4489242558</v>
       </c>
       <c r="H21" t="n">
-        <v>310793.5513581467</v>
+        <v>372169.6848041679</v>
       </c>
       <c r="I21" t="n">
-        <v>557.4886109672077</v>
+        <v>610.0571160179742</v>
       </c>
     </row>
     <row r="22">
@@ -1105,25 +1105,25 @@
         <v>400</v>
       </c>
       <c r="C22" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D22" t="n">
-        <v>73570</v>
+        <v>74383.75</v>
       </c>
       <c r="E22" t="n">
-        <v>85183.5625</v>
+        <v>85203.375</v>
       </c>
       <c r="F22" t="n">
-        <v>830846485381.6719</v>
+        <v>418339955947.125</v>
       </c>
       <c r="G22" t="n">
-        <v>83886.13864989745</v>
+        <v>83967.33473776502</v>
       </c>
       <c r="H22" t="n">
-        <v>407808.8253914824</v>
+        <v>482030.1787100612</v>
       </c>
       <c r="I22" t="n">
-        <v>638.5991116431986</v>
+        <v>694.2839323432894</v>
       </c>
     </row>
     <row r="23">
@@ -1136,25 +1136,25 @@
         <v>350</v>
       </c>
       <c r="C23" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D23" t="n">
-        <v>83467.6875</v>
+        <v>84689.0625</v>
       </c>
       <c r="E23" t="n">
-        <v>96108.6875</v>
+        <v>96222.875</v>
       </c>
       <c r="F23" t="n">
-        <v>937788418727.625</v>
+        <v>472684150339</v>
       </c>
       <c r="G23" t="n">
-        <v>94683.49532888229</v>
+        <v>94875.05965547184</v>
       </c>
       <c r="H23" t="n">
-        <v>543792.2484778526</v>
+        <v>622944.1676740673</v>
       </c>
       <c r="I23" t="n">
-        <v>737.4227067821091</v>
+        <v>789.2681215366977</v>
       </c>
     </row>
     <row r="24">
@@ -1167,25 +1167,25 @@
         <v>300</v>
       </c>
       <c r="C24" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D24" t="n">
-        <v>95173.625</v>
+        <v>96949.625</v>
       </c>
       <c r="E24" t="n">
-        <v>108594.3125</v>
+        <v>108903.6875</v>
       </c>
       <c r="F24" t="n">
-        <v>1059507117999.188</v>
+        <v>534602296708.375</v>
       </c>
       <c r="G24" t="n">
-        <v>106972.7832575529</v>
+        <v>107302.9945171285</v>
       </c>
       <c r="H24" t="n">
-        <v>718045.5007289799</v>
+        <v>781596.2986229055</v>
       </c>
       <c r="I24" t="n">
-        <v>847.37565502496</v>
+        <v>884.0793508633179</v>
       </c>
     </row>
     <row r="25">
@@ -1198,25 +1198,25 @@
         <v>250</v>
       </c>
       <c r="C25" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D25" t="n">
-        <v>101950.5625</v>
+        <v>104002.375</v>
       </c>
       <c r="E25" t="n">
-        <v>115556.1875</v>
+        <v>116044.6875</v>
       </c>
       <c r="F25" t="n">
-        <v>1127511967707.625</v>
+        <v>569205121193.125</v>
       </c>
       <c r="G25" t="n">
-        <v>113838.8702566292</v>
+        <v>114248.3194976341</v>
       </c>
       <c r="H25" t="n">
-        <v>807606.2457732505</v>
+        <v>849773.905442551</v>
       </c>
       <c r="I25" t="n">
-        <v>898.669152565754</v>
+        <v>921.8318205847263</v>
       </c>
     </row>
     <row r="26">
@@ -1229,25 +1229,25 @@
         <v>200</v>
       </c>
       <c r="C26" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D26" t="n">
-        <v>109531.375</v>
+        <v>111805.1875</v>
       </c>
       <c r="E26" t="n">
-        <v>123144.6875</v>
+        <v>123807.875</v>
       </c>
       <c r="F26" t="n">
-        <v>1201605377631.812</v>
+        <v>606881600534.3125</v>
       </c>
       <c r="G26" t="n">
-        <v>121319.6867098505</v>
+        <v>121810.5748060458</v>
       </c>
       <c r="H26" t="n">
-        <v>876553.8941034599</v>
+        <v>889130.3977627774</v>
       </c>
       <c r="I26" t="n">
-        <v>936.2445695989162</v>
+        <v>942.9371123053634</v>
       </c>
     </row>
     <row r="27">
@@ -1260,25 +1260,25 @@
         <v>150</v>
       </c>
       <c r="C27" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D27" t="n">
-        <v>118047.75</v>
+        <v>120537.125</v>
       </c>
       <c r="E27" t="n">
-        <v>131516.5625</v>
+        <v>132370.8125</v>
       </c>
       <c r="F27" t="n">
-        <v>1283308347025.375</v>
+        <v>648344143353.5</v>
       </c>
       <c r="G27" t="n">
-        <v>129568.7998002286</v>
+        <v>130132.7519313348</v>
       </c>
       <c r="H27" t="n">
-        <v>891515.1865617182</v>
+        <v>879791.3573342932</v>
       </c>
       <c r="I27" t="n">
-        <v>944.2008189795846</v>
+        <v>937.9719384578054</v>
       </c>
     </row>
     <row r="28">
@@ -1291,25 +1291,25 @@
         <v>100</v>
       </c>
       <c r="C28" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D28" t="n">
-        <v>127832.875</v>
+        <v>130436.8125</v>
       </c>
       <c r="E28" t="n">
-        <v>140910.1875</v>
+        <v>141954.375</v>
       </c>
       <c r="F28" t="n">
-        <v>1374969015143.625</v>
+        <v>694656951815</v>
       </c>
       <c r="G28" t="n">
-        <v>138823.2886255346</v>
+        <v>139428.4527972218</v>
       </c>
       <c r="H28" t="n">
-        <v>813139.4504046426</v>
+        <v>805283.9937372867</v>
       </c>
       <c r="I28" t="n">
-        <v>901.7424523691022</v>
+        <v>897.3761718127391</v>
       </c>
     </row>
     <row r="29">
@@ -1322,25 +1322,25 @@
         <v>1000</v>
       </c>
       <c r="C29" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D29" t="n">
-        <v>-2.018579483032227</v>
+        <v>-2.513562202453613</v>
       </c>
       <c r="E29" t="n">
-        <v>1.798852920532227</v>
+        <v>2.296822547912598</v>
       </c>
       <c r="F29" t="n">
-        <v>-2545.117341995239</v>
+        <v>-9155.868096351624</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0002569669246813929</v>
+        <v>-0.001837725109284928</v>
       </c>
       <c r="H29" t="n">
-        <v>0.003622592962962754</v>
+        <v>0.004210828631750718</v>
       </c>
       <c r="I29" t="n">
-        <v>0.06018798021999704</v>
+        <v>0.06489089791142297</v>
       </c>
     </row>
     <row r="30">
@@ -1353,25 +1353,25 @@
         <v>975</v>
       </c>
       <c r="C30" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D30" t="n">
-        <v>-2.665791511535645</v>
+        <v>-2.61563777923584</v>
       </c>
       <c r="E30" t="n">
-        <v>2.307659149169922</v>
+        <v>2.460256576538086</v>
       </c>
       <c r="F30" t="n">
-        <v>-10187.47474384308</v>
+        <v>-18490.38595867157</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.001028574994166067</v>
+        <v>-0.00371130800477133</v>
       </c>
       <c r="H30" t="n">
-        <v>0.008391431594142275</v>
+        <v>0.009749531070296984</v>
       </c>
       <c r="I30" t="n">
-        <v>0.09160475748640065</v>
+        <v>0.09873971374425279</v>
       </c>
     </row>
     <row r="31">
@@ -1384,25 +1384,25 @@
         <v>950</v>
       </c>
       <c r="C31" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D31" t="n">
-        <v>-4.483035087585449</v>
+        <v>-4.636687278747559</v>
       </c>
       <c r="E31" t="n">
-        <v>2.412403106689453</v>
+        <v>4.337244033813477</v>
       </c>
       <c r="F31" t="n">
-        <v>-21250.07687282562</v>
+        <v>-29804.87431049347</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.002145506933276555</v>
+        <v>-0.005982301767901271</v>
       </c>
       <c r="H31" t="n">
-        <v>0.01629225734534536</v>
+        <v>0.01903077855677252</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1276411271704593</v>
+        <v>0.1379520879029111</v>
       </c>
     </row>
     <row r="32">
@@ -1415,25 +1415,25 @@
         <v>925</v>
       </c>
       <c r="C32" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D32" t="n">
-        <v>-6.002691268920898</v>
+        <v>-6.511506080627441</v>
       </c>
       <c r="E32" t="n">
-        <v>2.613036155700684</v>
+        <v>5.372445106506348</v>
       </c>
       <c r="F32" t="n">
-        <v>-30916.20142173767</v>
+        <v>-41648.26327323914</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.003121443978667936</v>
+        <v>-0.008359454108544821</v>
       </c>
       <c r="H32" t="n">
-        <v>0.02425014423273291</v>
+        <v>0.0282148453336459</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1557245781266814</v>
+        <v>0.1679727517594622</v>
       </c>
     </row>
     <row r="33">
@@ -1446,25 +1446,25 @@
         <v>900</v>
       </c>
       <c r="C33" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D33" t="n">
-        <v>-7.213781356811523</v>
+        <v>-8.217581748962402</v>
       </c>
       <c r="E33" t="n">
-        <v>3.39769172668457</v>
+        <v>6.740886688232422</v>
       </c>
       <c r="F33" t="n">
-        <v>-37831.50194644928</v>
+        <v>-52614.06098651886</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.003819644992727925</v>
+        <v>-0.0105604602380524</v>
       </c>
       <c r="H33" t="n">
-        <v>0.03058255758319868</v>
+        <v>0.03575365390223927</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1748786939086597</v>
+        <v>0.1890863662516133</v>
       </c>
     </row>
     <row r="34">
@@ -1477,25 +1477,25 @@
         <v>875</v>
       </c>
       <c r="C34" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D34" t="n">
-        <v>-8.089030265808105</v>
+        <v>-9.723431587219238</v>
       </c>
       <c r="E34" t="n">
-        <v>4.389358520507812</v>
+        <v>7.983111381530762</v>
       </c>
       <c r="F34" t="n">
-        <v>-42149.72807216644</v>
+        <v>-63161.72490024567</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.004255633255153008</v>
+        <v>-0.01267754041161659</v>
       </c>
       <c r="H34" t="n">
-        <v>0.03500458133462445</v>
+        <v>0.04145497138110273</v>
       </c>
       <c r="I34" t="n">
-        <v>0.187095113069862</v>
+        <v>0.2036049394811008</v>
       </c>
     </row>
     <row r="35">
@@ -1508,25 +1508,25 @@
         <v>850</v>
       </c>
       <c r="C35" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D35" t="n">
-        <v>-9.663198471069336</v>
+        <v>-10.89955520629883</v>
       </c>
       <c r="E35" t="n">
-        <v>5.186410903930664</v>
+        <v>9.103950500488281</v>
       </c>
       <c r="F35" t="n">
-        <v>-44967.81840610504</v>
+        <v>-72811.02966499329</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.004540160807041402</v>
+        <v>-0.01461430593365209</v>
       </c>
       <c r="H35" t="n">
-        <v>0.03799295427840122</v>
+        <v>0.04567007106988402</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1949178141638194</v>
+        <v>0.2137055709846704</v>
       </c>
     </row>
     <row r="36">
@@ -1539,25 +1539,25 @@
         <v>825</v>
       </c>
       <c r="C36" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D36" t="n">
-        <v>-10.84944725036621</v>
+        <v>-11.7749605178833</v>
       </c>
       <c r="E36" t="n">
-        <v>5.845376968383789</v>
+        <v>10.00683498382568</v>
       </c>
       <c r="F36" t="n">
-        <v>-47130.8146314621</v>
+        <v>-82310.43229198456</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.004758547000462133</v>
+        <v>-0.01652098376552094</v>
       </c>
       <c r="H36" t="n">
-        <v>0.04013955172505033</v>
+        <v>0.04891611273158619</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2003485755503401</v>
+        <v>0.2211698730197813</v>
       </c>
     </row>
     <row r="37">
@@ -1570,25 +1570,25 @@
         <v>800</v>
       </c>
       <c r="C37" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D37" t="n">
-        <v>-11.63267517089844</v>
+        <v>-12.34621620178223</v>
       </c>
       <c r="E37" t="n">
-        <v>6.301895141601562</v>
+        <v>10.60941505432129</v>
       </c>
       <c r="F37" t="n">
-        <v>-48777.04995441437</v>
+        <v>-91282.20023727417</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.004924758601499451</v>
+        <v>-0.01832175711155751</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0416425576762125</v>
+        <v>0.05161534748845893</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2040650819621341</v>
+        <v>0.2271901130957484</v>
       </c>
     </row>
     <row r="38">
@@ -1601,25 +1601,25 @@
         <v>775</v>
       </c>
       <c r="C38" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D38" t="n">
-        <v>-12.10081577301025</v>
+        <v>-12.61206150054932</v>
       </c>
       <c r="E38" t="n">
-        <v>6.637953758239746</v>
+        <v>10.87205505371094</v>
       </c>
       <c r="F38" t="n">
-        <v>-49135.34728908539</v>
+        <v>-99936.11868095398</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.004960933972549249</v>
+        <v>-0.02005873311976277</v>
       </c>
       <c r="H38" t="n">
-        <v>0.04284451436138358</v>
+        <v>0.05387839660056626</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2069891648405384</v>
+        <v>0.2321172044475942</v>
       </c>
     </row>
     <row r="39">
@@ -1632,25 +1632,25 @@
         <v>750</v>
       </c>
       <c r="C39" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D39" t="n">
-        <v>-12.29857349395752</v>
+        <v>-14.06427955627441</v>
       </c>
       <c r="E39" t="n">
-        <v>6.95191478729248</v>
+        <v>10.86666965484619</v>
       </c>
       <c r="F39" t="n">
-        <v>-49356.79205036163</v>
+        <v>-108534.3553085327</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.004983292069110488</v>
+        <v>-0.02178453292157197</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0439999258187638</v>
+        <v>0.05620484044914634</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2097615928113719</v>
+        <v>0.237075600703966</v>
       </c>
     </row>
     <row r="40">
@@ -1663,25 +1663,25 @@
         <v>725</v>
       </c>
       <c r="C40" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D40" t="n">
-        <v>-13.4630069732666</v>
+        <v>-16.34870910644531</v>
       </c>
       <c r="E40" t="n">
-        <v>7.426641464233398</v>
+        <v>10.177734375</v>
       </c>
       <c r="F40" t="n">
-        <v>-48921.56094264984</v>
+        <v>-124799.9720954895</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.004939349105291446</v>
+        <v>-0.0250492951563302</v>
       </c>
       <c r="H40" t="n">
-        <v>0.04641202569741818</v>
+        <v>0.06055159974573696</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2154345044263295</v>
+        <v>0.2460723465685183</v>
       </c>
     </row>
     <row r="41">
@@ -1694,25 +1694,25 @@
         <v>700</v>
       </c>
       <c r="C41" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D41" t="n">
-        <v>-14.41956996917725</v>
+        <v>-17.37271118164062</v>
       </c>
       <c r="E41" t="n">
-        <v>7.039414405822754</v>
+        <v>9.009433746337891</v>
       </c>
       <c r="F41" t="n">
-        <v>-49406.89451408386</v>
+        <v>-137983.8543863297</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.004988350647671554</v>
+        <v>-0.02769550535385245</v>
       </c>
       <c r="H41" t="n">
-        <v>0.04848868350143795</v>
+        <v>0.06449274807842784</v>
       </c>
       <c r="I41" t="n">
-        <v>0.2202014611700793</v>
+        <v>0.2539542243760238</v>
       </c>
     </row>
     <row r="42">
@@ -1725,25 +1725,25 @@
         <v>650</v>
       </c>
       <c r="C42" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D42" t="n">
-        <v>-14.66117763519287</v>
+        <v>-17.17404174804688</v>
       </c>
       <c r="E42" t="n">
-        <v>5.498002052307129</v>
+        <v>7.450851440429688</v>
       </c>
       <c r="F42" t="n">
-        <v>-49743.17499542236</v>
+        <v>-148312.6796236038</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.005022303094458242</v>
+        <v>-0.02976866120190557</v>
       </c>
       <c r="H42" t="n">
-        <v>0.04790965919091781</v>
+        <v>0.06363812809201973</v>
       </c>
       <c r="I42" t="n">
-        <v>0.218882752154933</v>
+        <v>0.2522659867917586</v>
       </c>
     </row>
     <row r="43">
@@ -1756,25 +1756,25 @@
         <v>600</v>
       </c>
       <c r="C43" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D43" t="n">
-        <v>-14.94180870056152</v>
+        <v>-16.0579833984375</v>
       </c>
       <c r="E43" t="n">
-        <v>6.040891647338867</v>
+        <v>5.980673789978027</v>
       </c>
       <c r="F43" t="n">
-        <v>-51427.74940872192</v>
+        <v>-157555.3182020187</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.005192385588982109</v>
+        <v>-0.03162380249630307</v>
       </c>
       <c r="H43" t="n">
-        <v>0.04690278074480758</v>
+        <v>0.06084442147688311</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2165704983251587</v>
+        <v>0.2466666201107947</v>
       </c>
     </row>
     <row r="44">
@@ -1787,25 +1787,25 @@
         <v>550</v>
       </c>
       <c r="C44" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D44" t="n">
-        <v>-15.25595188140869</v>
+        <v>-16.49374389648438</v>
       </c>
       <c r="E44" t="n">
-        <v>6.178739547729492</v>
+        <v>4.244629859924316</v>
       </c>
       <c r="F44" t="n">
-        <v>-51414.62700843811</v>
+        <v>-163346.8405122757</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.005191060690208411</v>
+        <v>-0.03278625108758239</v>
       </c>
       <c r="H44" t="n">
-        <v>0.04604575138372741</v>
+        <v>0.060911333921046</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2145827378512247</v>
+        <v>0.2468022161996241</v>
       </c>
     </row>
     <row r="45">
@@ -1818,25 +1818,25 @@
         <v>500</v>
       </c>
       <c r="C45" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D45" t="n">
-        <v>-14.8433780670166</v>
+        <v>-16.76646423339844</v>
       </c>
       <c r="E45" t="n">
-        <v>5.498003005981445</v>
+        <v>3.349468231201172</v>
       </c>
       <c r="F45" t="n">
-        <v>-51868.24850749969</v>
+        <v>-164934.7663164139</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.005236860433764368</v>
+        <v>-0.03310497249021025</v>
       </c>
       <c r="H45" t="n">
-        <v>0.04495171849315378</v>
+        <v>0.06239337944935755</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2120182032117851</v>
+        <v>0.2497866678775262</v>
       </c>
     </row>
     <row r="46">
@@ -1849,25 +1849,25 @@
         <v>450</v>
       </c>
       <c r="C46" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D46" t="n">
-        <v>-14.42695903778076</v>
+        <v>-16.09329223632812</v>
       </c>
       <c r="E46" t="n">
-        <v>3.790817260742188</v>
+        <v>2.633770942687988</v>
       </c>
       <c r="F46" t="n">
-        <v>-52945.61805725098</v>
+        <v>-162592.312040329</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.005345636691494003</v>
+        <v>-0.03263480548963642</v>
       </c>
       <c r="H46" t="n">
-        <v>0.04164679652687933</v>
+        <v>0.06091105673338391</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2040754677242694</v>
+        <v>0.246801654640693</v>
       </c>
     </row>
     <row r="47">
@@ -1880,25 +1880,25 @@
         <v>400</v>
       </c>
       <c r="C47" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D47" t="n">
-        <v>-13.51175689697266</v>
+        <v>-14.54584121704102</v>
       </c>
       <c r="E47" t="n">
-        <v>2.974142074584961</v>
+        <v>2.079618453979492</v>
       </c>
       <c r="F47" t="n">
-        <v>-52356.18314743042</v>
+        <v>-156903.9416780472</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.005286124592158797</v>
+        <v>-0.03149306109842534</v>
       </c>
       <c r="H47" t="n">
-        <v>0.03573288526472417</v>
+        <v>0.0548843612545324</v>
       </c>
       <c r="I47" t="n">
-        <v>0.18903143988428</v>
+        <v>0.2342741156306697</v>
       </c>
     </row>
     <row r="48">
@@ -1911,25 +1911,25 @@
         <v>350</v>
       </c>
       <c r="C48" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D48" t="n">
-        <v>-11.9915885925293</v>
+        <v>-12.48834991455078</v>
       </c>
       <c r="E48" t="n">
-        <v>2.847209930419922</v>
+        <v>2.530440330505371</v>
       </c>
       <c r="F48" t="n">
-        <v>-45868.96747303009</v>
+        <v>-145301.3562393188</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.004631145022419724</v>
+        <v>-0.029164241769773</v>
       </c>
       <c r="H48" t="n">
-        <v>0.02806401425373653</v>
+        <v>0.04515986440773819</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1675231752735619</v>
+        <v>0.2125085043186229</v>
       </c>
     </row>
     <row r="49">
@@ -1942,25 +1942,25 @@
         <v>300</v>
       </c>
       <c r="C49" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D49" t="n">
-        <v>-10.08780384063721</v>
+        <v>-10.49493026733398</v>
       </c>
       <c r="E49" t="n">
-        <v>2.621424674987793</v>
+        <v>2.246088981628418</v>
       </c>
       <c r="F49" t="n">
-        <v>-32174.1876077652</v>
+        <v>-122634.6552715302</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.003248456134917587</v>
+        <v>-0.02461468239705152</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0198978685735314</v>
+        <v>0.03520365465202809</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1410598049535423</v>
+        <v>0.1876263698205241</v>
       </c>
     </row>
     <row r="50">
@@ -1973,25 +1973,25 @@
         <v>250</v>
       </c>
       <c r="C50" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D50" t="n">
-        <v>-9.601442337036133</v>
+        <v>-9.271552085876465</v>
       </c>
       <c r="E50" t="n">
-        <v>2.766477584838867</v>
+        <v>2.361527442932129</v>
       </c>
       <c r="F50" t="n">
-        <v>-24422.53395557404</v>
+        <v>-106397.6660022736</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.002465813005922479</v>
+        <v>-0.02135566615028047</v>
       </c>
       <c r="H50" t="n">
-        <v>0.01550333379751017</v>
+        <v>0.03039439249730426</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1245123841130278</v>
+        <v>0.1743398763831851</v>
       </c>
     </row>
     <row r="51">
@@ -2004,25 +2004,25 @@
         <v>200</v>
       </c>
       <c r="C51" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D51" t="n">
-        <v>-8.764391899108887</v>
+        <v>-7.878938674926758</v>
       </c>
       <c r="E51" t="n">
-        <v>3.319348335266113</v>
+        <v>2.189702033996582</v>
       </c>
       <c r="F51" t="n">
-        <v>-17577.10592746735</v>
+        <v>-87136.80856132507</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.001774666645208374</v>
+        <v>-0.01748971253746113</v>
       </c>
       <c r="H51" t="n">
-        <v>0.01069777299772647</v>
+        <v>0.02442640452583918</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1034300391459197</v>
+        <v>0.1562894894925413</v>
       </c>
     </row>
     <row r="52">
@@ -2035,25 +2035,25 @@
         <v>150</v>
       </c>
       <c r="C52" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D52" t="n">
-        <v>-7.643311500549316</v>
+        <v>-6.360499382019043</v>
       </c>
       <c r="E52" t="n">
-        <v>3.166014671325684</v>
+        <v>2.062668800354004</v>
       </c>
       <c r="F52" t="n">
-        <v>-12195.98041915894</v>
+        <v>-65500.81876564026</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.001231363100661162</v>
+        <v>-0.01314703292550748</v>
       </c>
       <c r="H52" t="n">
-        <v>0.006217648357252597</v>
+        <v>0.01687123734602653</v>
       </c>
       <c r="I52" t="n">
-        <v>0.07885206628397633</v>
+        <v>0.1298893272983833</v>
       </c>
     </row>
     <row r="53">
@@ -2066,25 +2066,25 @@
         <v>100</v>
       </c>
       <c r="C53" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D53" t="n">
-        <v>-6.201698303222656</v>
+        <v>-4.778258323669434</v>
       </c>
       <c r="E53" t="n">
-        <v>2.209678649902344</v>
+        <v>1.664827346801758</v>
       </c>
       <c r="F53" t="n">
-        <v>-7296.581416249275</v>
+        <v>-42632.93434327841</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.0007366969122732421</v>
+        <v>-0.00855709290486152</v>
       </c>
       <c r="H53" t="n">
-        <v>0.003006586844945881</v>
+        <v>0.009145443714609222</v>
       </c>
       <c r="I53" t="n">
-        <v>0.05483235217411233</v>
+        <v>0.09563181329771606</v>
       </c>
     </row>
     <row r="54">
@@ -2097,25 +2097,25 @@
         <v>1000</v>
       </c>
       <c r="C54" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D54" t="n">
-        <v>5.067600250244141</v>
+        <v>4.575157165527344</v>
       </c>
       <c r="E54" t="n">
-        <v>116.6183471679688</v>
+        <v>114.1811065673828</v>
       </c>
       <c r="F54" t="n">
-        <v>788589479.3050032</v>
+        <v>399119954.6571631</v>
       </c>
       <c r="G54" t="n">
-        <v>79.61967410675287</v>
+        <v>80.10958158980027</v>
       </c>
       <c r="H54" t="n">
-        <v>140.606027165696</v>
+        <v>112.189229489958</v>
       </c>
       <c r="I54" t="n">
-        <v>11.85774123371294</v>
+        <v>10.59194172425236</v>
       </c>
     </row>
     <row r="55">
@@ -2128,25 +2128,25 @@
         <v>975</v>
       </c>
       <c r="C55" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D55" t="n">
-        <v>5.196361541748047</v>
+        <v>4.613472938537598</v>
       </c>
       <c r="E55" t="n">
-        <v>116.6277618408203</v>
+        <v>114.2002334594727</v>
       </c>
       <c r="F55" t="n">
-        <v>835021803.2158451</v>
+        <v>426435932.4967527</v>
       </c>
       <c r="G55" t="n">
-        <v>84.30769822426825</v>
+        <v>85.59232313131366</v>
       </c>
       <c r="H55" t="n">
-        <v>163.5782981486893</v>
+        <v>130.5130240046693</v>
       </c>
       <c r="I55" t="n">
-        <v>12.78977318597516</v>
+        <v>11.42422968977205</v>
       </c>
     </row>
     <row r="56">
@@ -2159,25 +2159,25 @@
         <v>950</v>
       </c>
       <c r="C56" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D56" t="n">
-        <v>1.62249755859375</v>
+        <v>3.758903503417969</v>
       </c>
       <c r="E56" t="n">
-        <v>117.5825347900391</v>
+        <v>114.0754852294922</v>
       </c>
       <c r="F56" t="n">
-        <v>835802388.3034761</v>
+        <v>433342149.4187665</v>
       </c>
       <c r="G56" t="n">
-        <v>84.38650973763586</v>
+        <v>86.97850826572071</v>
       </c>
       <c r="H56" t="n">
-        <v>179.4135952790548</v>
+        <v>145.2809145854119</v>
       </c>
       <c r="I56" t="n">
-        <v>13.39453602328408</v>
+        <v>12.05325327807443</v>
       </c>
     </row>
     <row r="57">
@@ -2190,25 +2190,25 @@
         <v>925</v>
       </c>
       <c r="C57" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D57" t="n">
-        <v>0.09112149477005005</v>
+        <v>-0.9681915640830994</v>
       </c>
       <c r="E57" t="n">
-        <v>117.4900207519531</v>
+        <v>114.7192077636719</v>
       </c>
       <c r="F57" t="n">
-        <v>797110613.5747745</v>
+        <v>415862092.1244768</v>
       </c>
       <c r="G57" t="n">
-        <v>80.48000758999579</v>
+        <v>83.46998893545015</v>
       </c>
       <c r="H57" t="n">
-        <v>204.369187329616</v>
+        <v>169.7480904801403</v>
       </c>
       <c r="I57" t="n">
-        <v>14.29577515665436</v>
+        <v>13.02874093994275</v>
       </c>
     </row>
     <row r="58">
@@ -2221,25 +2221,25 @@
         <v>900</v>
       </c>
       <c r="C58" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.2024116516113281</v>
+        <v>-0.04389762878417969</v>
       </c>
       <c r="E58" t="n">
-        <v>117.3299407958984</v>
+        <v>114.0550155639648</v>
       </c>
       <c r="F58" t="n">
-        <v>758518382.7094388</v>
+        <v>397710447.0807335</v>
       </c>
       <c r="G58" t="n">
-        <v>76.58355585536411</v>
+        <v>79.82667150004427</v>
       </c>
       <c r="H58" t="n">
-        <v>256.7416559077095</v>
+        <v>202.6790711385388</v>
       </c>
       <c r="I58" t="n">
-        <v>16.02315998508751</v>
+        <v>14.23653999883886</v>
       </c>
     </row>
     <row r="59">
@@ -2252,25 +2252,25 @@
         <v>875</v>
       </c>
       <c r="C59" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.9581308364868164</v>
+        <v>-4.472452163696289</v>
       </c>
       <c r="E59" t="n">
-        <v>114.7705993652344</v>
+        <v>114.0908355712891</v>
       </c>
       <c r="F59" t="n">
-        <v>717247450.6439204</v>
+        <v>382910120.5655409</v>
       </c>
       <c r="G59" t="n">
-        <v>72.41664994630355</v>
+        <v>76.85601580946884</v>
       </c>
       <c r="H59" t="n">
-        <v>336.570999226416</v>
+        <v>245.4900627686449</v>
       </c>
       <c r="I59" t="n">
-        <v>18.34587144908674</v>
+        <v>15.66812250298819</v>
       </c>
     </row>
     <row r="60">
@@ -2283,25 +2283,25 @@
         <v>850</v>
       </c>
       <c r="C60" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D60" t="n">
-        <v>-3.572824478149414</v>
+        <v>-3.922420501708984</v>
       </c>
       <c r="E60" t="n">
-        <v>115.5573806762695</v>
+        <v>115.9544525146484</v>
       </c>
       <c r="F60" t="n">
-        <v>675139288.3842309</v>
+        <v>369488814.6291548</v>
       </c>
       <c r="G60" t="n">
-        <v>68.16521336956298</v>
+        <v>74.16215099412526</v>
       </c>
       <c r="H60" t="n">
-        <v>419.277882977458</v>
+        <v>301.1165631847878</v>
       </c>
       <c r="I60" t="n">
-        <v>20.47627610131925</v>
+        <v>17.3527105428745</v>
       </c>
     </row>
     <row r="61">
@@ -2314,25 +2314,25 @@
         <v>825</v>
       </c>
       <c r="C61" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D61" t="n">
-        <v>-5.618928909301758</v>
+        <v>-3.508291244506836</v>
       </c>
       <c r="E61" t="n">
-        <v>116.4183731079102</v>
+        <v>114.0113983154297</v>
       </c>
       <c r="F61" t="n">
-        <v>637129889.2165781</v>
+        <v>355986583.9467067</v>
       </c>
       <c r="G61" t="n">
-        <v>64.3276070431514</v>
+        <v>71.45204332379079</v>
       </c>
       <c r="H61" t="n">
-        <v>479.7062667121182</v>
+        <v>364.3996352289961</v>
       </c>
       <c r="I61" t="n">
-        <v>21.90219775986233</v>
+        <v>19.08925444403202</v>
       </c>
     </row>
     <row r="62">
@@ -2345,25 +2345,25 @@
         <v>800</v>
       </c>
       <c r="C62" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D62" t="n">
-        <v>-3.283346176147461</v>
+        <v>-5.777054786682129</v>
       </c>
       <c r="E62" t="n">
-        <v>116.4541397094727</v>
+        <v>127.7446060180664</v>
       </c>
       <c r="F62" t="n">
-        <v>605409706.1707394</v>
+        <v>342932057.9549736</v>
       </c>
       <c r="G62" t="n">
-        <v>61.12498932760446</v>
+        <v>68.83179694711109</v>
       </c>
       <c r="H62" t="n">
-        <v>514.3013910427478</v>
+        <v>428.9981747067345</v>
       </c>
       <c r="I62" t="n">
-        <v>22.67821401792363</v>
+        <v>20.71227111416646</v>
       </c>
     </row>
     <row r="63">
@@ -2376,25 +2376,25 @@
         <v>775</v>
       </c>
       <c r="C63" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D63" t="n">
-        <v>-5.978819847106934</v>
+        <v>-2.888693809509277</v>
       </c>
       <c r="E63" t="n">
-        <v>120.837776184082</v>
+        <v>113.8688507080078</v>
       </c>
       <c r="F63" t="n">
-        <v>577915154.0804738</v>
+        <v>330561569.7335046</v>
       </c>
       <c r="G63" t="n">
-        <v>58.34901103397174</v>
+        <v>66.34884758835331</v>
       </c>
       <c r="H63" t="n">
-        <v>535.9126250883144</v>
+        <v>483.3911793761364</v>
       </c>
       <c r="I63" t="n">
-        <v>23.14978671798758</v>
+        <v>21.98615881358398</v>
       </c>
     </row>
     <row r="64">
@@ -2407,25 +2407,25 @@
         <v>750</v>
       </c>
       <c r="C64" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D64" t="n">
-        <v>-5.913242340087891</v>
+        <v>-6.347699165344238</v>
       </c>
       <c r="E64" t="n">
-        <v>115.3855743408203</v>
+        <v>114.046630859375</v>
       </c>
       <c r="F64" t="n">
-        <v>552534237.0440724</v>
+        <v>318488383.9336515</v>
       </c>
       <c r="G64" t="n">
-        <v>55.78643519952108</v>
+        <v>63.92557144894597</v>
       </c>
       <c r="H64" t="n">
-        <v>543.2771864136471</v>
+        <v>526.9300209644225</v>
       </c>
       <c r="I64" t="n">
-        <v>23.30830724041639</v>
+        <v>22.95495634856278</v>
       </c>
     </row>
     <row r="65">
@@ -2438,25 +2438,25 @@
         <v>725</v>
       </c>
       <c r="C65" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D65" t="n">
-        <v>-6.19677734375</v>
+        <v>-2.02164363861084</v>
       </c>
       <c r="E65" t="n">
-        <v>112.7630233764648</v>
+        <v>114.2298889160156</v>
       </c>
       <c r="F65" t="n">
-        <v>509840291.6445113</v>
+        <v>297048995.1327813</v>
       </c>
       <c r="G65" t="n">
-        <v>51.47585522318095</v>
+        <v>59.62235271398145</v>
       </c>
       <c r="H65" t="n">
-        <v>540.5429482536663</v>
+        <v>567.0819232481621</v>
       </c>
       <c r="I65" t="n">
-        <v>23.24957952853484</v>
+        <v>23.81348196396659</v>
       </c>
     </row>
     <row r="66">
@@ -2469,25 +2469,25 @@
         <v>700</v>
       </c>
       <c r="C66" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D66" t="n">
-        <v>-9.847058296203613</v>
+        <v>-6.350820541381836</v>
       </c>
       <c r="E66" t="n">
-        <v>119.0913238525391</v>
+        <v>119.31689453125</v>
       </c>
       <c r="F66" t="n">
-        <v>485400263.5296825</v>
+        <v>284978732.6194952</v>
       </c>
       <c r="G66" t="n">
-        <v>49.00827592529642</v>
+        <v>57.19966332364785</v>
       </c>
       <c r="H66" t="n">
-        <v>596.7649932855552</v>
+        <v>627.4498571940811</v>
       </c>
       <c r="I66" t="n">
-        <v>24.42877388011022</v>
+        <v>25.04894922335229</v>
       </c>
     </row>
     <row r="67">
@@ -2500,25 +2500,25 @@
         <v>650</v>
       </c>
       <c r="C67" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D67" t="n">
-        <v>-9.189784049987793</v>
+        <v>-11.47881412506104</v>
       </c>
       <c r="E67" t="n">
-        <v>117.3552017211914</v>
+        <v>117.5105590820312</v>
       </c>
       <c r="F67" t="n">
-        <v>467880795.5822323</v>
+        <v>284955441.6283297</v>
       </c>
       <c r="G67" t="n">
-        <v>47.23942867954186</v>
+        <v>57.1949884595242</v>
       </c>
       <c r="H67" t="n">
-        <v>732.6056884215355</v>
+        <v>798.5530106349405</v>
       </c>
       <c r="I67" t="n">
-        <v>27.06668964652928</v>
+        <v>28.25868027058129</v>
       </c>
     </row>
     <row r="68">
@@ -2531,25 +2531,25 @@
         <v>600</v>
       </c>
       <c r="C68" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D68" t="n">
-        <v>-6.82654857635498</v>
+        <v>-11.69305992126465</v>
       </c>
       <c r="E68" t="n">
-        <v>132.5256805419922</v>
+        <v>118.1297988891602</v>
       </c>
       <c r="F68" t="n">
-        <v>426225859.3938842</v>
+        <v>275986961.7920065</v>
       </c>
       <c r="G68" t="n">
-        <v>43.03375192212842</v>
+        <v>55.39487508809052</v>
       </c>
       <c r="H68" t="n">
-        <v>791.3816306882889</v>
+        <v>904.9587544703326</v>
       </c>
       <c r="I68" t="n">
-        <v>28.13150601528985</v>
+        <v>30.0825323812729</v>
       </c>
     </row>
     <row r="69">
@@ -2562,25 +2562,25 @@
         <v>550</v>
       </c>
       <c r="C69" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D69" t="n">
-        <v>-5.642542839050293</v>
+        <v>-4.73216438293457</v>
       </c>
       <c r="E69" t="n">
-        <v>128.0203857421875</v>
+        <v>120.3573150634766</v>
       </c>
       <c r="F69" t="n">
-        <v>376152582.7525846</v>
+        <v>255977404.3343142</v>
       </c>
       <c r="G69" t="n">
-        <v>37.97812022494792</v>
+        <v>51.37864573892214</v>
       </c>
       <c r="H69" t="n">
-        <v>731.8469821666702</v>
+        <v>878.6435830701396</v>
       </c>
       <c r="I69" t="n">
-        <v>27.05267051820707</v>
+        <v>29.6419227289685</v>
       </c>
     </row>
     <row r="70">
@@ -2593,25 +2593,25 @@
         <v>500</v>
       </c>
       <c r="C70" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D70" t="n">
-        <v>-8.479220390319824</v>
+        <v>-9.983388900756836</v>
       </c>
       <c r="E70" t="n">
-        <v>133.5879058837891</v>
+        <v>133.2417755126953</v>
       </c>
       <c r="F70" t="n">
-        <v>352205976.3473574</v>
+        <v>242135404.6972444</v>
       </c>
       <c r="G70" t="n">
-        <v>35.56035908561936</v>
+        <v>48.60034115566895</v>
       </c>
       <c r="H70" t="n">
-        <v>706.7285190077654</v>
+        <v>869.5359906497538</v>
       </c>
       <c r="I70" t="n">
-        <v>26.58436606368046</v>
+        <v>29.48789566330147</v>
       </c>
     </row>
     <row r="71">
@@ -2624,25 +2624,25 @@
         <v>450</v>
       </c>
       <c r="C71" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D71" t="n">
-        <v>-10.94512271881104</v>
+        <v>-6.259783744812012</v>
       </c>
       <c r="E71" t="n">
-        <v>133.7244262695312</v>
+        <v>138.3233184814453</v>
       </c>
       <c r="F71" t="n">
-        <v>363179030.1803893</v>
+        <v>239993231.3398396</v>
       </c>
       <c r="G71" t="n">
-        <v>36.66824981085693</v>
+        <v>48.17037365003024</v>
       </c>
       <c r="H71" t="n">
-        <v>745.7641346622869</v>
+        <v>900.3394813136567</v>
       </c>
       <c r="I71" t="n">
-        <v>27.30868240436157</v>
+        <v>30.00565748844135</v>
       </c>
     </row>
     <row r="72">
@@ -2655,25 +2655,25 @@
         <v>400</v>
       </c>
       <c r="C72" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D72" t="n">
-        <v>-8.745258331298828</v>
+        <v>-8.60560131072998</v>
       </c>
       <c r="E72" t="n">
-        <v>133.2915802001953</v>
+        <v>140.9995422363281</v>
       </c>
       <c r="F72" t="n">
-        <v>398037181.6062763</v>
+        <v>248092331.0817825</v>
       </c>
       <c r="G72" t="n">
-        <v>40.18769145866931</v>
+        <v>49.79598891684498</v>
       </c>
       <c r="H72" t="n">
-        <v>802.7754258543857</v>
+        <v>953.0393651442098</v>
       </c>
       <c r="I72" t="n">
-        <v>28.33329182877248</v>
+        <v>30.8713356553326</v>
       </c>
     </row>
     <row r="73">
@@ -2686,25 +2686,25 @@
         <v>350</v>
       </c>
       <c r="C73" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D73" t="n">
-        <v>-5.27549934387207</v>
+        <v>-6.483906745910645</v>
       </c>
       <c r="E73" t="n">
-        <v>134.7029724121094</v>
+        <v>144.803466796875</v>
       </c>
       <c r="F73" t="n">
-        <v>455176111.9500782</v>
+        <v>263085893.1199887</v>
       </c>
       <c r="G73" t="n">
-        <v>45.95670452842477</v>
+        <v>52.80542998188307</v>
       </c>
       <c r="H73" t="n">
-        <v>857.248276339919</v>
+        <v>979.3004718728577</v>
       </c>
       <c r="I73" t="n">
-        <v>29.27880250863958</v>
+        <v>31.29377688731192</v>
       </c>
     </row>
     <row r="74">
@@ -2717,25 +2717,25 @@
         <v>300</v>
       </c>
       <c r="C74" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D74" t="n">
-        <v>-3.193296432495117</v>
+        <v>-8.464282035827637</v>
       </c>
       <c r="E74" t="n">
-        <v>149.8188629150391</v>
+        <v>167.2162017822266</v>
       </c>
       <c r="F74" t="n">
-        <v>542160537.4497203</v>
+        <v>293977538.5334855</v>
       </c>
       <c r="G74" t="n">
-        <v>54.73905807535306</v>
+        <v>59.00586361046849</v>
       </c>
       <c r="H74" t="n">
-        <v>900.8690202394084</v>
+        <v>1020.612184733157</v>
       </c>
       <c r="I74" t="n">
-        <v>30.01448017606516</v>
+        <v>31.94702153148486</v>
       </c>
     </row>
     <row r="75">
@@ -2748,25 +2748,25 @@
         <v>250</v>
       </c>
       <c r="C75" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D75" t="n">
-        <v>-5.87335205078125</v>
+        <v>-9.264033317565918</v>
       </c>
       <c r="E75" t="n">
-        <v>154.9700012207031</v>
+        <v>140.8383636474609</v>
       </c>
       <c r="F75" t="n">
-        <v>582965196.7388428</v>
+        <v>311824847.7967636</v>
       </c>
       <c r="G75" t="n">
-        <v>58.85888690885515</v>
+        <v>62.58809612202771</v>
       </c>
       <c r="H75" t="n">
-        <v>884.0042290190599</v>
+        <v>1033.761787464503</v>
       </c>
       <c r="I75" t="n">
-        <v>29.73220861320363</v>
+        <v>32.15216613953876</v>
       </c>
     </row>
     <row r="76">
@@ -2779,25 +2779,25 @@
         <v>200</v>
       </c>
       <c r="C76" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D76" t="n">
-        <v>-2.776803016662598</v>
+        <v>-8.033509254455566</v>
       </c>
       <c r="E76" t="n">
-        <v>142.6777648925781</v>
+        <v>142.59521484375</v>
       </c>
       <c r="F76" t="n">
-        <v>607928662.6627564</v>
+        <v>325101779.3529676</v>
       </c>
       <c r="G76" t="n">
-        <v>61.37931493078182</v>
+        <v>65.2529827541118</v>
       </c>
       <c r="H76" t="n">
-        <v>828.1461726687463</v>
+        <v>1025.154806076208</v>
       </c>
       <c r="I76" t="n">
-        <v>28.77752895348637</v>
+        <v>32.01803876061444</v>
       </c>
     </row>
     <row r="77">
@@ -2810,25 +2810,25 @@
         <v>150</v>
       </c>
       <c r="C77" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.261675834655762</v>
+        <v>-2.83782958984375</v>
       </c>
       <c r="E77" t="n">
-        <v>151.2321319580078</v>
+        <v>145.2798309326172</v>
       </c>
       <c r="F77" t="n">
-        <v>621660019.269586</v>
+        <v>334698930.4697342</v>
       </c>
       <c r="G77" t="n">
-        <v>62.76569677681254</v>
+        <v>67.17928022795986</v>
       </c>
       <c r="H77" t="n">
-        <v>794.2579538336554</v>
+        <v>995.8749692598813</v>
       </c>
       <c r="I77" t="n">
-        <v>28.18258245501386</v>
+        <v>31.557486738647</v>
       </c>
     </row>
     <row r="78">
@@ -2841,25 +2841,25 @@
         <v>100</v>
       </c>
       <c r="C78" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D78" t="n">
-        <v>-13.85577201843262</v>
+        <v>-0.8013095855712891</v>
       </c>
       <c r="E78" t="n">
-        <v>163.2067260742188</v>
+        <v>164.0784606933594</v>
       </c>
       <c r="F78" t="n">
-        <v>622995978.0552262</v>
+        <v>344405693.9567532</v>
       </c>
       <c r="G78" t="n">
-        <v>62.90058141061036</v>
+        <v>69.12757860909225</v>
       </c>
       <c r="H78" t="n">
-        <v>852.6120465842278</v>
+        <v>983.5600373773208</v>
       </c>
       <c r="I78" t="n">
-        <v>29.19952134169716</v>
+        <v>31.36176075059117</v>
       </c>
     </row>
     <row r="79">
@@ -2872,25 +2872,25 @@
         <v>1000</v>
       </c>
       <c r="C79" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D79" t="n">
-        <v>254.3196563720703</v>
+        <v>266.1596374511719</v>
       </c>
       <c r="E79" t="n">
-        <v>317.78955078125</v>
+        <v>319.6982116699219</v>
       </c>
       <c r="F79" t="n">
-        <v>2946632435.486938</v>
+        <v>1486485130.774231</v>
       </c>
       <c r="G79" t="n">
-        <v>297.5057623551161</v>
+        <v>298.3606819861267</v>
       </c>
       <c r="H79" t="n">
-        <v>10.47361501275375</v>
+        <v>10.67614558227715</v>
       </c>
       <c r="I79" t="n">
-        <v>3.236296496422068</v>
+        <v>3.267437158122119</v>
       </c>
     </row>
     <row r="80">
@@ -2903,25 +2903,25 @@
         <v>975</v>
       </c>
       <c r="C80" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D80" t="n">
-        <v>253.1016693115234</v>
+        <v>265.0053100585938</v>
       </c>
       <c r="E80" t="n">
-        <v>316.5765380859375</v>
+        <v>318.1322937011719</v>
       </c>
       <c r="F80" t="n">
-        <v>2928093826.634644</v>
+        <v>1476916299.231964</v>
       </c>
       <c r="G80" t="n">
-        <v>295.63401788737</v>
+        <v>296.4400686912763</v>
       </c>
       <c r="H80" t="n">
-        <v>10.44498327302808</v>
+        <v>10.08198263853366</v>
       </c>
       <c r="I80" t="n">
-        <v>3.231869934423117</v>
+        <v>3.175213794145784</v>
       </c>
     </row>
     <row r="81">
@@ -2934,25 +2934,25 @@
         <v>950</v>
       </c>
       <c r="C81" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D81" t="n">
-        <v>251.9278564453125</v>
+        <v>263.318603515625</v>
       </c>
       <c r="E81" t="n">
-        <v>314.1771240234375</v>
+        <v>316.5408935546875</v>
       </c>
       <c r="F81" t="n">
-        <v>2913503548.240021</v>
+        <v>1469291073.957367</v>
       </c>
       <c r="G81" t="n">
-        <v>294.160915289133</v>
+        <v>294.9095673992519</v>
       </c>
       <c r="H81" t="n">
-        <v>10.722842444887</v>
+        <v>9.883526839041242</v>
       </c>
       <c r="I81" t="n">
-        <v>3.274575154869255</v>
+        <v>3.143807697528785</v>
       </c>
     </row>
     <row r="82">
@@ -2965,25 +2965,25 @@
         <v>925</v>
       </c>
       <c r="C82" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D82" t="n">
-        <v>250.6466522216797</v>
+        <v>261.6773986816406</v>
       </c>
       <c r="E82" t="n">
-        <v>311.7510986328125</v>
+        <v>314.9103088378906</v>
       </c>
       <c r="F82" t="n">
-        <v>2901670959.49234</v>
+        <v>1463545798.281616</v>
       </c>
       <c r="G82" t="n">
-        <v>292.9662419075396</v>
+        <v>293.7564012266971</v>
       </c>
       <c r="H82" t="n">
-        <v>10.96182917689805</v>
+        <v>10.26219632696367</v>
       </c>
       <c r="I82" t="n">
-        <v>3.310865321467796</v>
+        <v>3.203466298708896</v>
       </c>
     </row>
     <row r="83">
@@ -2996,25 +2996,25 @@
         <v>900</v>
       </c>
       <c r="C83" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D83" t="n">
-        <v>249.2161865234375</v>
+        <v>260.2918701171875</v>
       </c>
       <c r="E83" t="n">
-        <v>309.3198547363281</v>
+        <v>313.2462158203125</v>
       </c>
       <c r="F83" t="n">
-        <v>2890517331.167633</v>
+        <v>1457947005.375092</v>
       </c>
       <c r="G83" t="n">
-        <v>291.8401195388983</v>
+        <v>292.6326364238699</v>
       </c>
       <c r="H83" t="n">
-        <v>10.74370414270511</v>
+        <v>10.38493112579185</v>
       </c>
       <c r="I83" t="n">
-        <v>3.277759012298664</v>
+        <v>3.222565922644849</v>
       </c>
     </row>
     <row r="84">
@@ -3027,25 +3027,25 @@
         <v>875</v>
       </c>
       <c r="C84" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D84" t="n">
-        <v>247.9276275634766</v>
+        <v>259.96142578125</v>
       </c>
       <c r="E84" t="n">
-        <v>306.8099365234375</v>
+        <v>311.5317993164062</v>
       </c>
       <c r="F84" t="n">
-        <v>2879879374.901581</v>
+        <v>1452190491.052185</v>
       </c>
       <c r="G84" t="n">
-        <v>290.7660618278929</v>
+        <v>291.4772144800582</v>
       </c>
       <c r="H84" t="n">
-        <v>10.30541099230571</v>
+        <v>10.1170855876287</v>
       </c>
       <c r="I84" t="n">
-        <v>3.210204197914162</v>
+        <v>3.180736642293526</v>
       </c>
     </row>
     <row r="85">
@@ -3058,25 +3058,25 @@
         <v>850</v>
       </c>
       <c r="C85" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D85" t="n">
-        <v>247.3075866699219</v>
+        <v>258.7708435058594</v>
       </c>
       <c r="E85" t="n">
-        <v>304.2629699707031</v>
+        <v>309.8024291992188</v>
       </c>
       <c r="F85" t="n">
-        <v>2869131315.764175</v>
+        <v>1446317228.645111</v>
       </c>
       <c r="G85" t="n">
-        <v>289.6808876171564</v>
+        <v>290.2983593802123</v>
       </c>
       <c r="H85" t="n">
-        <v>9.655725942591474</v>
+        <v>9.581875951977514</v>
       </c>
       <c r="I85" t="n">
-        <v>3.107366399797661</v>
+        <v>3.095460539560715</v>
       </c>
     </row>
     <row r="86">
@@ -3089,25 +3089,25 @@
         <v>825</v>
       </c>
       <c r="C86" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D86" t="n">
-        <v>247.0019073486328</v>
+        <v>257.1343383789062</v>
       </c>
       <c r="E86" t="n">
-        <v>302.1187133789062</v>
+        <v>308.1824340820312</v>
       </c>
       <c r="F86" t="n">
-        <v>2857589458.447571</v>
+        <v>1440351633.405121</v>
       </c>
       <c r="G86" t="n">
-        <v>288.5155678376628</v>
+        <v>289.1009716449379</v>
       </c>
       <c r="H86" t="n">
-        <v>8.730867258283723</v>
+        <v>8.923311309812554</v>
       </c>
       <c r="I86" t="n">
-        <v>2.954804098122873</v>
+        <v>2.987191207440956</v>
       </c>
     </row>
     <row r="87">
@@ -3120,25 +3120,25 @@
         <v>800</v>
       </c>
       <c r="C87" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D87" t="n">
-        <v>246.7183990478516</v>
+        <v>255.6154327392578</v>
       </c>
       <c r="E87" t="n">
-        <v>300.1513977050781</v>
+        <v>305.44287109375</v>
       </c>
       <c r="F87" t="n">
-        <v>2844960479.480789</v>
+        <v>1434223222.095306</v>
       </c>
       <c r="G87" t="n">
-        <v>287.2404871828671</v>
+        <v>287.8709041925076</v>
       </c>
       <c r="H87" t="n">
-        <v>7.793389339404394</v>
+        <v>8.290608478849332</v>
       </c>
       <c r="I87" t="n">
-        <v>2.791664259792784</v>
+        <v>2.879341674558498</v>
       </c>
     </row>
     <row r="88">
@@ -3151,25 +3151,25 @@
         <v>775</v>
       </c>
       <c r="C88" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D88" t="n">
-        <v>245.77685546875</v>
+        <v>254.1870269775391</v>
       </c>
       <c r="E88" t="n">
-        <v>297.8041381835938</v>
+        <v>302.618896484375</v>
       </c>
       <c r="F88" t="n">
-        <v>2831397659.48967</v>
+        <v>1427809408.314102</v>
       </c>
       <c r="G88" t="n">
-        <v>285.8711215801037</v>
+        <v>286.5835520257934</v>
       </c>
       <c r="H88" t="n">
-        <v>6.984014800767743</v>
+        <v>7.807563733152138</v>
       </c>
       <c r="I88" t="n">
-        <v>2.642728665748291</v>
+        <v>2.794201806089198</v>
       </c>
     </row>
     <row r="89">
@@ -3182,25 +3182,25 @@
         <v>750</v>
       </c>
       <c r="C89" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D89" t="n">
-        <v>244.6638641357422</v>
+        <v>252.6962585449219</v>
       </c>
       <c r="E89" t="n">
-        <v>297.671630859375</v>
+        <v>300.5802001953125</v>
       </c>
       <c r="F89" t="n">
-        <v>2817037931.251205</v>
+        <v>1421102048.451553</v>
       </c>
       <c r="G89" t="n">
-        <v>284.4212964015895</v>
+        <v>285.2372805956338</v>
       </c>
       <c r="H89" t="n">
-        <v>6.28295059186824</v>
+        <v>7.450949357434158</v>
       </c>
       <c r="I89" t="n">
-        <v>2.506581455262972</v>
+        <v>2.729642716077355</v>
       </c>
     </row>
     <row r="90">
@@ -3213,25 +3213,25 @@
         <v>725</v>
       </c>
       <c r="C90" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D90" t="n">
-        <v>241.5117797851562</v>
+        <v>250.8626556396484</v>
       </c>
       <c r="E90" t="n">
-        <v>294.9127807617188</v>
+        <v>298.2769775390625</v>
       </c>
       <c r="F90" t="n">
-        <v>2785567990.744934</v>
+        <v>1406400943.787399</v>
       </c>
       <c r="G90" t="n">
-        <v>281.2439443406974</v>
+        <v>282.2865402735541</v>
       </c>
       <c r="H90" t="n">
-        <v>5.183560536247198</v>
+        <v>6.89891990721791</v>
       </c>
       <c r="I90" t="n">
-        <v>2.276743405886398</v>
+        <v>2.62657950711908</v>
       </c>
     </row>
     <row r="91">
@@ -3244,25 +3244,25 @@
         <v>700</v>
       </c>
       <c r="C91" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D91" t="n">
-        <v>239.3909912109375</v>
+        <v>246.3679504394531</v>
       </c>
       <c r="E91" t="n">
-        <v>292.1351928710938</v>
+        <v>292.3034057617188</v>
       </c>
       <c r="F91" t="n">
-        <v>2750267628.544312</v>
+        <v>1389501358.422272</v>
       </c>
       <c r="G91" t="n">
-        <v>277.6798550293093</v>
+        <v>278.8945306863511</v>
       </c>
       <c r="H91" t="n">
-        <v>4.577352300679132</v>
+        <v>6.593295170514883</v>
       </c>
       <c r="I91" t="n">
-        <v>2.139474772153</v>
+        <v>2.56774125848281</v>
       </c>
     </row>
     <row r="92">
@@ -3275,25 +3275,25 @@
         <v>650</v>
       </c>
       <c r="C92" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D92" t="n">
-        <v>238.0354156494141</v>
+        <v>242.1678314208984</v>
       </c>
       <c r="E92" t="n">
-        <v>288.7566223144531</v>
+        <v>289.1287841796875</v>
       </c>
       <c r="F92" t="n">
-        <v>2713834135.602066</v>
+        <v>1371167585.716873</v>
       </c>
       <c r="G92" t="n">
-        <v>274.0013595500276</v>
+        <v>275.2146573969941</v>
       </c>
       <c r="H92" t="n">
-        <v>4.409659398916618</v>
+        <v>6.373948373811361</v>
       </c>
       <c r="I92" t="n">
-        <v>2.099918902938068</v>
+        <v>2.524667972984044</v>
       </c>
     </row>
     <row r="93">
@@ -3306,25 +3306,25 @@
         <v>600</v>
       </c>
       <c r="C93" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D93" t="n">
-        <v>234.7569122314453</v>
+        <v>238.1876983642578</v>
       </c>
       <c r="E93" t="n">
-        <v>283.3309326171875</v>
+        <v>286.1202392578125</v>
       </c>
       <c r="F93" t="n">
-        <v>2676915473.054916</v>
+        <v>1353516675.824753</v>
       </c>
       <c r="G93" t="n">
-        <v>270.2738790831924</v>
+        <v>271.6718452934208</v>
       </c>
       <c r="H93" t="n">
-        <v>5.008298228264893</v>
+        <v>6.541531227032552</v>
       </c>
       <c r="I93" t="n">
-        <v>2.23792274850248</v>
+        <v>2.557641731562994</v>
       </c>
     </row>
     <row r="94">
@@ -3337,25 +3337,25 @@
         <v>550</v>
       </c>
       <c r="C94" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D94" t="n">
-        <v>231.8300323486328</v>
+        <v>233.5069885253906</v>
       </c>
       <c r="E94" t="n">
-        <v>279.7101440429688</v>
+        <v>278.8964233398438</v>
       </c>
       <c r="F94" t="n">
-        <v>2635290789.360687</v>
+        <v>1333064825.25267</v>
       </c>
       <c r="G94" t="n">
-        <v>266.0712567587726</v>
+        <v>267.5668408381219</v>
       </c>
       <c r="H94" t="n">
-        <v>5.856825407494704</v>
+        <v>6.991214544423778</v>
       </c>
       <c r="I94" t="n">
-        <v>2.420087892514382</v>
+        <v>2.644090494749334</v>
       </c>
     </row>
     <row r="95">
@@ -3368,25 +3368,25 @@
         <v>500</v>
       </c>
       <c r="C95" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D95" t="n">
-        <v>228.6268768310547</v>
+        <v>231.5751190185547</v>
       </c>
       <c r="E95" t="n">
-        <v>276.3261108398438</v>
+        <v>273.7361450195312</v>
       </c>
       <c r="F95" t="n">
-        <v>2586434360.782028</v>
+        <v>1309449350.041702</v>
       </c>
       <c r="G95" t="n">
-        <v>261.1384837209135</v>
+        <v>262.8268477204636</v>
       </c>
       <c r="H95" t="n">
-        <v>6.899376076590056</v>
+        <v>7.535707967853172</v>
       </c>
       <c r="I95" t="n">
-        <v>2.626666342836497</v>
+        <v>2.745124399340251</v>
       </c>
     </row>
     <row r="96">
@@ -3399,25 +3399,25 @@
         <v>450</v>
       </c>
       <c r="C96" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D96" t="n">
-        <v>225.0690765380859</v>
+        <v>230.4542236328125</v>
       </c>
       <c r="E96" t="n">
-        <v>270.71875</v>
+        <v>268.59912109375</v>
       </c>
       <c r="F96" t="n">
-        <v>2527744478.127563</v>
+        <v>1281500457.567093</v>
       </c>
       <c r="G96" t="n">
-        <v>255.2128792677195</v>
+        <v>257.217070369285</v>
       </c>
       <c r="H96" t="n">
-        <v>7.705515311810009</v>
+        <v>7.936077219778411</v>
       </c>
       <c r="I96" t="n">
-        <v>2.775880997415057</v>
+        <v>2.817104403421785</v>
       </c>
     </row>
     <row r="97">
@@ -3430,25 +3430,25 @@
         <v>400</v>
       </c>
       <c r="C97" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D97" t="n">
-        <v>221.6041412353516</v>
+        <v>223.7515258789062</v>
       </c>
       <c r="E97" t="n">
-        <v>263.681640625</v>
+        <v>264.6561279296875</v>
       </c>
       <c r="F97" t="n">
-        <v>2457732863.997284</v>
+        <v>1247902982.883347</v>
       </c>
       <c r="G97" t="n">
-        <v>248.1441799672258</v>
+        <v>250.4735347279743</v>
       </c>
       <c r="H97" t="n">
-        <v>8.092607266499595</v>
+        <v>7.949329974740023</v>
       </c>
       <c r="I97" t="n">
-        <v>2.844750826785994</v>
+        <v>2.819455616735263</v>
       </c>
     </row>
     <row r="98">
@@ -3461,25 +3461,25 @@
         <v>350</v>
       </c>
       <c r="C98" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D98" t="n">
-        <v>216.7074432373047</v>
+        <v>217.1015014648438</v>
       </c>
       <c r="E98" t="n">
-        <v>255.7990875244141</v>
+        <v>256.788818359375</v>
       </c>
       <c r="F98" t="n">
-        <v>2374541560.531219</v>
+        <v>1207311285.648758</v>
       </c>
       <c r="G98" t="n">
-        <v>239.7447977229657</v>
+        <v>242.326149853981</v>
       </c>
       <c r="H98" t="n">
-        <v>7.722623300677319</v>
+        <v>7.101187172741607</v>
       </c>
       <c r="I98" t="n">
-        <v>2.778960831080085</v>
+        <v>2.664805278578832</v>
       </c>
     </row>
     <row r="99">
@@ -3492,25 +3492,25 @@
         <v>300</v>
       </c>
       <c r="C99" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D99" t="n">
-        <v>209.8344573974609</v>
+        <v>211.1538696289062</v>
       </c>
       <c r="E99" t="n">
-        <v>245.8572235107422</v>
+        <v>246.5374145507812</v>
       </c>
       <c r="F99" t="n">
-        <v>2276344154.098923</v>
+        <v>1158273608.929565</v>
       </c>
       <c r="G99" t="n">
-        <v>229.8303292911035</v>
+        <v>232.483525554515</v>
       </c>
       <c r="H99" t="n">
-        <v>6.110700129219928</v>
+        <v>5.122165031856394</v>
       </c>
       <c r="I99" t="n">
-        <v>2.471983035787246</v>
+        <v>2.263220058203884</v>
       </c>
     </row>
     <row r="100">
@@ -3523,25 +3523,25 @@
         <v>250</v>
       </c>
       <c r="C100" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D100" t="n">
-        <v>206.8453216552734</v>
+        <v>207.8876495361328</v>
       </c>
       <c r="E100" t="n">
-        <v>239.6231536865234</v>
+        <v>240.4794158935547</v>
       </c>
       <c r="F100" t="n">
-        <v>2221121307.007431</v>
+        <v>1129986389.432144</v>
       </c>
       <c r="G100" t="n">
-        <v>224.25477292869</v>
+        <v>226.8058407085552</v>
       </c>
       <c r="H100" t="n">
-        <v>4.74228599998435</v>
+        <v>3.984294226583815</v>
       </c>
       <c r="I100" t="n">
-        <v>2.177679039708182</v>
+        <v>1.996069694821254</v>
       </c>
     </row>
     <row r="101">
@@ -3554,25 +3554,25 @@
         <v>200</v>
       </c>
       <c r="C101" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D101" t="n">
-        <v>203.9869079589844</v>
+        <v>208.3517303466797</v>
       </c>
       <c r="E101" t="n">
-        <v>235.3334808349609</v>
+        <v>235.2235260009766</v>
       </c>
       <c r="F101" t="n">
-        <v>2162443892.994141</v>
+        <v>1098849553.893738</v>
       </c>
       <c r="G101" t="n">
-        <v>218.3304273676994</v>
+        <v>220.5561936089631</v>
       </c>
       <c r="H101" t="n">
-        <v>3.456563859657978</v>
+        <v>3.551747006741866</v>
       </c>
       <c r="I101" t="n">
-        <v>1.85918365409606</v>
+        <v>1.884607918571358</v>
       </c>
     </row>
     <row r="102">
@@ -3585,25 +3585,25 @@
         <v>150</v>
       </c>
       <c r="C102" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D102" t="n">
-        <v>199.7282409667969</v>
+        <v>203.334228515625</v>
       </c>
       <c r="E102" t="n">
-        <v>231.5911560058594</v>
+        <v>233.3539886474609</v>
       </c>
       <c r="F102" t="n">
-        <v>2101854445.244751</v>
+        <v>1064885822.281677</v>
       </c>
       <c r="G102" t="n">
-        <v>212.2130339574209</v>
+        <v>213.7391445065012</v>
       </c>
       <c r="H102" t="n">
-        <v>3.727950877535779</v>
+        <v>4.887157032092421</v>
       </c>
       <c r="I102" t="n">
-        <v>1.930790221006875</v>
+        <v>2.210691528027468</v>
       </c>
     </row>
     <row r="103">
@@ -3616,25 +3616,25 @@
         <v>100</v>
       </c>
       <c r="C103" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D103" t="n">
-        <v>197.5082550048828</v>
+        <v>196.3067474365234</v>
       </c>
       <c r="E103" t="n">
-        <v>228.7249298095703</v>
+        <v>232.0498962402344</v>
       </c>
       <c r="F103" t="n">
-        <v>2042909904.433975</v>
+        <v>1028806784.473999</v>
       </c>
       <c r="G103" t="n">
-        <v>206.2617180282992</v>
+        <v>206.4975205555798</v>
       </c>
       <c r="H103" t="n">
-        <v>7.957001502644427</v>
+        <v>9.249405445245944</v>
       </c>
       <c r="I103" t="n">
-        <v>2.820815751275582</v>
+        <v>3.041283519378939</v>
       </c>
     </row>
     <row r="104">
@@ -3647,25 +3647,25 @@
         <v>1000</v>
       </c>
       <c r="C104" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D104" t="n">
-        <v>-38.69720458984375</v>
+        <v>-31.76536560058594</v>
       </c>
       <c r="E104" t="n">
-        <v>30.55911254882812</v>
+        <v>30.84010314941406</v>
       </c>
       <c r="F104" t="n">
-        <v>-28485397.36917114</v>
+        <v>-8472865.945755005</v>
       </c>
       <c r="G104" t="n">
-        <v>-2.876018657177108</v>
+        <v>-1.700635956335339</v>
       </c>
       <c r="H104" t="n">
-        <v>20.81096202419509</v>
+        <v>24.5355857095112</v>
       </c>
       <c r="I104" t="n">
-        <v>4.561903333499636</v>
+        <v>4.953340863448749</v>
       </c>
     </row>
     <row r="105">
@@ -3678,25 +3678,25 @@
         <v>975</v>
       </c>
       <c r="C105" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D105" t="n">
-        <v>-44.34205627441406</v>
+        <v>-37.4046630859375</v>
       </c>
       <c r="E105" t="n">
-        <v>36.06578063964844</v>
+        <v>33.95054626464844</v>
       </c>
       <c r="F105" t="n">
-        <v>-30828405.46591187</v>
+        <v>-8679038.375976562</v>
       </c>
       <c r="G105" t="n">
-        <v>-3.112579689231937</v>
+        <v>-1.742017969255711</v>
       </c>
       <c r="H105" t="n">
-        <v>24.87714970616775</v>
+        <v>29.98992263310273</v>
       </c>
       <c r="I105" t="n">
-        <v>4.987699841226188</v>
+        <v>5.476305564256137</v>
       </c>
     </row>
     <row r="106">
@@ -3709,25 +3709,25 @@
         <v>950</v>
       </c>
       <c r="C106" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D106" t="n">
-        <v>-55.7569580078125</v>
+        <v>-50.18016052246094</v>
       </c>
       <c r="E106" t="n">
-        <v>46.89558410644531</v>
+        <v>47.136474609375</v>
       </c>
       <c r="F106" t="n">
-        <v>-32300441.23620605</v>
+        <v>-8445603.502441406</v>
       </c>
       <c r="G106" t="n">
-        <v>-3.26120329045931</v>
+        <v>-1.695163960005704</v>
       </c>
       <c r="H106" t="n">
-        <v>27.89172639003009</v>
+        <v>34.05022368190922</v>
       </c>
       <c r="I106" t="n">
-        <v>5.281261817977791</v>
+        <v>5.835256950804243</v>
       </c>
     </row>
     <row r="107">
@@ -3740,25 +3740,25 @@
         <v>925</v>
       </c>
       <c r="C107" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D107" t="n">
-        <v>-61.9556884765625</v>
+        <v>-55.93026733398438</v>
       </c>
       <c r="E107" t="n">
-        <v>51.88597106933594</v>
+        <v>52.02481079101562</v>
       </c>
       <c r="F107" t="n">
-        <v>-32347670.70326233</v>
+        <v>-7778543.360626221</v>
       </c>
       <c r="G107" t="n">
-        <v>-3.265971797868959</v>
+        <v>-1.561274616131756</v>
       </c>
       <c r="H107" t="n">
-        <v>29.44244765134103</v>
+        <v>37.07660829436866</v>
       </c>
       <c r="I107" t="n">
-        <v>5.426089535875817</v>
+        <v>6.089056437114757</v>
       </c>
     </row>
     <row r="108">
@@ -3771,25 +3771,25 @@
         <v>900</v>
       </c>
       <c r="C108" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D108" t="n">
-        <v>-62.35000610351562</v>
+        <v>-59.71502685546875</v>
       </c>
       <c r="E108" t="n">
-        <v>51.50082397460938</v>
+        <v>53.48114013671875</v>
       </c>
       <c r="F108" t="n">
-        <v>-31893965.07331848</v>
+        <v>-7046405.716094971</v>
       </c>
       <c r="G108" t="n">
-        <v>-3.220163560066508</v>
+        <v>-1.414323205446409</v>
       </c>
       <c r="H108" t="n">
-        <v>30.12949181280628</v>
+        <v>39.06854584521029</v>
       </c>
       <c r="I108" t="n">
-        <v>5.489033777706809</v>
+        <v>6.250483648903522</v>
       </c>
     </row>
     <row r="109">
@@ -3802,25 +3802,25 @@
         <v>875</v>
       </c>
       <c r="C109" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D109" t="n">
-        <v>-63.30732727050781</v>
+        <v>-58.30183410644531</v>
       </c>
       <c r="E109" t="n">
-        <v>51.68013000488281</v>
+        <v>51.97718811035156</v>
       </c>
       <c r="F109" t="n">
-        <v>-31132721.64068604</v>
+        <v>-6229117.473953247</v>
       </c>
       <c r="G109" t="n">
-        <v>-3.143304870453351</v>
+        <v>-1.250280745648889</v>
       </c>
       <c r="H109" t="n">
-        <v>30.61963203249524</v>
+        <v>40.15471748670822</v>
       </c>
       <c r="I109" t="n">
-        <v>5.533500883933717</v>
+        <v>6.336775006792353</v>
       </c>
     </row>
     <row r="110">
@@ -3833,25 +3833,25 @@
         <v>850</v>
       </c>
       <c r="C110" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D110" t="n">
-        <v>-63.0902099609375</v>
+        <v>-54.81388854980469</v>
       </c>
       <c r="E110" t="n">
-        <v>50.84359741210938</v>
+        <v>49.75730895996094</v>
       </c>
       <c r="F110" t="n">
-        <v>-30294053.06414795</v>
+        <v>-5354265.768386841</v>
       </c>
       <c r="G110" t="n">
-        <v>-3.058628976975302</v>
+        <v>-1.074684403576118</v>
       </c>
       <c r="H110" t="n">
-        <v>31.36525652958391</v>
+        <v>40.86131654191145</v>
       </c>
       <c r="I110" t="n">
-        <v>5.600469313332939</v>
+        <v>6.392285705591659</v>
       </c>
     </row>
     <row r="111">
@@ -3864,25 +3864,25 @@
         <v>825</v>
       </c>
       <c r="C111" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D111" t="n">
-        <v>-62.351318359375</v>
+        <v>-54.06510925292969</v>
       </c>
       <c r="E111" t="n">
-        <v>50.95205688476562</v>
+        <v>47.75399780273438</v>
       </c>
       <c r="F111" t="n">
-        <v>-29476024.06838989</v>
+        <v>-4454173.267211914</v>
       </c>
       <c r="G111" t="n">
-        <v>-2.976036951895874</v>
+        <v>-0.8940218413066418</v>
       </c>
       <c r="H111" t="n">
-        <v>32.54356938871108</v>
+        <v>41.57173400085171</v>
       </c>
       <c r="I111" t="n">
-        <v>5.704697133828498</v>
+        <v>6.44761459772928</v>
       </c>
     </row>
     <row r="112">
@@ -3895,25 +3895,25 @@
         <v>800</v>
       </c>
       <c r="C112" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D112" t="n">
-        <v>-61.39985656738281</v>
+        <v>-53.60504150390625</v>
       </c>
       <c r="E112" t="n">
-        <v>50.50736999511719</v>
+        <v>46.82339477539062</v>
       </c>
       <c r="F112" t="n">
-        <v>-28722261.02346802</v>
+        <v>-3621838.827392578</v>
       </c>
       <c r="G112" t="n">
-        <v>-2.899933517136269</v>
+        <v>-0.726959375652718</v>
       </c>
       <c r="H112" t="n">
-        <v>34.17599223637693</v>
+        <v>42.49279241742693</v>
       </c>
       <c r="I112" t="n">
-        <v>5.846023626053604</v>
+        <v>6.518649585414677</v>
       </c>
     </row>
     <row r="113">
@@ -3926,25 +3926,25 @@
         <v>775</v>
       </c>
       <c r="C113" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D113" t="n">
-        <v>-60.44361877441406</v>
+        <v>-53.11727905273438</v>
       </c>
       <c r="E113" t="n">
-        <v>49.86827087402344</v>
+        <v>46.38627624511719</v>
       </c>
       <c r="F113" t="n">
-        <v>-28023921.97550964</v>
+        <v>-2929940.190200806</v>
       </c>
       <c r="G113" t="n">
-        <v>-2.829425947768919</v>
+        <v>-0.5880845594947591</v>
       </c>
       <c r="H113" t="n">
-        <v>36.17797611460743</v>
+        <v>43.62604164905453</v>
       </c>
       <c r="I113" t="n">
-        <v>6.014813057328335</v>
+        <v>6.605001260337088</v>
       </c>
     </row>
     <row r="114">
@@ -3957,25 +3957,25 @@
         <v>750</v>
       </c>
       <c r="C114" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D114" t="n">
-        <v>-59.44984436035156</v>
+        <v>-52.48780822753906</v>
       </c>
       <c r="E114" t="n">
-        <v>50.59733581542969</v>
+        <v>46.07655334472656</v>
       </c>
       <c r="F114" t="n">
-        <v>-27282928.5418396</v>
+        <v>-2354124.198394775</v>
       </c>
       <c r="G114" t="n">
-        <v>-2.754611792555941</v>
+        <v>-0.472509335459869</v>
       </c>
       <c r="H114" t="n">
-        <v>38.35974345009902</v>
+        <v>45.06954987890392</v>
       </c>
       <c r="I114" t="n">
-        <v>6.193524315775229</v>
+        <v>6.713385872933562</v>
       </c>
     </row>
     <row r="115">
@@ -3988,25 +3988,25 @@
         <v>725</v>
       </c>
       <c r="C115" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D115" t="n">
-        <v>-57.47085571289062</v>
+        <v>-51.1328125</v>
       </c>
       <c r="E115" t="n">
-        <v>53.33103942871094</v>
+        <v>45.76243591308594</v>
       </c>
       <c r="F115" t="n">
-        <v>-25333419.78370667</v>
+        <v>-1437671.729751587</v>
       </c>
       <c r="G115" t="n">
-        <v>-2.557780290152926</v>
+        <v>-0.2885630733066565</v>
       </c>
       <c r="H115" t="n">
-        <v>42.79226711108313</v>
+        <v>48.59533275944592</v>
       </c>
       <c r="I115" t="n">
-        <v>6.541579863540851</v>
+        <v>6.971035271711507</v>
       </c>
     </row>
     <row r="116">
@@ -4019,25 +4019,25 @@
         <v>700</v>
       </c>
       <c r="C116" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D116" t="n">
-        <v>-55.18896484375</v>
+        <v>-50.26580810546875</v>
       </c>
       <c r="E116" t="n">
-        <v>53.3035888671875</v>
+        <v>46.11174011230469</v>
       </c>
       <c r="F116" t="n">
-        <v>-23018280.27198792</v>
+        <v>-1038868.840560913</v>
       </c>
       <c r="G116" t="n">
-        <v>-2.324033000502087</v>
+        <v>-0.208517131686645</v>
       </c>
       <c r="H116" t="n">
-        <v>46.95038988771768</v>
+        <v>53.96039733436345</v>
       </c>
       <c r="I116" t="n">
-        <v>6.852035455812942</v>
+        <v>7.345774114030696</v>
       </c>
     </row>
     <row r="117">
@@ -4050,25 +4050,25 @@
         <v>650</v>
       </c>
       <c r="C117" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D117" t="n">
-        <v>-52.69477844238281</v>
+        <v>-49.36032104492188</v>
       </c>
       <c r="E117" t="n">
-        <v>56.28604125976562</v>
+        <v>50.21888732910156</v>
       </c>
       <c r="F117" t="n">
-        <v>-20272360.38645935</v>
+        <v>-722361.0037841797</v>
       </c>
       <c r="G117" t="n">
-        <v>-2.046792113898176</v>
+        <v>-0.1449890868514619</v>
       </c>
       <c r="H117" t="n">
-        <v>49.88764361165846</v>
+        <v>61.2801915708222</v>
       </c>
       <c r="I117" t="n">
-        <v>7.063118547189935</v>
+        <v>7.828166552317484</v>
       </c>
     </row>
     <row r="118">
@@ -4081,25 +4081,25 @@
         <v>600</v>
       </c>
       <c r="C118" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D118" t="n">
-        <v>-49.88926696777344</v>
+        <v>-47.74227905273438</v>
       </c>
       <c r="E118" t="n">
-        <v>59.70863342285156</v>
+        <v>60.00752258300781</v>
       </c>
       <c r="F118" t="n">
-        <v>-17092248.7870636</v>
+        <v>-162451.2400512695</v>
       </c>
       <c r="G118" t="n">
-        <v>-1.725713205528586</v>
+        <v>-0.03260649014763105</v>
       </c>
       <c r="H118" t="n">
-        <v>52.7351273484099</v>
+        <v>70.39565637919686</v>
       </c>
       <c r="I118" t="n">
-        <v>7.261895575427252</v>
+        <v>8.390211938872394</v>
       </c>
     </row>
     <row r="119">
@@ -4112,25 +4112,25 @@
         <v>550</v>
       </c>
       <c r="C119" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D119" t="n">
-        <v>-47.72129821777344</v>
+        <v>-47.59382629394531</v>
       </c>
       <c r="E119" t="n">
-        <v>63.10870361328125</v>
+        <v>66.53193664550781</v>
       </c>
       <c r="F119" t="n">
-        <v>-13342884.38479614</v>
+        <v>135253.9615478516</v>
       </c>
       <c r="G119" t="n">
-        <v>-1.347159877529471</v>
+        <v>0.02714757340877061</v>
       </c>
       <c r="H119" t="n">
-        <v>57.59203663136957</v>
+        <v>83.33834638471465</v>
       </c>
       <c r="I119" t="n">
-        <v>7.588941733296519</v>
+        <v>9.128983863755849</v>
       </c>
     </row>
     <row r="120">
@@ -4143,25 +4143,25 @@
         <v>500</v>
       </c>
       <c r="C120" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D120" t="n">
-        <v>-45.96467590332031</v>
+        <v>-48.11669921875</v>
       </c>
       <c r="E120" t="n">
-        <v>68.8433837890625</v>
+        <v>74.33509826660156</v>
       </c>
       <c r="F120" t="n">
-        <v>-8081665.683181763</v>
+        <v>371984.4376220703</v>
       </c>
       <c r="G120" t="n">
-        <v>-0.8159626837803535</v>
+        <v>0.07466306133808365</v>
       </c>
       <c r="H120" t="n">
-        <v>64.79807183038747</v>
+        <v>101.3578127589477</v>
       </c>
       <c r="I120" t="n">
-        <v>8.049724953710374</v>
+        <v>10.06766173244551</v>
       </c>
     </row>
     <row r="121">
@@ -4174,25 +4174,25 @@
         <v>450</v>
       </c>
       <c r="C121" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D121" t="n">
-        <v>-44.16006469726562</v>
+        <v>-49.72097778320312</v>
       </c>
       <c r="E121" t="n">
-        <v>75.38790893554688</v>
+        <v>83.99830627441406</v>
       </c>
       <c r="F121" t="n">
-        <v>-1392350.452362061</v>
+        <v>1298237.05682373</v>
       </c>
       <c r="G121" t="n">
-        <v>-0.1405781996447121</v>
+        <v>0.2605763661099276</v>
       </c>
       <c r="H121" t="n">
-        <v>75.03823965913674</v>
+        <v>125.0009196980034</v>
       </c>
       <c r="I121" t="n">
-        <v>8.66246152425145</v>
+        <v>11.18038101756838</v>
       </c>
     </row>
     <row r="122">
@@ -4205,25 +4205,25 @@
         <v>400</v>
       </c>
       <c r="C122" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D122" t="n">
-        <v>-42.07801818847656</v>
+        <v>-49.22892761230469</v>
       </c>
       <c r="E122" t="n">
-        <v>77.19903564453125</v>
+        <v>93.02210998535156</v>
       </c>
       <c r="F122" t="n">
-        <v>6677834.168365479</v>
+        <v>2866455.565109253</v>
       </c>
       <c r="G122" t="n">
-        <v>0.6742253024891826</v>
+        <v>0.5753422079933465</v>
       </c>
       <c r="H122" t="n">
-        <v>89.72428834889688</v>
+        <v>154.3623129181507</v>
       </c>
       <c r="I122" t="n">
-        <v>9.472290554501424</v>
+        <v>12.42426307344426</v>
       </c>
     </row>
     <row r="123">
@@ -4236,25 +4236,25 @@
         <v>350</v>
       </c>
       <c r="C123" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D123" t="n">
-        <v>-43.08665466308594</v>
+        <v>-46.3956298828125</v>
       </c>
       <c r="E123" t="n">
-        <v>84.96342468261719</v>
+        <v>99.10317993164062</v>
       </c>
       <c r="F123" t="n">
-        <v>17055716.34919739</v>
+        <v>5166827.908493042</v>
       </c>
       <c r="G123" t="n">
-        <v>1.72202472010801</v>
+        <v>1.03706271026069</v>
       </c>
       <c r="H123" t="n">
-        <v>110.8579537774895</v>
+        <v>191.7870880492768</v>
       </c>
       <c r="I123" t="n">
-        <v>10.52891037940249</v>
+        <v>13.84872153122001</v>
       </c>
     </row>
     <row r="124">
@@ -4267,25 +4267,25 @@
         <v>300</v>
       </c>
       <c r="C124" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D124" t="n">
-        <v>-48.26020812988281</v>
+        <v>-41.59117126464844</v>
       </c>
       <c r="E124" t="n">
-        <v>87.12361145019531</v>
+        <v>102.8563232421875</v>
       </c>
       <c r="F124" t="n">
-        <v>30137028.19355774</v>
+        <v>7084700.482284546</v>
       </c>
       <c r="G124" t="n">
-        <v>3.042775013219585</v>
+        <v>1.422009560540235</v>
       </c>
       <c r="H124" t="n">
-        <v>139.3159406519879</v>
+        <v>240.0070220267403</v>
       </c>
       <c r="I124" t="n">
-        <v>11.80321738561092</v>
+        <v>15.49216001811046</v>
       </c>
     </row>
     <row r="125">
@@ -4298,25 +4298,25 @@
         <v>250</v>
       </c>
       <c r="C125" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D125" t="n">
-        <v>-47.76541137695312</v>
+        <v>-42.46122741699219</v>
       </c>
       <c r="E125" t="n">
-        <v>82.59519958496094</v>
+        <v>101.2830047607422</v>
       </c>
       <c r="F125" t="n">
-        <v>37787374.69078064</v>
+        <v>7536587.534103394</v>
       </c>
       <c r="G125" t="n">
-        <v>3.815189699057711</v>
+        <v>1.5127103191083</v>
       </c>
       <c r="H125" t="n">
-        <v>154.0149336731059</v>
+        <v>264.5280073388265</v>
       </c>
       <c r="I125" t="n">
-        <v>12.41027532624099</v>
+        <v>16.26431699576796</v>
       </c>
     </row>
     <row r="126">
@@ -4329,25 +4329,25 @@
         <v>200</v>
       </c>
       <c r="C126" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D126" t="n">
-        <v>-42.19203186035156</v>
+        <v>-42.65321350097656</v>
       </c>
       <c r="E126" t="n">
-        <v>84.77070617675781</v>
+        <v>101.8826599121094</v>
       </c>
       <c r="F126" t="n">
-        <v>46038909.79142761</v>
+        <v>7051499.298553467</v>
       </c>
       <c r="G126" t="n">
-        <v>4.648303191990639</v>
+        <v>1.415345566655821</v>
       </c>
       <c r="H126" t="n">
-        <v>162.6779853278291</v>
+        <v>285.3466297528597</v>
       </c>
       <c r="I126" t="n">
-        <v>12.75452803234322</v>
+        <v>16.89220618370673</v>
       </c>
     </row>
     <row r="127">
@@ -4360,25 +4360,25 @@
         <v>150</v>
       </c>
       <c r="C127" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D127" t="n">
-        <v>-41.26174926757812</v>
+        <v>-47.66954040527344</v>
       </c>
       <c r="E127" t="n">
-        <v>79.56495666503906</v>
+        <v>97.74311828613281</v>
       </c>
       <c r="F127" t="n">
-        <v>51891153.00796509</v>
+        <v>4766252.659759521</v>
       </c>
       <c r="G127" t="n">
-        <v>5.239172979024613</v>
+        <v>0.9566610285185716</v>
       </c>
       <c r="H127" t="n">
-        <v>155.8666527236148</v>
+        <v>296.5012213622478</v>
       </c>
       <c r="I127" t="n">
-        <v>12.4846566922609</v>
+        <v>17.21921082286432</v>
       </c>
     </row>
     <row r="128">
@@ -4391,25 +4391,25 @@
         <v>100</v>
       </c>
       <c r="C128" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D128" t="n">
-        <v>-41.47625732421875</v>
+        <v>-46.87788391113281</v>
       </c>
       <c r="E128" t="n">
-        <v>72.023681640625</v>
+        <v>88.11170959472656</v>
       </c>
       <c r="F128" t="n">
-        <v>51835718.18338013</v>
+        <v>-295739.7707519531</v>
       </c>
       <c r="G128" t="n">
-        <v>5.233576020425165</v>
+        <v>-0.05935957102108186</v>
       </c>
       <c r="H128" t="n">
-        <v>130.229618442277</v>
+        <v>290.0494297120348</v>
       </c>
       <c r="I128" t="n">
-        <v>11.411819243323</v>
+        <v>17.03083761040645</v>
       </c>
     </row>
     <row r="129">
@@ -4422,25 +4422,25 @@
         <v>1000</v>
       </c>
       <c r="C129" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D129" t="n">
-        <v>-37.298583984375</v>
+        <v>-30.80792236328125</v>
       </c>
       <c r="E129" t="n">
-        <v>34.28530883789062</v>
+        <v>33.40806579589844</v>
       </c>
       <c r="F129" t="n">
-        <v>2722053.059677124</v>
+        <v>3999496.444046021</v>
       </c>
       <c r="G129" t="n">
-        <v>0.2748311804816246</v>
+        <v>0.8027611322456606</v>
       </c>
       <c r="H129" t="n">
-        <v>14.30414320368521</v>
+        <v>16.06409547684538</v>
       </c>
       <c r="I129" t="n">
-        <v>3.782081861050235</v>
+        <v>4.008003926750245</v>
       </c>
     </row>
     <row r="130">
@@ -4453,25 +4453,25 @@
         <v>975</v>
       </c>
       <c r="C130" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D130" t="n">
-        <v>-39.46832275390625</v>
+        <v>-37.37339782714844</v>
       </c>
       <c r="E130" t="n">
-        <v>41.77491760253906</v>
+        <v>39.17864990234375</v>
       </c>
       <c r="F130" t="n">
-        <v>3317250.00680542</v>
+        <v>4638515.900466919</v>
       </c>
       <c r="G130" t="n">
-        <v>0.334925041994276</v>
+        <v>0.9310222745019819</v>
       </c>
       <c r="H130" t="n">
-        <v>16.9563766958445</v>
+        <v>19.50837468108423</v>
       </c>
       <c r="I130" t="n">
-        <v>4.117812124884343</v>
+        <v>4.416828577280788</v>
       </c>
     </row>
     <row r="131">
@@ -4484,25 +4484,25 @@
         <v>950</v>
       </c>
       <c r="C131" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D131" t="n">
-        <v>-54.18948364257812</v>
+        <v>-50.78488159179688</v>
       </c>
       <c r="E131" t="n">
-        <v>59.4952392578125</v>
+        <v>53.43524169921875</v>
       </c>
       <c r="F131" t="n">
-        <v>4336245.421279907</v>
+        <v>4982099.215103149</v>
       </c>
       <c r="G131" t="n">
-        <v>0.4378075745995006</v>
+        <v>0.9999847887926752</v>
       </c>
       <c r="H131" t="n">
-        <v>17.72748990822002</v>
+        <v>20.58052283118051</v>
       </c>
       <c r="I131" t="n">
-        <v>4.210402582677816</v>
+        <v>4.536576113235676</v>
       </c>
     </row>
     <row r="132">
@@ -4515,25 +4515,25 @@
         <v>925</v>
       </c>
       <c r="C132" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D132" t="n">
-        <v>-61.78614807128906</v>
+        <v>-59.95918273925781</v>
       </c>
       <c r="E132" t="n">
-        <v>64.50277709960938</v>
+        <v>63.70193481445312</v>
       </c>
       <c r="F132" t="n">
-        <v>5148640.639938354</v>
+        <v>5120522.690963745</v>
       </c>
       <c r="G132" t="n">
-        <v>0.5198307872506207</v>
+        <v>1.027768533012936</v>
       </c>
       <c r="H132" t="n">
-        <v>17.07536442418462</v>
+        <v>20.14836516583944</v>
       </c>
       <c r="I132" t="n">
-        <v>4.132234797804285</v>
+        <v>4.488693035376716</v>
       </c>
     </row>
     <row r="133">
@@ -4546,25 +4546,25 @@
         <v>900</v>
       </c>
       <c r="C133" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D133" t="n">
-        <v>-62.3619384765625</v>
+        <v>-62.70808410644531</v>
       </c>
       <c r="E133" t="n">
-        <v>65.13273620605469</v>
+        <v>68.14022827148438</v>
       </c>
       <c r="F133" t="n">
-        <v>5514459.938323975</v>
+        <v>5097631.94493103</v>
       </c>
       <c r="G133" t="n">
-        <v>0.5567656108613738</v>
+        <v>1.023174004311579</v>
       </c>
       <c r="H133" t="n">
-        <v>16.14136307614882</v>
+        <v>19.2491159085588</v>
       </c>
       <c r="I133" t="n">
-        <v>4.01763152568137</v>
+        <v>4.387381440968952</v>
       </c>
     </row>
     <row r="134">
@@ -4577,25 +4577,25 @@
         <v>875</v>
       </c>
       <c r="C134" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D134" t="n">
-        <v>-60.04344177246094</v>
+        <v>-61.24490356445312</v>
       </c>
       <c r="E134" t="n">
-        <v>66.50411987304688</v>
+        <v>67.74917602539062</v>
       </c>
       <c r="F134" t="n">
-        <v>5589507.06791687</v>
+        <v>4993456.940750122</v>
       </c>
       <c r="G134" t="n">
-        <v>0.564342719303268</v>
+        <v>1.002264460953325</v>
       </c>
       <c r="H134" t="n">
-        <v>15.45974643937352</v>
+        <v>18.45042714570938</v>
       </c>
       <c r="I134" t="n">
-        <v>3.931888406271663</v>
+        <v>4.295396040612482</v>
       </c>
     </row>
     <row r="135">
@@ -4608,25 +4608,25 @@
         <v>850</v>
       </c>
       <c r="C135" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D135" t="n">
-        <v>-58.49705505371094</v>
+        <v>-58.14166259765625</v>
       </c>
       <c r="E135" t="n">
-        <v>66.01028442382812</v>
+        <v>63.97665405273438</v>
       </c>
       <c r="F135" t="n">
-        <v>5510976.213912964</v>
+        <v>4838445.395782471</v>
       </c>
       <c r="G135" t="n">
-        <v>0.5564138777866089</v>
+        <v>0.9711512333032183</v>
       </c>
       <c r="H135" t="n">
-        <v>15.12214828476894</v>
+        <v>17.94719962372668</v>
       </c>
       <c r="I135" t="n">
-        <v>3.888720648846988</v>
+        <v>4.236413533134681</v>
       </c>
     </row>
     <row r="136">
@@ -4639,25 +4639,25 @@
         <v>825</v>
       </c>
       <c r="C136" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D136" t="n">
-        <v>-57.33427429199219</v>
+        <v>-54.58976745605469</v>
       </c>
       <c r="E136" t="n">
-        <v>64.4208984375</v>
+        <v>61.52851867675781</v>
       </c>
       <c r="F136" t="n">
-        <v>5350445.757858276</v>
+        <v>4669613.049453735</v>
       </c>
       <c r="G136" t="n">
-        <v>0.540205973762137</v>
+        <v>0.9372639558935082</v>
       </c>
       <c r="H136" t="n">
-        <v>15.01834188021675</v>
+        <v>17.69958891927202</v>
       </c>
       <c r="I136" t="n">
-        <v>3.875350549333151</v>
+        <v>4.20708793814344</v>
       </c>
     </row>
     <row r="137">
@@ -4670,25 +4670,25 @@
         <v>800</v>
       </c>
       <c r="C137" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D137" t="n">
-        <v>-56.57296752929688</v>
+        <v>-51.47319030761719</v>
       </c>
       <c r="E137" t="n">
-        <v>62.50079345703125</v>
+        <v>60.57154846191406</v>
       </c>
       <c r="F137" t="n">
-        <v>5195667.209335327</v>
+        <v>4501043.197143555</v>
       </c>
       <c r="G137" t="n">
-        <v>0.5245788091657099</v>
+        <v>0.9034293651153473</v>
       </c>
       <c r="H137" t="n">
-        <v>15.05579209600858</v>
+        <v>17.63776843869502</v>
       </c>
       <c r="I137" t="n">
-        <v>3.880179389668548</v>
+        <v>4.199734329537407</v>
       </c>
     </row>
     <row r="138">
@@ -4701,25 +4701,25 @@
         <v>775</v>
       </c>
       <c r="C138" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D138" t="n">
-        <v>-55.9935302734375</v>
+        <v>-52.31842041015625</v>
       </c>
       <c r="E138" t="n">
-        <v>60.65386962890625</v>
+        <v>59.73426818847656</v>
       </c>
       <c r="F138" t="n">
-        <v>5040895.727371216</v>
+        <v>4325399.032455444</v>
       </c>
       <c r="G138" t="n">
-        <v>0.5089523580420352</v>
+        <v>0.8681748498307348</v>
       </c>
       <c r="H138" t="n">
-        <v>15.19906026417564</v>
+        <v>17.67773863566617</v>
       </c>
       <c r="I138" t="n">
-        <v>3.898597217484212</v>
+        <v>4.204490294395525</v>
       </c>
     </row>
     <row r="139">
@@ -4732,25 +4732,25 @@
         <v>750</v>
       </c>
       <c r="C139" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D139" t="n">
-        <v>-54.71180725097656</v>
+        <v>-51.91337585449219</v>
       </c>
       <c r="E139" t="n">
-        <v>60.21696472167969</v>
+        <v>59.91481018066406</v>
       </c>
       <c r="F139" t="n">
-        <v>4870023.809310913</v>
+        <v>4143153.871963501</v>
       </c>
       <c r="G139" t="n">
-        <v>0.4917003317508046</v>
+        <v>0.831595412036611</v>
       </c>
       <c r="H139" t="n">
-        <v>15.43317483305329</v>
+        <v>17.84372381456459</v>
       </c>
       <c r="I139" t="n">
-        <v>3.928507965252621</v>
+        <v>4.224183212712795</v>
       </c>
     </row>
     <row r="140">
@@ -4763,25 +4763,25 @@
         <v>725</v>
       </c>
       <c r="C140" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D140" t="n">
-        <v>-50.73023986816406</v>
+        <v>-49.68173217773438</v>
       </c>
       <c r="E140" t="n">
-        <v>59.89950561523438</v>
+        <v>60.3739013671875</v>
       </c>
       <c r="F140" t="n">
-        <v>4468144.072311401</v>
+        <v>3807904.766677856</v>
       </c>
       <c r="G140" t="n">
-        <v>0.4511246779667738</v>
+        <v>0.764305703167363</v>
       </c>
       <c r="H140" t="n">
-        <v>16.1600652836442</v>
+        <v>18.29018231382538</v>
       </c>
       <c r="I140" t="n">
-        <v>4.019958368396892</v>
+        <v>4.276702270888795</v>
       </c>
     </row>
     <row r="141">
@@ -4794,25 +4794,25 @@
         <v>700</v>
       </c>
       <c r="C141" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D141" t="n">
-        <v>-45.50639343261719</v>
+        <v>-45.26548767089844</v>
       </c>
       <c r="E141" t="n">
-        <v>58.38702392578125</v>
+        <v>58.09425354003906</v>
       </c>
       <c r="F141" t="n">
-        <v>4015814.099975586</v>
+        <v>3659131.139602661</v>
       </c>
       <c r="G141" t="n">
-        <v>0.405455332976482</v>
+        <v>0.7344445226437575</v>
       </c>
       <c r="H141" t="n">
-        <v>17.17154041476632</v>
+        <v>19.06268790532804</v>
       </c>
       <c r="I141" t="n">
-        <v>4.143855742514007</v>
+        <v>4.366083817945785</v>
       </c>
     </row>
     <row r="142">
@@ -4825,25 +4825,25 @@
         <v>650</v>
       </c>
       <c r="C142" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D142" t="n">
-        <v>-43.6400146484375</v>
+        <v>-41.62356567382812</v>
       </c>
       <c r="E142" t="n">
-        <v>56.6099853515625</v>
+        <v>55.09764099121094</v>
       </c>
       <c r="F142" t="n">
-        <v>3096296.016693115</v>
+        <v>3519474.265228271</v>
       </c>
       <c r="G142" t="n">
-        <v>0.3126164959801551</v>
+        <v>0.706413216161269</v>
       </c>
       <c r="H142" t="n">
-        <v>17.99134883299492</v>
+        <v>20.22542204171953</v>
       </c>
       <c r="I142" t="n">
-        <v>4.241621014776652</v>
+        <v>4.49726828660683</v>
       </c>
     </row>
     <row r="143">
@@ -4856,25 +4856,25 @@
         <v>600</v>
       </c>
       <c r="C143" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D143" t="n">
-        <v>-43.83694458007812</v>
+        <v>-41.93943786621094</v>
       </c>
       <c r="E143" t="n">
-        <v>54.10940551757812</v>
+        <v>55.90625</v>
       </c>
       <c r="F143" t="n">
-        <v>1683393.780944824</v>
+        <v>3192674.184677124</v>
       </c>
       <c r="G143" t="n">
-        <v>0.1699632923714456</v>
+        <v>0.6408193579465045</v>
       </c>
       <c r="H143" t="n">
-        <v>18.88071287889355</v>
+        <v>21.65343961331599</v>
       </c>
       <c r="I143" t="n">
-        <v>4.345194227982628</v>
+        <v>4.653325650899149</v>
       </c>
     </row>
     <row r="144">
@@ -4887,25 +4887,25 @@
         <v>550</v>
       </c>
       <c r="C144" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D144" t="n">
-        <v>-46.11848449707031</v>
+        <v>-44.40814208984375</v>
       </c>
       <c r="E144" t="n">
-        <v>51.68350219726562</v>
+        <v>55.96891784667969</v>
       </c>
       <c r="F144" t="n">
-        <v>876209.2996063232</v>
+        <v>2717853.637664795</v>
       </c>
       <c r="G144" t="n">
-        <v>0.08846618007818947</v>
+        <v>0.5455154902557194</v>
       </c>
       <c r="H144" t="n">
-        <v>20.73150990335025</v>
+        <v>23.32656365691149</v>
       </c>
       <c r="I144" t="n">
-        <v>4.553186785466884</v>
+        <v>4.829758136481732</v>
       </c>
     </row>
     <row r="145">
@@ -4918,25 +4918,25 @@
         <v>500</v>
       </c>
       <c r="C145" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D145" t="n">
-        <v>-53.49273681640625</v>
+        <v>-47.26991271972656</v>
       </c>
       <c r="E145" t="n">
-        <v>55.87313842773438</v>
+        <v>54.57283020019531</v>
       </c>
       <c r="F145" t="n">
-        <v>606624.3642425537</v>
+        <v>2174759.988067627</v>
       </c>
       <c r="G145" t="n">
-        <v>0.06124762687523455</v>
+        <v>0.4365081491652988</v>
       </c>
       <c r="H145" t="n">
-        <v>24.43359387259374</v>
+        <v>26.21070706591205</v>
       </c>
       <c r="I145" t="n">
-        <v>4.94303488482468</v>
+        <v>5.119639349203424</v>
       </c>
     </row>
     <row r="146">
@@ -4949,25 +4949,25 @@
         <v>450</v>
       </c>
       <c r="C146" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D146" t="n">
-        <v>-60.30949401855469</v>
+        <v>-49.80780029296875</v>
       </c>
       <c r="E146" t="n">
-        <v>60.88302612304688</v>
+        <v>51.39276123046875</v>
       </c>
       <c r="F146" t="n">
-        <v>442040.8657684326</v>
+        <v>1665879.236801147</v>
       </c>
       <c r="G146" t="n">
-        <v>0.04463050877291382</v>
+        <v>0.3343678688125457</v>
       </c>
       <c r="H146" t="n">
-        <v>30.59825982524179</v>
+        <v>30.5805031904817</v>
       </c>
       <c r="I146" t="n">
-        <v>5.531569381761544</v>
+        <v>5.52996412198865</v>
       </c>
     </row>
     <row r="147">
@@ -4980,25 +4980,25 @@
         <v>400</v>
       </c>
       <c r="C147" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D147" t="n">
-        <v>-65.55380249023438</v>
+        <v>-52.41317749023438</v>
       </c>
       <c r="E147" t="n">
-        <v>69.10142517089844</v>
+        <v>57.25358581542969</v>
       </c>
       <c r="F147" t="n">
-        <v>-1297944.910583496</v>
+        <v>831108.5536651611</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.1310465755645817</v>
+        <v>0.1668164112390995</v>
       </c>
       <c r="H147" t="n">
-        <v>39.86690231730142</v>
+        <v>37.05739293579857</v>
       </c>
       <c r="I147" t="n">
-        <v>6.314024256945915</v>
+        <v>6.087478372511772</v>
       </c>
     </row>
     <row r="148">
@@ -5011,25 +5011,25 @@
         <v>350</v>
       </c>
       <c r="C148" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D148" t="n">
-        <v>-68.04991149902344</v>
+        <v>-63.99067687988281</v>
       </c>
       <c r="E148" t="n">
-        <v>75.79129028320312</v>
+        <v>66.78927612304688</v>
       </c>
       <c r="F148" t="n">
-        <v>-4485034.063308716</v>
+        <v>-1666011.722610474</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.4528299702819311</v>
+        <v>-0.3343944607747565</v>
       </c>
       <c r="H148" t="n">
-        <v>54.34302113850518</v>
+        <v>46.67157053215963</v>
       </c>
       <c r="I148" t="n">
-        <v>7.371771913082036</v>
+        <v>6.831659427412906</v>
       </c>
     </row>
     <row r="149">
@@ -5042,25 +5042,25 @@
         <v>300</v>
       </c>
       <c r="C149" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D149" t="n">
-        <v>-75.88917541503906</v>
+        <v>-78.40255737304688</v>
       </c>
       <c r="E149" t="n">
-        <v>76.22332763671875</v>
+        <v>66.33203125</v>
       </c>
       <c r="F149" t="n">
-        <v>-7393021.889068604</v>
+        <v>-5870781.259658813</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.7464339924880878</v>
+        <v>-1.17835709497535</v>
       </c>
       <c r="H149" t="n">
-        <v>74.46044016084734</v>
+        <v>62.70170680732002</v>
       </c>
       <c r="I149" t="n">
-        <v>8.629046306565247</v>
+        <v>7.918440932868037</v>
       </c>
     </row>
     <row r="150">
@@ -5073,25 +5073,25 @@
         <v>250</v>
       </c>
       <c r="C150" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D150" t="n">
-        <v>-75.75390625</v>
+        <v>-80.1456298828125</v>
       </c>
       <c r="E150" t="n">
-        <v>76.65879821777344</v>
+        <v>60.91340637207031</v>
       </c>
       <c r="F150" t="n">
-        <v>-7878754.465148926</v>
+        <v>-8390917.045455933</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.7954758202393685</v>
+        <v>-1.684187537662958</v>
       </c>
       <c r="H150" t="n">
-        <v>82.81196684952947</v>
+        <v>72.31689666586263</v>
       </c>
       <c r="I150" t="n">
-        <v>9.100108068013778</v>
+        <v>8.503934187531241</v>
       </c>
     </row>
     <row r="151">
@@ -5104,25 +5104,25 @@
         <v>200</v>
       </c>
       <c r="C151" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D151" t="n">
-        <v>-73.10708618164062</v>
+        <v>-72.71397399902344</v>
       </c>
       <c r="E151" t="n">
-        <v>73.15193176269531</v>
+        <v>65.52130126953125</v>
       </c>
       <c r="F151" t="n">
-        <v>-7850755.585342407</v>
+        <v>-10962300.03987122</v>
       </c>
       <c r="G151" t="n">
-        <v>-0.7926489226658529</v>
+        <v>-2.200304092062438</v>
       </c>
       <c r="H151" t="n">
-        <v>84.7807729290198</v>
+        <v>79.70852145545834</v>
       </c>
       <c r="I151" t="n">
-        <v>9.207647524151856</v>
+        <v>8.927962895053851</v>
       </c>
     </row>
     <row r="152">
@@ -5135,25 +5135,25 @@
         <v>150</v>
       </c>
       <c r="C152" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D152" t="n">
-        <v>-67.24429321289062</v>
+        <v>-72.9625244140625</v>
       </c>
       <c r="E152" t="n">
-        <v>68.32243347167969</v>
+        <v>61.62760925292969</v>
       </c>
       <c r="F152" t="n">
-        <v>-7648084.759048462</v>
+        <v>-13336182.41790771</v>
       </c>
       <c r="G152" t="n">
-        <v>-0.7721863301967119</v>
+        <v>-2.676779201434653</v>
       </c>
       <c r="H152" t="n">
-        <v>76.23530081738039</v>
+        <v>82.00809858341998</v>
       </c>
       <c r="I152" t="n">
-        <v>8.731282884970593</v>
+        <v>9.055832296560045</v>
       </c>
     </row>
     <row r="153">
@@ -5166,25 +5166,25 @@
         <v>100</v>
       </c>
       <c r="C153" t="n">
-        <v>9904455</v>
+        <v>4982175</v>
       </c>
       <c r="D153" t="n">
-        <v>-56.85836791992188</v>
+        <v>-60.74427795410156</v>
       </c>
       <c r="E153" t="n">
-        <v>53.3455810546875</v>
+        <v>50.53684997558594</v>
       </c>
       <c r="F153" t="n">
-        <v>-6530851.576309204</v>
+        <v>-13901610.35908508</v>
       </c>
       <c r="G153" t="n">
-        <v>-0.6593852540406531</v>
+        <v>-2.790269382164429</v>
       </c>
       <c r="H153" t="n">
-        <v>58.35943216376103</v>
+        <v>76.2130067721568</v>
       </c>
       <c r="I153" t="n">
-        <v>7.639334536709401</v>
+        <v>8.730006115241661</v>
       </c>
     </row>
   </sheetData>
